--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -2876,10 +2876,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122717554</v>
+        <v>122716416</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>78762</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2888,30 +2888,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2919,21 +2919,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452007</v>
+        <v>451964</v>
       </c>
       <c r="R19" t="n">
-        <v>7029050</v>
+        <v>7029026</v>
       </c>
       <c r="S19" t="n">
         <v>6</v>
@@ -2965,7 +2960,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2975,12 +2970,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2994,17 +2989,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3022,10 +3017,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122717325</v>
+        <v>122717554</v>
       </c>
       <c r="B20" t="n">
-        <v>79843</v>
+        <v>79714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3034,30 +3029,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3065,19 +3060,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452006</v>
+        <v>452007</v>
       </c>
       <c r="R20" t="n">
-        <v>7029026</v>
+        <v>7029050</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3163,10 +3163,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122716868</v>
+        <v>122717325</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3179,27 +3179,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3208,13 +3212,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451931</v>
+        <v>452006</v>
       </c>
       <c r="R21" t="n">
-        <v>7029005</v>
+        <v>7029026</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3243,7 +3247,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3253,12 +3257,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3272,17 +3276,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3300,10 +3304,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122716416</v>
+        <v>122717285</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3316,31 +3320,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3349,13 +3349,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451964</v>
+        <v>452000</v>
       </c>
       <c r="R22" t="n">
         <v>7029026</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3410,21 +3410,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3441,7 +3426,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122717285</v>
+        <v>122716868</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3486,13 +3471,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452000</v>
+        <v>451931</v>
       </c>
       <c r="R23" t="n">
-        <v>7029026</v>
+        <v>7029005</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3521,7 +3506,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3531,12 +3516,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3547,6 +3532,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3563,10 +3563,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715391</v>
+        <v>122715838</v>
       </c>
       <c r="B24" t="n">
-        <v>79803</v>
+        <v>74863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3575,25 +3575,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452136</v>
+        <v>452109</v>
       </c>
       <c r="R24" t="n">
-        <v>7029025</v>
+        <v>7029006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3664,6 +3664,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3680,10 +3695,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715838</v>
+        <v>122715391</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>79803</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3692,25 +3707,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3720,10 +3735,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452109</v>
+        <v>452136</v>
       </c>
       <c r="R25" t="n">
-        <v>7029006</v>
+        <v>7029025</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3755,7 +3770,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3765,12 +3780,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3781,21 +3796,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122717356</v>
+        <v>122717401</v>
       </c>
       <c r="B33" t="n">
         <v>78762</v>
@@ -4716,13 +4716,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452001</v>
+        <v>452013</v>
       </c>
       <c r="R33" t="n">
-        <v>7029043</v>
+        <v>7029064</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4780,17 +4780,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122719701</v>
+        <v>122715547</v>
       </c>
       <c r="B34" t="n">
-        <v>79747</v>
+        <v>79878</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4824,46 +4824,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452180</v>
+        <v>452141</v>
       </c>
       <c r="R34" t="n">
-        <v>7029296</v>
+        <v>7028992</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4892,7 +4883,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4902,12 +4893,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4927,17 +4918,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715007</v>
+        <v>122720150</v>
       </c>
       <c r="B35" t="n">
-        <v>79747</v>
+        <v>77699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4946,25 +4937,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4974,13 +4965,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452170</v>
+        <v>452132</v>
       </c>
       <c r="R35" t="n">
-        <v>7029085</v>
+        <v>7029266</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5009,7 +5000,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5019,12 +5010,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5038,17 +5029,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5066,10 +5057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122717401</v>
+        <v>122715754</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
+        <v>79803</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5078,50 +5069,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452013</v>
+        <v>452130</v>
       </c>
       <c r="R36" t="n">
-        <v>7029064</v>
+        <v>7029002</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5150,7 +5132,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5160,12 +5142,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5176,21 +5158,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>granar</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5207,10 +5174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122715547</v>
+        <v>122717356</v>
       </c>
       <c r="B37" t="n">
-        <v>79878</v>
+        <v>78762</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5219,20 +5186,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5240,20 +5207,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452141</v>
+        <v>452001</v>
       </c>
       <c r="R37" t="n">
-        <v>7028992</v>
+        <v>7029043</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5282,7 +5258,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5292,12 +5268,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5308,26 +5284,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122720150</v>
+        <v>122719701</v>
       </c>
       <c r="B38" t="n">
-        <v>77699</v>
+        <v>79747</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5336,38 +5327,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452132</v>
+        <v>452180</v>
       </c>
       <c r="R38" t="n">
-        <v>7029266</v>
+        <v>7029296</v>
       </c>
       <c r="S38" t="n">
         <v>8</v>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5425,41 +5425,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715754</v>
+        <v>122715007</v>
       </c>
       <c r="B39" t="n">
-        <v>79803</v>
+        <v>79747</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5472,21 +5457,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5496,10 +5481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452130</v>
+        <v>452170</v>
       </c>
       <c r="R39" t="n">
-        <v>7029002</v>
+        <v>7029085</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5531,7 +5516,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5541,12 +5526,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5557,6 +5542,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5573,10 +5573,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122719930</v>
+        <v>122715131</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>77699</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5589,46 +5589,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452148</v>
+        <v>452147</v>
       </c>
       <c r="R40" t="n">
-        <v>7029296</v>
+        <v>7029041</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5657,7 +5648,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5667,12 +5658,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5687,22 +5678,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122716759</v>
+        <v>122719930</v>
       </c>
       <c r="B41" t="n">
-        <v>79747</v>
+        <v>78762</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5711,30 +5702,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5748,10 +5739,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451898</v>
+        <v>452148</v>
       </c>
       <c r="R41" t="n">
-        <v>7028975</v>
+        <v>7029296</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5783,7 +5774,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5793,12 +5784,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5813,22 +5804,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122720261</v>
+        <v>122716759</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>79747</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5837,38 +5828,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452124</v>
+        <v>451898</v>
       </c>
       <c r="R42" t="n">
-        <v>7029259</v>
+        <v>7028975</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5926,41 +5926,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122715131</v>
+        <v>122720261</v>
       </c>
       <c r="B43" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5973,21 +5958,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5997,13 +5982,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452147</v>
+        <v>452124</v>
       </c>
       <c r="R43" t="n">
-        <v>7029041</v>
+        <v>7029259</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6032,7 +6017,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6042,12 +6027,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6058,16 +6043,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122714976</v>
+        <v>122717157</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6236,31 +6236,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6269,13 +6265,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452178</v>
+        <v>451983</v>
       </c>
       <c r="R45" t="n">
-        <v>7029092</v>
+        <v>7029027</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6304,7 +6300,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6314,7 +6310,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6329,19 +6330,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122719770</v>
+        <v>122714976</v>
       </c>
       <c r="B46" t="n">
         <v>78762</v>
@@ -6390,13 +6391,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452163</v>
+        <v>452178</v>
       </c>
       <c r="R46" t="n">
-        <v>7029302</v>
+        <v>7029092</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6425,7 +6426,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6435,12 +6436,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6460,17 +6456,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122717157</v>
+        <v>122719770</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6483,27 +6479,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6512,13 +6512,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451983</v>
+        <v>452163</v>
       </c>
       <c r="R47" t="n">
-        <v>7029027</v>
+        <v>7029302</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6577,22 +6577,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122716081</v>
+        <v>122717676</v>
       </c>
       <c r="B48" t="n">
-        <v>78955</v>
+        <v>79714</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6605,26 +6605,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230552</v>
+        <v>389</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6632,19 +6632,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452077</v>
+        <v>452027</v>
       </c>
       <c r="R48" t="n">
-        <v>7029012</v>
+        <v>7029091</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6673,7 +6678,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6683,12 +6688,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6702,17 +6707,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6730,7 +6735,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122717676</v>
+        <v>122716262</v>
       </c>
       <c r="B49" t="n">
         <v>79714</v>
@@ -6765,7 +6770,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6784,10 +6789,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452027</v>
+        <v>452093</v>
       </c>
       <c r="R49" t="n">
-        <v>7029091</v>
+        <v>7029013</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6819,7 +6824,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6829,12 +6834,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6845,21 +6850,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6876,10 +6866,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122716262</v>
+        <v>122716787</v>
       </c>
       <c r="B50" t="n">
-        <v>79714</v>
+        <v>79803</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6888,40 +6878,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6930,13 +6911,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452093</v>
+        <v>451914</v>
       </c>
       <c r="R50" t="n">
-        <v>7029013</v>
+        <v>7028996</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6965,7 +6946,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6975,12 +6956,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6991,6 +6972,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7007,10 +7003,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122715067</v>
+        <v>122716081</v>
       </c>
       <c r="B51" t="n">
-        <v>79747</v>
+        <v>78955</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7019,38 +7015,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>230552</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452163</v>
+        <v>452077</v>
       </c>
       <c r="R51" t="n">
-        <v>7029067</v>
+        <v>7029012</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -7082,7 +7087,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7092,12 +7097,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7111,17 +7116,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7139,10 +7144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122716787</v>
+        <v>122715067</v>
       </c>
       <c r="B52" t="n">
-        <v>79803</v>
+        <v>79747</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7155,42 +7160,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451914</v>
+        <v>452163</v>
       </c>
       <c r="R52" t="n">
-        <v>7028996</v>
+        <v>7029067</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7248,17 +7248,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -8450,10 +8450,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122719902</v>
+        <v>122716428</v>
       </c>
       <c r="B62" t="n">
-        <v>79844</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8466,46 +8466,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452150</v>
+        <v>451979</v>
       </c>
       <c r="R62" t="n">
-        <v>7029301</v>
+        <v>7029020</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8534,7 +8525,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8544,12 +8535,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8560,41 +8551,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716428</v>
+        <v>122719902</v>
       </c>
       <c r="B63" t="n">
-        <v>74863</v>
+        <v>79844</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8607,37 +8583,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451979</v>
+        <v>452150</v>
       </c>
       <c r="R63" t="n">
-        <v>7029020</v>
+        <v>7029301</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8666,7 +8651,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8676,12 +8661,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8692,16 +8677,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122715120</v>
+        <v>122717990</v>
       </c>
       <c r="B71" t="n">
-        <v>79803</v>
+        <v>79843</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9615,41 +9615,50 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452148</v>
+        <v>452063</v>
       </c>
       <c r="R71" t="n">
-        <v>7029055</v>
+        <v>7029079</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9678,7 +9687,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9688,12 +9697,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9708,22 +9717,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122717990</v>
+        <v>122715120</v>
       </c>
       <c r="B72" t="n">
-        <v>79843</v>
+        <v>79803</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9732,50 +9741,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452063</v>
+        <v>452148</v>
       </c>
       <c r="R72" t="n">
-        <v>7029079</v>
+        <v>7029055</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9834,12 +9834,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9967,10 +9967,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122720303</v>
+        <v>122719668</v>
       </c>
       <c r="B74" t="n">
-        <v>78762</v>
+        <v>79879</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9979,35 +9979,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -10016,10 +10012,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452124</v>
+        <v>452187</v>
       </c>
       <c r="R74" t="n">
-        <v>7029259</v>
+        <v>7029250</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10051,7 +10047,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10061,12 +10057,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10080,17 +10076,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10357,10 +10353,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122719668</v>
+        <v>122720303</v>
       </c>
       <c r="B77" t="n">
-        <v>79879</v>
+        <v>78762</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10369,31 +10365,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -10402,10 +10402,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452187</v>
+        <v>452124</v>
       </c>
       <c r="R77" t="n">
-        <v>7029250</v>
+        <v>7029259</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10466,17 +10466,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122717199</v>
+        <v>122715921</v>
       </c>
       <c r="B2" t="n">
-        <v>77699</v>
+        <v>79807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451981</v>
+        <v>452116</v>
       </c>
       <c r="R2" t="n">
-        <v>7029020</v>
+        <v>7028982</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +784,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715739</v>
+        <v>122719668</v>
       </c>
       <c r="B3" t="n">
-        <v>77699</v>
+        <v>79883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,41 +824,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452142</v>
+        <v>452187</v>
       </c>
       <c r="R3" t="n">
-        <v>7029004</v>
+        <v>7029250</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,26 +918,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122716687</v>
+        <v>122715067</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,46 +961,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451933</v>
+        <v>452163</v>
       </c>
       <c r="R4" t="n">
-        <v>7028984</v>
+        <v>7029067</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,26 +1050,41 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720088</v>
+        <v>122717632</v>
       </c>
       <c r="B5" t="n">
-        <v>79872</v>
+        <v>79718</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,38 +1093,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>389</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452118</v>
+        <v>452015</v>
       </c>
       <c r="R5" t="n">
-        <v>7029273</v>
+        <v>7029092</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1121,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1180,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,17 +1199,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122717632</v>
+        <v>122719912</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,30 +1239,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>389</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1221,24 +1270,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452015</v>
+        <v>452222</v>
       </c>
       <c r="R6" t="n">
-        <v>7029092</v>
+        <v>7029287</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1311,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,12 +1321,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,41 +1337,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122717731</v>
+        <v>122719982</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>79022</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,37 +1365,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>389</v>
+        <v>6459</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -1378,13 +1398,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452035</v>
+        <v>452143</v>
       </c>
       <c r="R7" t="n">
-        <v>7029085</v>
+        <v>7029283</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1413,7 +1433,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1423,12 +1443,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,17 +1462,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1470,10 +1490,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122715130</v>
+        <v>122719813</v>
       </c>
       <c r="B8" t="n">
-        <v>90951</v>
+        <v>79876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1486,21 +1506,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1510,10 +1530,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452148</v>
+        <v>452159</v>
       </c>
       <c r="R8" t="n">
-        <v>7029055</v>
+        <v>7029305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1545,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1555,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,6 +1591,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1587,10 +1622,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122716396</v>
+        <v>122716346</v>
       </c>
       <c r="B9" t="n">
-        <v>78846</v>
+        <v>74868</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1603,46 +1638,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451975</v>
+        <v>451984</v>
       </c>
       <c r="R9" t="n">
-        <v>7029033</v>
+        <v>7029029</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1671,7 +1697,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1681,12 +1707,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,6 +1723,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1713,10 +1754,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122719813</v>
+        <v>122717731</v>
       </c>
       <c r="B10" t="n">
-        <v>79872</v>
+        <v>79718</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1725,41 +1766,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>389</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452159</v>
+        <v>452035</v>
       </c>
       <c r="R10" t="n">
-        <v>7029305</v>
+        <v>7029085</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1788,7 +1843,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1798,12 +1853,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,17 +1872,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1845,10 +1900,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122715370</v>
+        <v>122720127</v>
       </c>
       <c r="B11" t="n">
-        <v>79298</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1861,26 +1916,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1352</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1890,7 +1945,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1899,13 +1954,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452135</v>
+        <v>452123</v>
       </c>
       <c r="R11" t="n">
-        <v>7029012</v>
+        <v>7029202</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1934,7 +1989,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,12 +1999,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1976,10 +2031,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720354</v>
+        <v>122715140</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1992,37 +2047,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452114</v>
+        <v>452148</v>
       </c>
       <c r="R12" t="n">
-        <v>7029211</v>
+        <v>7029055</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2051,7 +2115,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2061,12 +2125,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2081,22 +2145,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122715140</v>
+        <v>122716262</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>79718</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,35 +2169,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>389</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2142,13 +2211,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452148</v>
+        <v>452093</v>
       </c>
       <c r="R13" t="n">
-        <v>7029055</v>
+        <v>7029013</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2177,7 +2246,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2187,12 +2256,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2219,10 +2288,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122720379</v>
+        <v>122719930</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2268,13 +2337,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452127</v>
+        <v>452148</v>
       </c>
       <c r="R14" t="n">
-        <v>7029209</v>
+        <v>7029296</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2303,7 +2372,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2313,12 +2382,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2345,10 +2414,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122717893</v>
+        <v>122719902</v>
       </c>
       <c r="B15" t="n">
-        <v>79714</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2357,40 +2426,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>389</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2399,10 +2463,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452029</v>
+        <v>452150</v>
       </c>
       <c r="R15" t="n">
-        <v>7029076</v>
+        <v>7029301</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2434,7 +2498,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2444,12 +2508,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2463,17 +2527,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2491,10 +2555,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122715191</v>
+        <v>122715547</v>
       </c>
       <c r="B16" t="n">
-        <v>79747</v>
+        <v>79882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2507,21 +2571,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2531,13 +2595,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452150</v>
+        <v>452141</v>
       </c>
       <c r="R16" t="n">
-        <v>7029062</v>
+        <v>7028992</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2566,7 +2630,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2576,12 +2640,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2596,22 +2660,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715592</v>
+        <v>122720088</v>
       </c>
       <c r="B17" t="n">
-        <v>79803</v>
+        <v>79876</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2624,51 +2688,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452141</v>
+        <v>452118</v>
       </c>
       <c r="R17" t="n">
-        <v>7028992</v>
+        <v>7029273</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2697,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2707,12 +2757,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2723,26 +2773,41 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122716633</v>
+        <v>122717724</v>
       </c>
       <c r="B18" t="n">
-        <v>79872</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2751,31 +2816,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2784,13 +2853,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451941</v>
+        <v>452034</v>
       </c>
       <c r="R18" t="n">
-        <v>7028960</v>
+        <v>7029103</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2819,7 +2888,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2829,12 +2898,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2845,41 +2914,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122716416</v>
+        <v>122717199</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>77699</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2892,46 +2946,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451964</v>
+        <v>451981</v>
       </c>
       <c r="R19" t="n">
-        <v>7029026</v>
+        <v>7029020</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2960,7 +3005,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2970,12 +3015,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3017,10 +3062,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122717554</v>
+        <v>122715754</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>79807</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3029,55 +3074,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452007</v>
+        <v>452130</v>
       </c>
       <c r="R20" t="n">
-        <v>7029050</v>
+        <v>7029002</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3106,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3116,12 +3147,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3132,21 +3163,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3163,10 +3179,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122717325</v>
+        <v>122720379</v>
       </c>
       <c r="B21" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3179,26 +3195,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3212,13 +3228,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452006</v>
+        <v>452127</v>
       </c>
       <c r="R21" t="n">
-        <v>7029026</v>
+        <v>7029209</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3247,7 +3263,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3257,12 +3273,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3273,21 +3289,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3304,10 +3305,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122717285</v>
+        <v>122715838</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3320,39 +3321,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452000</v>
+        <v>452109</v>
       </c>
       <c r="R22" t="n">
-        <v>7029026</v>
+        <v>7029006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3384,7 +3380,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3394,12 +3390,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3410,6 +3406,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3426,10 +3437,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122716868</v>
+        <v>122720532</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3442,27 +3453,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3471,13 +3491,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451931</v>
+        <v>452156</v>
       </c>
       <c r="R23" t="n">
-        <v>7029005</v>
+        <v>7029109</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3506,7 +3526,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3516,12 +3536,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3563,10 +3583,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715838</v>
+        <v>122715104</v>
       </c>
       <c r="B24" t="n">
-        <v>74863</v>
+        <v>91389</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3575,25 +3595,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3603,13 +3623,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452109</v>
+        <v>452162</v>
       </c>
       <c r="R24" t="n">
-        <v>7029006</v>
+        <v>7029063</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3638,7 +3658,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3648,12 +3668,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3664,21 +3684,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3695,10 +3700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715391</v>
+        <v>122720150</v>
       </c>
       <c r="B25" t="n">
-        <v>79803</v>
+        <v>77699</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3707,25 +3712,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3735,13 +3740,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452136</v>
+        <v>452132</v>
       </c>
       <c r="R25" t="n">
-        <v>7029025</v>
+        <v>7029266</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3770,7 +3775,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3780,12 +3785,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3796,6 +3801,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3812,10 +3832,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122718456</v>
+        <v>122719822</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3824,46 +3844,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452038</v>
+        <v>452152</v>
       </c>
       <c r="R26" t="n">
-        <v>7029084</v>
+        <v>7029283</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3892,7 +3907,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3902,12 +3917,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3922,22 +3937,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715784</v>
+        <v>122715877</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>79751</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3946,50 +3961,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452116</v>
+        <v>452106</v>
       </c>
       <c r="R27" t="n">
-        <v>7029000</v>
+        <v>7028977</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4018,7 +4024,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4028,12 +4034,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4044,6 +4050,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4060,10 +4081,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122719605</v>
+        <v>122714960</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4076,46 +4097,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452187</v>
+        <v>452178</v>
       </c>
       <c r="R28" t="n">
-        <v>7029250</v>
+        <v>7029093</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4144,7 +4156,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4154,12 +4166,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4186,10 +4198,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122720194</v>
+        <v>122719701</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>79751</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4198,30 +4210,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4235,13 +4247,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452133</v>
+        <v>452180</v>
       </c>
       <c r="R29" t="n">
-        <v>7029299</v>
+        <v>7029296</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4270,7 +4282,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4280,12 +4292,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4305,17 +4317,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122715104</v>
+        <v>122716687</v>
       </c>
       <c r="B30" t="n">
-        <v>91385</v>
+        <v>90944</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4324,41 +4336,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452162</v>
+        <v>451933</v>
       </c>
       <c r="R30" t="n">
-        <v>7029063</v>
+        <v>7028984</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4387,7 +4404,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4397,12 +4414,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4417,22 +4434,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122717724</v>
+        <v>122714976</v>
       </c>
       <c r="B31" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4445,26 +4462,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4478,13 +4495,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452034</v>
+        <v>452178</v>
       </c>
       <c r="R31" t="n">
-        <v>7029103</v>
+        <v>7029092</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4513,7 +4530,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4523,12 +4540,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4555,10 +4567,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715650</v>
+        <v>122715859</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4571,21 +4583,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4595,13 +4607,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452125</v>
+        <v>452106</v>
       </c>
       <c r="R32" t="n">
-        <v>7028994</v>
+        <v>7028976</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4630,7 +4642,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4640,7 +4652,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4667,10 +4684,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122717401</v>
+        <v>122720266</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>77699</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4683,46 +4700,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452013</v>
+        <v>452125</v>
       </c>
       <c r="R33" t="n">
-        <v>7029064</v>
+        <v>7029254</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4751,7 +4759,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4761,12 +4769,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4777,41 +4785,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>granar</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715547</v>
+        <v>122715337</v>
       </c>
       <c r="B34" t="n">
-        <v>79878</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4820,20 +4813,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4841,20 +4834,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452141</v>
+        <v>452138</v>
       </c>
       <c r="R34" t="n">
-        <v>7028992</v>
+        <v>7029066</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4883,7 +4885,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4893,12 +4895,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4909,26 +4911,41 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720150</v>
+        <v>122720354</v>
       </c>
       <c r="B35" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4941,21 +4958,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4965,13 +4982,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452132</v>
+        <v>452114</v>
       </c>
       <c r="R35" t="n">
-        <v>7029266</v>
+        <v>7029211</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5000,7 +5017,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5010,12 +5027,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5026,41 +5043,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122715754</v>
+        <v>122715671</v>
       </c>
       <c r="B36" t="n">
-        <v>79803</v>
+        <v>79718</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5069,41 +5071,55 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452130</v>
+        <v>452132</v>
       </c>
       <c r="R36" t="n">
-        <v>7029002</v>
+        <v>7028982</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5132,7 +5148,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5142,12 +5158,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5158,6 +5174,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5174,10 +5205,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122717356</v>
+        <v>122717676</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>79718</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5186,30 +5217,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5217,16 +5248,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452001</v>
+        <v>452027</v>
       </c>
       <c r="R37" t="n">
-        <v>7029043</v>
+        <v>7029091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5258,7 +5294,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5268,12 +5304,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5287,17 +5323,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5315,10 +5351,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122719701</v>
+        <v>122715739</v>
       </c>
       <c r="B38" t="n">
-        <v>79747</v>
+        <v>77699</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5327,50 +5363,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452180</v>
+        <v>452142</v>
       </c>
       <c r="R38" t="n">
-        <v>7029296</v>
+        <v>7029004</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5399,7 +5426,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5409,12 +5436,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5434,17 +5461,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715007</v>
+        <v>122716633</v>
       </c>
       <c r="B39" t="n">
-        <v>79747</v>
+        <v>79876</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5457,37 +5484,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452170</v>
+        <v>451941</v>
       </c>
       <c r="R39" t="n">
-        <v>7029085</v>
+        <v>7028960</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5516,7 +5548,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5526,12 +5558,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5545,17 +5577,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5573,10 +5605,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122715131</v>
+        <v>122716759</v>
       </c>
       <c r="B40" t="n">
-        <v>77699</v>
+        <v>79751</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5585,41 +5617,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452147</v>
+        <v>451898</v>
       </c>
       <c r="R40" t="n">
-        <v>7029041</v>
+        <v>7028975</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5648,7 +5689,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5658,12 +5699,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5690,10 +5731,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122719930</v>
+        <v>122715130</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>90955</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5702,37 +5743,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
@@ -5742,7 +5774,7 @@
         <v>452148</v>
       </c>
       <c r="R41" t="n">
-        <v>7029296</v>
+        <v>7029055</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5774,7 +5806,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5784,12 +5816,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5816,10 +5848,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122716759</v>
+        <v>122720261</v>
       </c>
       <c r="B42" t="n">
-        <v>79747</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5828,47 +5860,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451898</v>
+        <v>452124</v>
       </c>
       <c r="R42" t="n">
-        <v>7028975</v>
+        <v>7029259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5900,7 +5923,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5910,12 +5933,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5926,26 +5949,41 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122720261</v>
+        <v>122715191</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5954,25 +5992,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5982,13 +6020,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452124</v>
+        <v>452150</v>
       </c>
       <c r="R43" t="n">
-        <v>7029259</v>
+        <v>7029062</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6017,7 +6055,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6027,12 +6065,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6043,21 +6081,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6074,10 +6097,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122715671</v>
+        <v>122716182</v>
       </c>
       <c r="B44" t="n">
-        <v>79714</v>
+        <v>57499</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6086,55 +6109,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>389</v>
+        <v>100110</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452132</v>
+        <v>452106</v>
       </c>
       <c r="R44" t="n">
-        <v>7028982</v>
+        <v>7028976</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6163,7 +6181,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6173,12 +6191,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6189,41 +6202,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717157</v>
+        <v>122717893</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79718</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6232,31 +6230,40 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>389</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6265,13 +6272,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451983</v>
+        <v>452029</v>
       </c>
       <c r="R45" t="n">
-        <v>7029027</v>
+        <v>7029076</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6300,7 +6307,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6310,12 +6317,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6326,6 +6333,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6342,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122714976</v>
+        <v>122717356</v>
       </c>
       <c r="B46" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6377,7 +6399,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6391,13 +6413,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452178</v>
+        <v>452001</v>
       </c>
       <c r="R46" t="n">
-        <v>7029092</v>
+        <v>7029043</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6426,7 +6448,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6436,7 +6458,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6447,26 +6474,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122719770</v>
+        <v>122718273</v>
       </c>
       <c r="B47" t="n">
-        <v>78762</v>
+        <v>57589</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6475,35 +6517,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6512,13 +6554,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452163</v>
+        <v>452012</v>
       </c>
       <c r="R47" t="n">
-        <v>7029302</v>
+        <v>7029081</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6547,7 +6589,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6557,12 +6599,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6577,22 +6619,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122717676</v>
+        <v>122719742</v>
       </c>
       <c r="B48" t="n">
-        <v>79714</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6601,30 +6643,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6632,21 +6674,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452027</v>
+        <v>452167</v>
       </c>
       <c r="R48" t="n">
-        <v>7029091</v>
+        <v>7029292</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6678,7 +6715,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6688,12 +6725,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6704,21 +6741,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6735,10 +6757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122716262</v>
+        <v>122717554</v>
       </c>
       <c r="B49" t="n">
-        <v>79714</v>
+        <v>79718</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6770,7 +6792,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6780,7 +6802,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6789,13 +6811,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452093</v>
+        <v>452007</v>
       </c>
       <c r="R49" t="n">
-        <v>7029013</v>
+        <v>7029050</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6824,7 +6846,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6834,12 +6856,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6850,6 +6872,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6866,10 +6903,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122716787</v>
+        <v>122717254</v>
       </c>
       <c r="B50" t="n">
-        <v>79803</v>
+        <v>74868</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6878,46 +6915,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>1467</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451914</v>
+        <v>451981</v>
       </c>
       <c r="R50" t="n">
-        <v>7028996</v>
+        <v>7029020</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6946,7 +6978,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6956,12 +6988,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7003,10 +7035,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122716081</v>
+        <v>122716416</v>
       </c>
       <c r="B51" t="n">
-        <v>78955</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7015,30 +7047,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>230552</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7052,13 +7084,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452077</v>
+        <v>451964</v>
       </c>
       <c r="R51" t="n">
-        <v>7029012</v>
+        <v>7029026</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7087,7 +7119,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7097,12 +7129,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7144,10 +7176,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715067</v>
+        <v>122717401</v>
       </c>
       <c r="B52" t="n">
-        <v>79747</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7156,41 +7188,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452163</v>
+        <v>452013</v>
       </c>
       <c r="R52" t="n">
-        <v>7029067</v>
+        <v>7029064</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7219,7 +7260,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7229,12 +7270,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7248,17 +7289,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7276,10 +7317,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122717834</v>
+        <v>122719770</v>
       </c>
       <c r="B53" t="n">
-        <v>79714</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7288,30 +7329,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7319,24 +7360,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452029</v>
+        <v>452163</v>
       </c>
       <c r="R53" t="n">
-        <v>7029079</v>
+        <v>7029302</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7365,7 +7401,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7375,12 +7411,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7391,41 +7427,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122718273</v>
+        <v>122720084</v>
       </c>
       <c r="B54" t="n">
-        <v>57589</v>
+        <v>79848</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7434,35 +7455,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7471,13 +7492,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452012</v>
+        <v>452101</v>
       </c>
       <c r="R54" t="n">
-        <v>7029081</v>
+        <v>7029256</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7506,7 +7527,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7516,12 +7537,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7536,22 +7557,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122720127</v>
+        <v>122715007</v>
       </c>
       <c r="B55" t="n">
-        <v>79844</v>
+        <v>79751</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7560,52 +7581,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452123</v>
+        <v>452170</v>
       </c>
       <c r="R55" t="n">
-        <v>7029202</v>
+        <v>7029085</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7637,7 +7644,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7647,12 +7654,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7663,26 +7670,41 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122719970</v>
+        <v>122717990</v>
       </c>
       <c r="B56" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7695,26 +7717,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7728,13 +7750,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452133</v>
+        <v>452063</v>
       </c>
       <c r="R56" t="n">
-        <v>7029267</v>
+        <v>7029079</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7763,7 +7785,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7773,12 +7795,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7805,10 +7827,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122719982</v>
+        <v>122717157</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7817,31 +7839,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7850,10 +7872,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452143</v>
+        <v>451983</v>
       </c>
       <c r="R57" t="n">
-        <v>7029283</v>
+        <v>7029027</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7885,7 +7907,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7895,12 +7917,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7911,21 +7933,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7942,10 +7949,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122715921</v>
+        <v>122719970</v>
       </c>
       <c r="B58" t="n">
-        <v>79803</v>
+        <v>79848</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7954,31 +7961,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med isidier</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7987,13 +7998,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452116</v>
+        <v>452133</v>
       </c>
       <c r="R58" t="n">
-        <v>7028982</v>
+        <v>7029267</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8022,7 +8033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8032,12 +8043,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8048,41 +8059,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122715859</v>
+        <v>122719605</v>
       </c>
       <c r="B59" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8095,37 +8091,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452106</v>
+        <v>452187</v>
       </c>
       <c r="R59" t="n">
-        <v>7028976</v>
+        <v>7029250</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8154,7 +8159,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8164,12 +8169,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8184,22 +8189,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122716459</v>
+        <v>122720303</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8212,27 +8217,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8241,10 +8250,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451969</v>
+        <v>452124</v>
       </c>
       <c r="R60" t="n">
-        <v>7029008</v>
+        <v>7029259</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8276,7 +8285,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8286,12 +8295,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8302,6 +8311,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8318,10 +8342,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122717254</v>
+        <v>122715370</v>
       </c>
       <c r="B61" t="n">
-        <v>74868</v>
+        <v>79302</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8334,37 +8358,51 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1467</v>
+        <v>1352</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451981</v>
+        <v>452135</v>
       </c>
       <c r="R61" t="n">
-        <v>7029020</v>
+        <v>7029012</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8393,7 +8431,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8403,12 +8441,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8419,41 +8457,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122716428</v>
+        <v>122717325</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8466,37 +8489,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451979</v>
+        <v>452006</v>
       </c>
       <c r="R62" t="n">
-        <v>7029020</v>
+        <v>7029026</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8525,7 +8557,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8535,12 +8567,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8551,26 +8583,41 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122719902</v>
+        <v>122715131</v>
       </c>
       <c r="B63" t="n">
-        <v>79844</v>
+        <v>77699</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8583,46 +8630,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452150</v>
+        <v>452147</v>
       </c>
       <c r="R63" t="n">
-        <v>7029301</v>
+        <v>7029041</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8651,7 +8689,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8661,12 +8699,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8677,41 +8715,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122714960</v>
+        <v>122715784</v>
       </c>
       <c r="B64" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8724,37 +8747,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452178</v>
+        <v>452116</v>
       </c>
       <c r="R64" t="n">
-        <v>7029093</v>
+        <v>7029000</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8783,7 +8815,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8793,12 +8825,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8825,10 +8857,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122716494</v>
+        <v>122715592</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8837,31 +8869,40 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8870,13 +8911,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451971</v>
+        <v>452141</v>
       </c>
       <c r="R65" t="n">
-        <v>7029000</v>
+        <v>7028992</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8905,7 +8946,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8915,12 +8956,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8931,41 +8972,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122719912</v>
+        <v>122716787</v>
       </c>
       <c r="B66" t="n">
-        <v>79844</v>
+        <v>79807</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8974,35 +9000,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -9011,13 +9033,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452222</v>
+        <v>451914</v>
       </c>
       <c r="R66" t="n">
-        <v>7029287</v>
+        <v>7028996</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9046,7 +9068,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9056,12 +9078,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9072,26 +9094,41 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122720084</v>
+        <v>122716428</v>
       </c>
       <c r="B67" t="n">
-        <v>79844</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9104,46 +9141,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452101</v>
+        <v>451979</v>
       </c>
       <c r="R67" t="n">
-        <v>7029256</v>
+        <v>7029020</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9172,7 +9200,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9182,12 +9210,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9214,10 +9242,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122719742</v>
+        <v>122716868</v>
       </c>
       <c r="B68" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9230,31 +9258,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9263,13 +9287,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452167</v>
+        <v>451931</v>
       </c>
       <c r="R68" t="n">
-        <v>7029292</v>
+        <v>7029005</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9298,7 +9322,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9308,12 +9332,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9324,6 +9348,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9340,10 +9379,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122720532</v>
+        <v>122715391</v>
       </c>
       <c r="B69" t="n">
-        <v>78846</v>
+        <v>79807</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9352,55 +9391,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>283</v>
+        <v>229497</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452156</v>
+        <v>452136</v>
       </c>
       <c r="R69" t="n">
-        <v>7029109</v>
+        <v>7029025</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9429,7 +9454,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9439,12 +9464,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9455,21 +9480,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9486,10 +9496,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122720266</v>
+        <v>122715120</v>
       </c>
       <c r="B70" t="n">
-        <v>77699</v>
+        <v>79807</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9498,25 +9508,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9526,13 +9536,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452125</v>
+        <v>452148</v>
       </c>
       <c r="R70" t="n">
-        <v>7029254</v>
+        <v>7029055</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9561,7 +9571,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9571,12 +9581,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9591,22 +9601,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122717990</v>
+        <v>122720194</v>
       </c>
       <c r="B71" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9619,26 +9629,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9652,13 +9662,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452063</v>
+        <v>452133</v>
       </c>
       <c r="R71" t="n">
-        <v>7029079</v>
+        <v>7029299</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9687,7 +9697,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9697,12 +9707,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9729,10 +9739,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122715120</v>
+        <v>122715650</v>
       </c>
       <c r="B72" t="n">
-        <v>79803</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9741,25 +9751,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9769,13 +9779,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452148</v>
+        <v>452125</v>
       </c>
       <c r="R72" t="n">
-        <v>7029055</v>
+        <v>7028994</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9804,7 +9814,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9814,12 +9824,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9834,22 +9839,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122716182</v>
+        <v>122716396</v>
       </c>
       <c r="B73" t="n">
-        <v>57499</v>
+        <v>78850</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9858,25 +9863,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100110</v>
+        <v>283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -9884,24 +9889,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452106</v>
+        <v>451975</v>
       </c>
       <c r="R73" t="n">
-        <v>7028976</v>
+        <v>7029033</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9930,7 +9935,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9940,7 +9945,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9955,22 +9965,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122719668</v>
+        <v>122717834</v>
       </c>
       <c r="B74" t="n">
-        <v>79879</v>
+        <v>79718</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9979,28 +9989,37 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6464</v>
+        <v>389</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -10012,10 +10031,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452187</v>
+        <v>452029</v>
       </c>
       <c r="R74" t="n">
-        <v>7029250</v>
+        <v>7029079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10047,7 +10066,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10057,12 +10076,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10076,17 +10095,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10104,10 +10123,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122719822</v>
+        <v>122716459</v>
       </c>
       <c r="B75" t="n">
-        <v>79747</v>
+        <v>57478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10116,41 +10135,49 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452152</v>
+        <v>451969</v>
       </c>
       <c r="R75" t="n">
-        <v>7029283</v>
+        <v>7029008</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10179,7 +10206,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10189,12 +10216,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10209,22 +10236,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122715877</v>
+        <v>122717285</v>
       </c>
       <c r="B76" t="n">
-        <v>79747</v>
+        <v>57478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10233,41 +10260,49 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452106</v>
+        <v>452000</v>
       </c>
       <c r="R76" t="n">
-        <v>7028977</v>
+        <v>7029026</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10296,7 +10331,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10306,12 +10341,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10322,21 +10357,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10353,10 +10373,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122720303</v>
+        <v>122716494</v>
       </c>
       <c r="B77" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10369,43 +10389,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452124</v>
+        <v>451971</v>
       </c>
       <c r="R77" t="n">
-        <v>7029259</v>
+        <v>7029000</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10437,7 +10456,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10447,12 +10466,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10494,10 +10513,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122716346</v>
+        <v>122718456</v>
       </c>
       <c r="B78" t="n">
-        <v>74868</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10510,37 +10529,45 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>451984</v>
+        <v>452038</v>
       </c>
       <c r="R78" t="n">
-        <v>7029029</v>
+        <v>7029084</v>
       </c>
       <c r="S78" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10569,7 +10596,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10579,12 +10606,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10595,21 +10622,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -10626,10 +10638,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122715337</v>
+        <v>122716081</v>
       </c>
       <c r="B79" t="n">
-        <v>78762</v>
+        <v>78959</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10638,30 +10650,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>230552</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10669,19 +10681,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452138</v>
+        <v>452077</v>
       </c>
       <c r="R79" t="n">
-        <v>7029066</v>
+        <v>7029012</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10710,7 +10724,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10720,12 +10734,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10734,6 +10748,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715921</v>
+        <v>122715067</v>
       </c>
       <c r="B2" t="n">
-        <v>79807</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452116</v>
+        <v>452163</v>
       </c>
       <c r="R2" t="n">
-        <v>7028982</v>
+        <v>7029067</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -949,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715067</v>
+        <v>122715921</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>79807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,37 +960,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452163</v>
+        <v>452116</v>
       </c>
       <c r="R4" t="n">
-        <v>7029067</v>
+        <v>7028982</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1490,10 +1490,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122719813</v>
+        <v>122717731</v>
       </c>
       <c r="B8" t="n">
-        <v>79876</v>
+        <v>79718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,41 +1502,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>389</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452159</v>
+        <v>452035</v>
       </c>
       <c r="R8" t="n">
-        <v>7029305</v>
+        <v>7029085</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1579,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,12 +1589,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,17 +1608,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1622,10 +1636,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122716346</v>
+        <v>122719813</v>
       </c>
       <c r="B9" t="n">
-        <v>74868</v>
+        <v>79876</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1634,25 +1648,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1662,13 +1676,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451984</v>
+        <v>452159</v>
       </c>
       <c r="R9" t="n">
-        <v>7029029</v>
+        <v>7029305</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1697,7 +1711,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1707,12 +1721,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1726,17 +1740,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1754,10 +1768,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122717731</v>
+        <v>122716346</v>
       </c>
       <c r="B10" t="n">
-        <v>79718</v>
+        <v>74868</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1766,55 +1780,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>389</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452035</v>
+        <v>451984</v>
       </c>
       <c r="R10" t="n">
-        <v>7029085</v>
+        <v>7029029</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720379</v>
+        <v>122715838</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3195,46 +3195,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452127</v>
+        <v>452109</v>
       </c>
       <c r="R21" t="n">
-        <v>7029209</v>
+        <v>7029006</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3263,7 +3254,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3273,12 +3264,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3289,6 +3280,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3305,10 +3311,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122715838</v>
+        <v>122720532</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
+        <v>78850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3321,37 +3327,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452109</v>
+        <v>452156</v>
       </c>
       <c r="R22" t="n">
-        <v>7029006</v>
+        <v>7029109</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3380,7 +3400,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3390,12 +3410,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3437,10 +3457,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720532</v>
+        <v>122720379</v>
       </c>
       <c r="B23" t="n">
-        <v>78850</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3453,26 +3473,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3480,24 +3500,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452156</v>
+        <v>452127</v>
       </c>
       <c r="R23" t="n">
-        <v>7029109</v>
+        <v>7029209</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3526,7 +3541,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3536,12 +3551,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3552,21 +3567,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -4198,10 +4198,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719701</v>
+        <v>122716687</v>
       </c>
       <c r="B29" t="n">
-        <v>79751</v>
+        <v>90944</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4210,35 +4210,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4247,13 +4243,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452180</v>
+        <v>451933</v>
       </c>
       <c r="R29" t="n">
-        <v>7029296</v>
+        <v>7028984</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4282,7 +4278,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4292,12 +4288,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4317,17 +4313,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122716687</v>
+        <v>122719701</v>
       </c>
       <c r="B30" t="n">
-        <v>90944</v>
+        <v>79751</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4336,31 +4332,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4369,13 +4369,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451933</v>
+        <v>452180</v>
       </c>
       <c r="R30" t="n">
-        <v>7028984</v>
+        <v>7029296</v>
       </c>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715337</v>
+        <v>122720354</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4817,46 +4817,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452138</v>
+        <v>452114</v>
       </c>
       <c r="R34" t="n">
-        <v>7029066</v>
+        <v>7029211</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4885,7 +4876,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4895,12 +4886,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4911,41 +4902,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720354</v>
+        <v>122715337</v>
       </c>
       <c r="B35" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4958,37 +4934,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452114</v>
+        <v>452138</v>
       </c>
       <c r="R35" t="n">
-        <v>7029211</v>
+        <v>7029066</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5017,7 +5002,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5027,12 +5012,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5043,16 +5028,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122715784</v>
+        <v>122716428</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8747,46 +8747,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452116</v>
+        <v>451979</v>
       </c>
       <c r="R64" t="n">
-        <v>7029000</v>
+        <v>7029020</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8815,7 +8806,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8825,12 +8816,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8845,12 +8836,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -9125,10 +9116,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122716428</v>
+        <v>122715784</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9141,37 +9132,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451979</v>
+        <v>452116</v>
       </c>
       <c r="R67" t="n">
-        <v>7029020</v>
+        <v>7029000</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9230,12 +9230,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122720194</v>
+        <v>122716396</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>78850</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9629,26 +9629,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452133</v>
+        <v>451975</v>
       </c>
       <c r="R71" t="n">
-        <v>7029299</v>
+        <v>7029033</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9727,22 +9727,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122715650</v>
+        <v>122717834</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9751,38 +9751,52 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452125</v>
+        <v>452029</v>
       </c>
       <c r="R72" t="n">
-        <v>7028994</v>
+        <v>7029079</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9814,7 +9828,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9824,7 +9838,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9835,26 +9854,41 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122716396</v>
+        <v>122720194</v>
       </c>
       <c r="B73" t="n">
-        <v>78850</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9867,26 +9901,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9900,13 +9934,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>451975</v>
+        <v>452133</v>
       </c>
       <c r="R73" t="n">
-        <v>7029033</v>
+        <v>7029299</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9935,7 +9969,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9945,12 +9979,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9965,22 +9999,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122717834</v>
+        <v>122715650</v>
       </c>
       <c r="B74" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9989,52 +10023,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452029</v>
+        <v>452125</v>
       </c>
       <c r="R74" t="n">
-        <v>7029079</v>
+        <v>7028994</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10066,7 +10086,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10076,12 +10096,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10092,31 +10107,16 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715067</v>
+        <v>122716687</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452163</v>
+        <v>451933</v>
       </c>
       <c r="R2" t="n">
-        <v>7029067</v>
+        <v>7028984</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,41 +781,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122719668</v>
+        <v>122714960</v>
       </c>
       <c r="B3" t="n">
-        <v>79883</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,46 +809,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452187</v>
+        <v>452178</v>
       </c>
       <c r="R3" t="n">
-        <v>7029250</v>
+        <v>7029093</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,21 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -944,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715921</v>
+        <v>122719701</v>
       </c>
       <c r="B4" t="n">
-        <v>79807</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,27 +930,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med isidier</t>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452116</v>
+        <v>452180</v>
       </c>
       <c r="R4" t="n">
-        <v>7028982</v>
+        <v>7029296</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,41 +1024,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122717632</v>
+        <v>122716346</v>
       </c>
       <c r="B5" t="n">
-        <v>79718</v>
+        <v>74868</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,52 +1052,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>389</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452015</v>
+        <v>451984</v>
       </c>
       <c r="R5" t="n">
-        <v>7029092</v>
+        <v>7029029</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1170,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,17 +1144,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1227,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719912</v>
+        <v>122719770</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1243,26 +1188,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1276,13 +1221,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452222</v>
+        <v>452163</v>
       </c>
       <c r="R6" t="n">
-        <v>7029287</v>
+        <v>7029302</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1311,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1321,12 +1266,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,17 +1291,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122719982</v>
+        <v>122717731</v>
       </c>
       <c r="B7" t="n">
-        <v>79022</v>
+        <v>79718</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,28 +1310,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6459</v>
+        <v>389</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -1398,13 +1352,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452143</v>
+        <v>452035</v>
       </c>
       <c r="R7" t="n">
-        <v>7029283</v>
+        <v>7029085</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1433,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1443,12 +1397,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1462,17 +1416,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1490,10 +1444,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122717731</v>
+        <v>122717254</v>
       </c>
       <c r="B8" t="n">
-        <v>79718</v>
+        <v>74868</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,55 +1456,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>389</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452035</v>
+        <v>451981</v>
       </c>
       <c r="R8" t="n">
-        <v>7029085</v>
+        <v>7029020</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1579,7 +1519,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1589,12 +1529,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,17 +1548,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1636,10 +1576,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719813</v>
+        <v>122716416</v>
       </c>
       <c r="B9" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1648,41 +1588,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452159</v>
+        <v>451964</v>
       </c>
       <c r="R9" t="n">
-        <v>7029305</v>
+        <v>7029026</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1711,7 +1660,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1721,12 +1670,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1740,17 +1689,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1768,10 +1717,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122716346</v>
+        <v>122719912</v>
       </c>
       <c r="B10" t="n">
-        <v>74868</v>
+        <v>79848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1784,37 +1733,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451984</v>
+        <v>452222</v>
       </c>
       <c r="R10" t="n">
-        <v>7029029</v>
+        <v>7029287</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1843,7 +1801,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1853,12 +1811,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1869,41 +1827,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122720127</v>
+        <v>122719605</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1916,26 +1859,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1943,21 +1886,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452123</v>
+        <v>452187</v>
       </c>
       <c r="R11" t="n">
-        <v>7029202</v>
+        <v>7029250</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1989,7 +1927,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1999,12 +1937,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2019,22 +1957,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122715140</v>
+        <v>122719813</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>79876</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2043,50 +1981,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452148</v>
+        <v>452159</v>
       </c>
       <c r="R12" t="n">
-        <v>7029055</v>
+        <v>7029305</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2115,7 +2044,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2125,12 +2054,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2141,6 +2070,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2157,10 +2101,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122716262</v>
+        <v>122715754</v>
       </c>
       <c r="B13" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2169,52 +2113,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452093</v>
+        <v>452130</v>
       </c>
       <c r="R13" t="n">
-        <v>7029013</v>
+        <v>7029002</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2246,7 +2176,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2256,12 +2186,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2288,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122719930</v>
+        <v>122720150</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2304,46 +2234,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452148</v>
+        <v>452132</v>
       </c>
       <c r="R14" t="n">
-        <v>7029296</v>
+        <v>7029266</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2372,7 +2293,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2382,12 +2303,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2398,6 +2319,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2414,10 +2350,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122719902</v>
+        <v>122716868</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2430,31 +2366,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2463,13 +2395,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452150</v>
+        <v>451931</v>
       </c>
       <c r="R15" t="n">
-        <v>7029301</v>
+        <v>7029005</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2498,7 +2430,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2508,12 +2440,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2527,17 +2459,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2555,10 +2487,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122715547</v>
+        <v>122715838</v>
       </c>
       <c r="B16" t="n">
-        <v>79882</v>
+        <v>74863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2567,25 +2499,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2595,13 +2527,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452141</v>
+        <v>452109</v>
       </c>
       <c r="R16" t="n">
-        <v>7028992</v>
+        <v>7029006</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2630,7 +2562,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2640,12 +2572,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2656,26 +2588,41 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122720088</v>
+        <v>122720532</v>
       </c>
       <c r="B17" t="n">
-        <v>79876</v>
+        <v>78850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2684,38 +2631,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452118</v>
+        <v>452156</v>
       </c>
       <c r="R17" t="n">
-        <v>7029273</v>
+        <v>7029109</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
@@ -2747,7 +2708,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2757,12 +2718,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2776,17 +2737,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2804,7 +2765,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122717724</v>
+        <v>122717990</v>
       </c>
       <c r="B18" t="n">
         <v>79847</v>
@@ -2839,7 +2800,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2853,13 +2814,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452034</v>
+        <v>452063</v>
       </c>
       <c r="R18" t="n">
-        <v>7029103</v>
+        <v>7029079</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2888,7 +2849,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2898,12 +2859,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2930,10 +2891,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122717199</v>
+        <v>122720194</v>
       </c>
       <c r="B19" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2946,37 +2907,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451981</v>
+        <v>452133</v>
       </c>
       <c r="R19" t="n">
-        <v>7029020</v>
+        <v>7029299</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3005,7 +2975,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3015,12 +2985,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3031,41 +3001,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122715754</v>
+        <v>122715337</v>
       </c>
       <c r="B20" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3074,41 +3029,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452130</v>
+        <v>452138</v>
       </c>
       <c r="R20" t="n">
-        <v>7029002</v>
+        <v>7029066</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,7 +3101,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,12 +3111,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3163,6 +3127,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3179,10 +3158,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122715838</v>
+        <v>122715140</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3195,37 +3174,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452109</v>
+        <v>452148</v>
       </c>
       <c r="R21" t="n">
-        <v>7029006</v>
+        <v>7029055</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3254,7 +3242,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3264,12 +3252,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3280,21 +3268,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3311,10 +3284,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122720532</v>
+        <v>122720303</v>
       </c>
       <c r="B22" t="n">
-        <v>78850</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3327,26 +3300,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3354,24 +3327,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452156</v>
+        <v>452124</v>
       </c>
       <c r="R22" t="n">
-        <v>7029109</v>
+        <v>7029259</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3400,7 +3368,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3410,12 +3378,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3457,10 +3425,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720379</v>
+        <v>122719970</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3473,26 +3441,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3506,13 +3474,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452127</v>
+        <v>452133</v>
       </c>
       <c r="R23" t="n">
-        <v>7029209</v>
+        <v>7029267</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3541,7 +3509,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3551,12 +3519,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3571,22 +3539,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715104</v>
+        <v>122717554</v>
       </c>
       <c r="B24" t="n">
-        <v>91389</v>
+        <v>79718</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3599,37 +3567,51 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452162</v>
+        <v>452007</v>
       </c>
       <c r="R24" t="n">
-        <v>7029063</v>
+        <v>7029050</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3658,7 +3640,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3668,12 +3650,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3684,6 +3666,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3700,10 +3697,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720150</v>
+        <v>122715671</v>
       </c>
       <c r="B25" t="n">
-        <v>77699</v>
+        <v>79718</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3712,28 +3709,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>389</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
@@ -3743,10 +3754,10 @@
         <v>452132</v>
       </c>
       <c r="R25" t="n">
-        <v>7029266</v>
+        <v>7028982</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3775,7 +3786,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3785,12 +3796,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3804,17 +3815,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3832,10 +3843,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122719822</v>
+        <v>122720354</v>
       </c>
       <c r="B26" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3844,25 +3855,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3872,13 +3883,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452152</v>
+        <v>452114</v>
       </c>
       <c r="R26" t="n">
-        <v>7029283</v>
+        <v>7029211</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3907,7 +3918,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3917,12 +3928,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3949,10 +3960,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715877</v>
+        <v>122719982</v>
       </c>
       <c r="B27" t="n">
-        <v>79751</v>
+        <v>79022</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3965,37 +3976,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6459</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452106</v>
+        <v>452143</v>
       </c>
       <c r="R27" t="n">
-        <v>7028977</v>
+        <v>7029283</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4024,7 +4040,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4034,12 +4050,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4053,17 +4069,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4081,10 +4097,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122714960</v>
+        <v>122720088</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>79876</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4093,25 +4109,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4121,13 +4137,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452178</v>
+        <v>452118</v>
       </c>
       <c r="R28" t="n">
-        <v>7029093</v>
+        <v>7029273</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4156,7 +4172,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4166,12 +4182,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4182,6 +4198,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4198,10 +4229,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122716687</v>
+        <v>122717401</v>
       </c>
       <c r="B29" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4214,27 +4245,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4243,13 +4278,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451933</v>
+        <v>452013</v>
       </c>
       <c r="R29" t="n">
-        <v>7028984</v>
+        <v>7029064</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4278,7 +4313,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4288,12 +4323,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4304,26 +4339,41 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>granar</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719701</v>
+        <v>122720266</v>
       </c>
       <c r="B30" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4332,50 +4382,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452180</v>
+        <v>452125</v>
       </c>
       <c r="R30" t="n">
-        <v>7029296</v>
+        <v>7029254</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4404,7 +4445,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4414,12 +4455,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4439,17 +4480,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122714976</v>
+        <v>122716633</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4458,35 +4499,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4495,13 +4532,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452178</v>
+        <v>451941</v>
       </c>
       <c r="R31" t="n">
-        <v>7029092</v>
+        <v>7028960</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4530,7 +4567,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4540,7 +4577,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4551,26 +4593,41 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715859</v>
+        <v>122719668</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>79883</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4579,41 +4636,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452106</v>
+        <v>452187</v>
       </c>
       <c r="R32" t="n">
-        <v>7028976</v>
+        <v>7029250</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4642,7 +4704,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4652,12 +4714,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4668,26 +4730,41 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122720266</v>
+        <v>122718273</v>
       </c>
       <c r="B33" t="n">
-        <v>77699</v>
+        <v>57589</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4696,41 +4773,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452125</v>
+        <v>452012</v>
       </c>
       <c r="R33" t="n">
-        <v>7029254</v>
+        <v>7029081</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4759,7 +4845,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4769,12 +4855,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4789,22 +4875,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122720354</v>
+        <v>122720127</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4817,37 +4903,51 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452114</v>
+        <v>452123</v>
       </c>
       <c r="R34" t="n">
-        <v>7029211</v>
+        <v>7029202</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4876,7 +4976,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4886,12 +4986,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4918,10 +5018,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715337</v>
+        <v>122715131</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4934,46 +5034,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452138</v>
+        <v>452147</v>
       </c>
       <c r="R35" t="n">
-        <v>7029066</v>
+        <v>7029041</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5002,7 +5093,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5012,12 +5103,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5028,41 +5119,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122715671</v>
+        <v>122717199</v>
       </c>
       <c r="B36" t="n">
-        <v>79718</v>
+        <v>77699</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5071,55 +5147,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>389</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452132</v>
+        <v>451981</v>
       </c>
       <c r="R36" t="n">
-        <v>7028982</v>
+        <v>7029020</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5148,7 +5210,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5158,12 +5220,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5177,17 +5239,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5205,7 +5267,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122717676</v>
+        <v>122717893</v>
       </c>
       <c r="B37" t="n">
         <v>79718</v>
@@ -5240,7 +5302,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5259,13 +5321,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452027</v>
+        <v>452029</v>
       </c>
       <c r="R37" t="n">
-        <v>7029091</v>
+        <v>7029076</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,7 +5356,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5304,12 +5366,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5351,10 +5413,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715739</v>
+        <v>122716182</v>
       </c>
       <c r="B38" t="n">
-        <v>77699</v>
+        <v>57499</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5363,41 +5425,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>100110</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452142</v>
+        <v>452106</v>
       </c>
       <c r="R38" t="n">
-        <v>7029004</v>
+        <v>7028976</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5426,7 +5497,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5436,12 +5507,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5468,10 +5534,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122716633</v>
+        <v>122715191</v>
       </c>
       <c r="B39" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5484,42 +5550,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451941</v>
+        <v>452150</v>
       </c>
       <c r="R39" t="n">
-        <v>7028960</v>
+        <v>7029062</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5548,7 +5609,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5558,12 +5619,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5574,21 +5635,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5605,10 +5651,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122716759</v>
+        <v>122719902</v>
       </c>
       <c r="B40" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5617,35 +5663,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5654,13 +5700,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451898</v>
+        <v>452150</v>
       </c>
       <c r="R40" t="n">
-        <v>7028975</v>
+        <v>7029301</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5689,7 +5735,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5699,12 +5745,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5715,26 +5761,41 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122715130</v>
+        <v>122720379</v>
       </c>
       <c r="B41" t="n">
-        <v>90955</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5743,41 +5804,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452148</v>
+        <v>452127</v>
       </c>
       <c r="R41" t="n">
-        <v>7029055</v>
+        <v>7029209</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5806,7 +5876,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5816,12 +5886,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5848,10 +5918,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122720261</v>
+        <v>122717356</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5864,34 +5934,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452124</v>
+        <v>452001</v>
       </c>
       <c r="R42" t="n">
-        <v>7029259</v>
+        <v>7029043</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5923,7 +6002,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5933,12 +6012,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5980,10 +6059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122715191</v>
+        <v>122717157</v>
       </c>
       <c r="B43" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5992,41 +6071,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452150</v>
+        <v>451983</v>
       </c>
       <c r="R43" t="n">
-        <v>7029062</v>
+        <v>7029027</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6055,7 +6139,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6065,12 +6149,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6097,10 +6181,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122716182</v>
+        <v>122717676</v>
       </c>
       <c r="B44" t="n">
-        <v>57499</v>
+        <v>79718</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6109,50 +6193,55 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100110</v>
+        <v>389</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452106</v>
+        <v>452027</v>
       </c>
       <c r="R44" t="n">
-        <v>7028976</v>
+        <v>7029091</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6181,7 +6270,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6191,7 +6280,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6202,26 +6296,41 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717893</v>
+        <v>122715007</v>
       </c>
       <c r="B45" t="n">
-        <v>79718</v>
+        <v>79751</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6230,55 +6339,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>389</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452029</v>
+        <v>452170</v>
       </c>
       <c r="R45" t="n">
-        <v>7029076</v>
+        <v>7029085</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6307,7 +6402,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6317,12 +6412,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6364,10 +6459,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122717356</v>
+        <v>122715067</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6376,50 +6471,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452001</v>
+        <v>452163</v>
       </c>
       <c r="R46" t="n">
-        <v>7029043</v>
+        <v>7029067</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6448,7 +6534,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6458,12 +6544,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6477,17 +6563,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6505,10 +6591,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122718273</v>
+        <v>122715370</v>
       </c>
       <c r="B47" t="n">
-        <v>57589</v>
+        <v>79302</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6517,35 +6603,40 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>1352</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6554,13 +6645,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452012</v>
+        <v>452135</v>
       </c>
       <c r="R47" t="n">
-        <v>7029081</v>
+        <v>7029012</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6589,7 +6680,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6599,12 +6690,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6619,22 +6710,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122719742</v>
+        <v>122720261</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6647,43 +6738,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452167</v>
+        <v>452124</v>
       </c>
       <c r="R48" t="n">
-        <v>7029292</v>
+        <v>7029259</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6715,7 +6797,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6725,12 +6807,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6741,6 +6823,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6757,10 +6854,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122717554</v>
+        <v>122715650</v>
       </c>
       <c r="B49" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6769,55 +6866,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452007</v>
+        <v>452125</v>
       </c>
       <c r="R49" t="n">
-        <v>7029050</v>
+        <v>7028994</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6846,7 +6929,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6856,12 +6939,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6872,41 +6950,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122717254</v>
+        <v>122714976</v>
       </c>
       <c r="B50" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6919,37 +6982,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451981</v>
+        <v>452178</v>
       </c>
       <c r="R50" t="n">
-        <v>7029020</v>
+        <v>7029092</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6978,7 +7050,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6988,12 +7060,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7004,38 +7071,23 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122716416</v>
+        <v>122719930</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -7070,7 +7122,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7084,13 +7136,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451964</v>
+        <v>452148</v>
       </c>
       <c r="R51" t="n">
-        <v>7029026</v>
+        <v>7029296</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7119,7 +7171,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7129,12 +7181,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7145,21 +7197,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -7176,10 +7213,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122717401</v>
+        <v>122717724</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7192,26 +7229,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7225,10 +7262,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452013</v>
+        <v>452034</v>
       </c>
       <c r="R52" t="n">
-        <v>7029064</v>
+        <v>7029103</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -7260,7 +7297,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7270,12 +7307,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7286,41 +7323,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>granar</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122719770</v>
+        <v>122715120</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7329,47 +7351,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452163</v>
+        <v>452148</v>
       </c>
       <c r="R53" t="n">
-        <v>7029302</v>
+        <v>7029055</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -7401,7 +7414,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7411,12 +7424,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7431,22 +7444,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720084</v>
+        <v>122717632</v>
       </c>
       <c r="B54" t="n">
-        <v>79848</v>
+        <v>79718</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7455,30 +7468,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>389</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7486,19 +7499,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452101</v>
+        <v>452015</v>
       </c>
       <c r="R54" t="n">
-        <v>7029256</v>
+        <v>7029092</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7527,7 +7545,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7537,12 +7555,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7553,26 +7571,41 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122715007</v>
+        <v>122717834</v>
       </c>
       <c r="B55" t="n">
-        <v>79751</v>
+        <v>79718</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7581,38 +7614,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>389</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452170</v>
+        <v>452029</v>
       </c>
       <c r="R55" t="n">
-        <v>7029085</v>
+        <v>7029079</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7644,7 +7691,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7654,12 +7701,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7701,10 +7748,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122717990</v>
+        <v>122715859</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7717,46 +7764,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452063</v>
+        <v>452106</v>
       </c>
       <c r="R56" t="n">
-        <v>7029079</v>
+        <v>7028976</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7785,7 +7823,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7795,12 +7833,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7827,10 +7865,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122717157</v>
+        <v>122716787</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7839,31 +7877,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7872,13 +7910,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451983</v>
+        <v>451914</v>
       </c>
       <c r="R57" t="n">
-        <v>7029027</v>
+        <v>7028996</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7907,7 +7945,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7917,12 +7955,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7933,6 +7971,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7949,7 +8002,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122719970</v>
+        <v>122720084</v>
       </c>
       <c r="B58" t="n">
         <v>79848</v>
@@ -7984,7 +8037,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7998,10 +8051,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452133</v>
+        <v>452101</v>
       </c>
       <c r="R58" t="n">
-        <v>7029267</v>
+        <v>7029256</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -8033,7 +8086,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8043,7 +8096,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8075,7 +8128,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719605</v>
+        <v>122719742</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -8110,7 +8163,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8124,10 +8177,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452187</v>
+        <v>452167</v>
       </c>
       <c r="R59" t="n">
-        <v>7029250</v>
+        <v>7029292</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8159,7 +8212,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8169,12 +8222,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8201,7 +8254,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720303</v>
+        <v>122715784</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -8236,7 +8289,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8250,10 +8303,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452124</v>
+        <v>452116</v>
       </c>
       <c r="R60" t="n">
-        <v>7029259</v>
+        <v>7029000</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8285,7 +8338,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8295,12 +8348,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8311,21 +8364,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8342,10 +8380,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715370</v>
+        <v>122715130</v>
       </c>
       <c r="B61" t="n">
-        <v>79302</v>
+        <v>90955</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8354,55 +8392,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1352</v>
+        <v>1205</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452135</v>
+        <v>452148</v>
       </c>
       <c r="R61" t="n">
-        <v>7029012</v>
+        <v>7029055</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8431,7 +8455,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8441,12 +8465,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8461,22 +8485,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122717325</v>
+        <v>122715592</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8485,30 +8509,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8516,19 +8540,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452006</v>
+        <v>452141</v>
       </c>
       <c r="R62" t="n">
-        <v>7029026</v>
+        <v>7028992</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8557,7 +8586,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8567,12 +8596,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8583,41 +8612,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122715131</v>
+        <v>122716262</v>
       </c>
       <c r="B63" t="n">
-        <v>77699</v>
+        <v>79718</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8626,41 +8640,55 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228579</v>
+        <v>389</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452147</v>
+        <v>452093</v>
       </c>
       <c r="R63" t="n">
-        <v>7029041</v>
+        <v>7029013</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8689,7 +8717,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8699,12 +8727,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8719,22 +8747,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122716428</v>
+        <v>122716759</v>
       </c>
       <c r="B64" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8743,41 +8771,50 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451979</v>
+        <v>451898</v>
       </c>
       <c r="R64" t="n">
-        <v>7029020</v>
+        <v>7028975</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8806,7 +8843,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8816,12 +8853,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8848,10 +8885,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122715592</v>
+        <v>122717325</v>
       </c>
       <c r="B65" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8860,30 +8897,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8891,24 +8928,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452141</v>
+        <v>452006</v>
       </c>
       <c r="R65" t="n">
-        <v>7028992</v>
+        <v>7029026</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8937,7 +8969,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8947,12 +8979,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8963,26 +8995,41 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122716787</v>
+        <v>122715547</v>
       </c>
       <c r="B66" t="n">
-        <v>79807</v>
+        <v>79882</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8995,42 +9042,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451914</v>
+        <v>452141</v>
       </c>
       <c r="R66" t="n">
-        <v>7028996</v>
+        <v>7028992</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9059,7 +9101,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9069,12 +9111,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9085,41 +9127,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122715784</v>
+        <v>122715877</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9128,50 +9155,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452116</v>
+        <v>452106</v>
       </c>
       <c r="R67" t="n">
-        <v>7029000</v>
+        <v>7028977</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9200,7 +9218,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9210,12 +9228,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9226,6 +9244,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -9242,10 +9275,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122716868</v>
+        <v>122715391</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9254,46 +9287,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>451931</v>
+        <v>452136</v>
       </c>
       <c r="R68" t="n">
-        <v>7029005</v>
+        <v>7029025</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9322,7 +9350,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9332,12 +9360,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9348,21 +9376,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9379,10 +9392,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122715391</v>
+        <v>122716428</v>
       </c>
       <c r="B69" t="n">
-        <v>79807</v>
+        <v>74863</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9391,25 +9404,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9419,13 +9432,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452136</v>
+        <v>451979</v>
       </c>
       <c r="R69" t="n">
-        <v>7029025</v>
+        <v>7029020</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9454,7 +9467,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9464,12 +9477,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9484,22 +9497,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122715120</v>
+        <v>122715104</v>
       </c>
       <c r="B70" t="n">
-        <v>79807</v>
+        <v>91389</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9508,25 +9521,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9536,13 +9549,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452148</v>
+        <v>452162</v>
       </c>
       <c r="R70" t="n">
-        <v>7029055</v>
+        <v>7029063</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9571,7 +9584,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9581,12 +9594,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9613,10 +9626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122716396</v>
+        <v>122715921</v>
       </c>
       <c r="B71" t="n">
-        <v>78850</v>
+        <v>79807</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9625,35 +9638,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>283</v>
+        <v>229497</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9662,10 +9671,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451975</v>
+        <v>452116</v>
       </c>
       <c r="R71" t="n">
-        <v>7029033</v>
+        <v>7028982</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9697,7 +9706,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9707,12 +9716,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9723,6 +9732,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9739,10 +9763,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122717834</v>
+        <v>122719822</v>
       </c>
       <c r="B72" t="n">
-        <v>79718</v>
+        <v>79751</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9751,55 +9775,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>389</v>
+        <v>6456</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452029</v>
+        <v>452152</v>
       </c>
       <c r="R72" t="n">
-        <v>7029079</v>
+        <v>7029283</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9828,7 +9838,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9838,12 +9848,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9854,41 +9864,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122720194</v>
+        <v>122715739</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9901,46 +9896,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452133</v>
+        <v>452142</v>
       </c>
       <c r="R73" t="n">
-        <v>7029299</v>
+        <v>7029004</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9969,7 +9955,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9979,12 +9965,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10011,10 +9997,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122715650</v>
+        <v>122716396</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>78850</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10027,34 +10013,43 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452125</v>
+        <v>451975</v>
       </c>
       <c r="R74" t="n">
-        <v>7028994</v>
+        <v>7029033</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10086,7 +10081,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10096,7 +10091,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10111,19 +10111,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122716459</v>
+        <v>122718456</v>
       </c>
       <c r="B75" t="n">
         <v>57478</v>
@@ -10167,14 +10167,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>451969</v>
+        <v>452038</v>
       </c>
       <c r="R75" t="n">
-        <v>7029008</v>
+        <v>7029084</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10248,7 +10248,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122717285</v>
+        <v>122716494</v>
       </c>
       <c r="B76" t="n">
         <v>57478</v>
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452000</v>
+        <v>451971</v>
       </c>
       <c r="R76" t="n">
-        <v>7029026</v>
+        <v>7029000</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10357,6 +10357,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10373,7 +10388,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122716494</v>
+        <v>122717285</v>
       </c>
       <c r="B77" t="n">
         <v>57478</v>
@@ -10421,10 +10436,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451971</v>
+        <v>452000</v>
       </c>
       <c r="R77" t="n">
-        <v>7029000</v>
+        <v>7029026</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10456,7 +10471,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10466,12 +10481,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10482,21 +10497,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10513,7 +10513,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122718456</v>
+        <v>122716459</v>
       </c>
       <c r="B78" t="n">
         <v>57478</v>
@@ -10557,14 +10557,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>452038</v>
+        <v>451969</v>
       </c>
       <c r="R78" t="n">
-        <v>7029084</v>
+        <v>7029008</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
+          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122716687</v>
+        <v>122720088</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
+        <v>79876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451933</v>
+        <v>452118</v>
       </c>
       <c r="R2" t="n">
-        <v>7028984</v>
+        <v>7029273</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,26 +776,41 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122714960</v>
+        <v>122717254</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>74868</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452178</v>
+        <v>451981</v>
       </c>
       <c r="R3" t="n">
-        <v>7029093</v>
+        <v>7029020</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +908,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122719701</v>
+        <v>122715370</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>79302</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,30 +951,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1352</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,16 +982,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452180</v>
+        <v>452135</v>
       </c>
       <c r="R4" t="n">
-        <v>7029296</v>
+        <v>7029012</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
@@ -998,7 +1028,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1038,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,17 +1063,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122716346</v>
+        <v>122714960</v>
       </c>
       <c r="B5" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1080,13 +1110,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451984</v>
+        <v>452178</v>
       </c>
       <c r="R5" t="n">
-        <v>7029029</v>
+        <v>7029093</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1155,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,21 +1171,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1172,7 +1187,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719770</v>
+        <v>122719605</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1221,13 +1236,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452163</v>
+        <v>452187</v>
       </c>
       <c r="R6" t="n">
-        <v>7029302</v>
+        <v>7029250</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,7 +1271,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,12 +1281,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,22 +1301,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122717731</v>
+        <v>122715838</v>
       </c>
       <c r="B7" t="n">
-        <v>79718</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,55 +1325,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>389</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452035</v>
+        <v>452109</v>
       </c>
       <c r="R7" t="n">
-        <v>7029085</v>
+        <v>7029006</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,12 +1398,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,17 +1417,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1444,10 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122717254</v>
+        <v>122716396</v>
       </c>
       <c r="B8" t="n">
-        <v>74868</v>
+        <v>78850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1460,34 +1461,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451981</v>
+        <v>451975</v>
       </c>
       <c r="R8" t="n">
-        <v>7029020</v>
+        <v>7029033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,7 +1529,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1529,12 +1539,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,21 +1555,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1576,7 +1571,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122716416</v>
+        <v>122719742</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1625,13 +1620,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451964</v>
+        <v>452167</v>
       </c>
       <c r="R9" t="n">
-        <v>7029026</v>
+        <v>7029292</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1660,7 +1655,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1670,12 +1665,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,21 +1681,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1717,10 +1697,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122719912</v>
+        <v>122717724</v>
       </c>
       <c r="B10" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,26 +1713,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1766,13 +1746,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452222</v>
+        <v>452034</v>
       </c>
       <c r="R10" t="n">
-        <v>7029287</v>
+        <v>7029103</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1801,7 +1781,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1811,12 +1791,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1843,10 +1823,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122719605</v>
+        <v>122719970</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1859,26 +1839,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1892,13 +1872,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452187</v>
+        <v>452133</v>
       </c>
       <c r="R11" t="n">
-        <v>7029250</v>
+        <v>7029267</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1927,7 +1907,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1937,12 +1917,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1957,22 +1937,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122719813</v>
+        <v>122715067</v>
       </c>
       <c r="B12" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,21 +1965,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2009,13 +1989,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452159</v>
+        <v>452163</v>
       </c>
       <c r="R12" t="n">
-        <v>7029305</v>
+        <v>7029067</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2044,7 +2024,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2054,12 +2034,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2073,17 +2053,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2101,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122715754</v>
+        <v>122715104</v>
       </c>
       <c r="B13" t="n">
-        <v>79807</v>
+        <v>91389</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2113,25 +2093,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2141,13 +2121,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452130</v>
+        <v>452162</v>
       </c>
       <c r="R13" t="n">
-        <v>7029002</v>
+        <v>7029063</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2176,7 +2156,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2186,12 +2166,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2218,10 +2198,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122720150</v>
+        <v>122720379</v>
       </c>
       <c r="B14" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2234,37 +2214,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452132</v>
+        <v>452127</v>
       </c>
       <c r="R14" t="n">
-        <v>7029266</v>
+        <v>7029209</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2293,7 +2282,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2303,12 +2292,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,21 +2308,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2350,10 +2324,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716868</v>
+        <v>122716416</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2366,27 +2340,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2395,13 +2373,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451931</v>
+        <v>451964</v>
       </c>
       <c r="R15" t="n">
-        <v>7029005</v>
+        <v>7029026</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2430,7 +2408,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2440,12 +2418,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2487,10 +2465,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122715838</v>
+        <v>122719930</v>
       </c>
       <c r="B16" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2503,34 +2481,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452109</v>
+        <v>452148</v>
       </c>
       <c r="R16" t="n">
-        <v>7029006</v>
+        <v>7029296</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2549,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2572,12 +2559,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,21 +2575,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2619,10 +2591,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122720532</v>
+        <v>122715120</v>
       </c>
       <c r="B17" t="n">
-        <v>78850</v>
+        <v>79807</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2631,55 +2603,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>283</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452156</v>
+        <v>452148</v>
       </c>
       <c r="R17" t="n">
-        <v>7029109</v>
+        <v>7029055</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2708,7 +2666,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2718,12 +2676,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2734,21 +2692,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2765,10 +2708,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122717990</v>
+        <v>122716787</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2777,35 +2720,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2814,13 +2753,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452063</v>
+        <v>451914</v>
       </c>
       <c r="R18" t="n">
-        <v>7029079</v>
+        <v>7028996</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2849,7 +2788,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2859,12 +2798,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2875,26 +2814,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122720194</v>
+        <v>122715754</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2903,50 +2857,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452133</v>
+        <v>452130</v>
       </c>
       <c r="R19" t="n">
-        <v>7029299</v>
+        <v>7029002</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2975,7 +2920,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2985,12 +2930,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3005,19 +2950,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122715337</v>
+        <v>122715784</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -3052,7 +2997,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3066,13 +3011,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452138</v>
+        <v>452116</v>
       </c>
       <c r="R20" t="n">
-        <v>7029066</v>
+        <v>7029000</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3101,7 +3046,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3111,12 +3056,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3127,21 +3072,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3158,10 +3088,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122715140</v>
+        <v>122717401</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3174,31 +3104,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3207,13 +3137,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452148</v>
+        <v>452013</v>
       </c>
       <c r="R21" t="n">
-        <v>7029055</v>
+        <v>7029064</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,7 +3172,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3252,12 +3182,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3268,6 +3198,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>granar</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3284,10 +3229,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122720303</v>
+        <v>122719822</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3296,50 +3241,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452124</v>
+        <v>452152</v>
       </c>
       <c r="R22" t="n">
-        <v>7029259</v>
+        <v>7029283</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3368,7 +3304,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3378,12 +3314,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3394,41 +3330,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122719970</v>
+        <v>122715191</v>
       </c>
       <c r="B23" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3437,50 +3358,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452133</v>
+        <v>452150</v>
       </c>
       <c r="R23" t="n">
-        <v>7029267</v>
+        <v>7029062</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3509,7 +3421,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3519,12 +3431,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3539,22 +3451,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122717554</v>
+        <v>122716687</v>
       </c>
       <c r="B24" t="n">
-        <v>79718</v>
+        <v>90944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3563,40 +3475,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>389</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3605,13 +3508,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452007</v>
+        <v>451933</v>
       </c>
       <c r="R24" t="n">
-        <v>7029050</v>
+        <v>7028984</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3640,7 +3543,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3650,12 +3553,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3666,41 +3569,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715671</v>
+        <v>122717325</v>
       </c>
       <c r="B25" t="n">
-        <v>79718</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3709,30 +3597,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3740,24 +3628,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452132</v>
+        <v>452006</v>
       </c>
       <c r="R25" t="n">
-        <v>7028982</v>
+        <v>7029026</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3786,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3796,12 +3679,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3843,10 +3726,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720354</v>
+        <v>122720084</v>
       </c>
       <c r="B26" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3859,37 +3742,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452114</v>
+        <v>452101</v>
       </c>
       <c r="R26" t="n">
-        <v>7029211</v>
+        <v>7029256</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3918,7 +3810,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3928,12 +3820,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3960,10 +3852,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122719982</v>
+        <v>122715592</v>
       </c>
       <c r="B27" t="n">
-        <v>79022</v>
+        <v>79807</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3976,27 +3868,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6459</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4005,13 +3906,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452143</v>
+        <v>452141</v>
       </c>
       <c r="R27" t="n">
-        <v>7029283</v>
+        <v>7028992</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4040,7 +3941,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4050,12 +3951,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4066,41 +3967,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720088</v>
+        <v>122717834</v>
       </c>
       <c r="B28" t="n">
-        <v>79876</v>
+        <v>79718</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4109,41 +3995,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>389</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452118</v>
+        <v>452029</v>
       </c>
       <c r="R28" t="n">
-        <v>7029273</v>
+        <v>7029079</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4172,7 +4072,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4182,12 +4082,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4201,17 +4101,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4229,10 +4129,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122717401</v>
+        <v>122720261</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4245,46 +4145,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452013</v>
+        <v>452124</v>
       </c>
       <c r="R29" t="n">
-        <v>7029064</v>
+        <v>7029259</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4313,7 +4204,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4323,12 +4214,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4342,17 +4233,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4370,10 +4261,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122720266</v>
+        <v>122719770</v>
       </c>
       <c r="B30" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4386,37 +4277,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452125</v>
+        <v>452163</v>
       </c>
       <c r="R30" t="n">
-        <v>7029254</v>
+        <v>7029302</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4445,7 +4345,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4455,12 +4355,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4480,17 +4380,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122716633</v>
+        <v>122716346</v>
       </c>
       <c r="B31" t="n">
-        <v>79876</v>
+        <v>74868</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4499,46 +4399,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451941</v>
+        <v>451984</v>
       </c>
       <c r="R31" t="n">
-        <v>7028960</v>
+        <v>7029029</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4567,7 +4462,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4577,12 +4472,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4596,17 +4491,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4624,10 +4519,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122719668</v>
+        <v>122715007</v>
       </c>
       <c r="B32" t="n">
-        <v>79883</v>
+        <v>79751</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4640,39 +4535,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452187</v>
+        <v>452170</v>
       </c>
       <c r="R32" t="n">
-        <v>7029250</v>
+        <v>7029085</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4704,7 +4594,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4714,12 +4604,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4733,17 +4623,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4761,10 +4651,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122718273</v>
+        <v>122715391</v>
       </c>
       <c r="B33" t="n">
-        <v>57589</v>
+        <v>79807</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4777,43 +4667,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452012</v>
+        <v>452136</v>
       </c>
       <c r="R33" t="n">
-        <v>7029081</v>
+        <v>7029025</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4845,7 +4726,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4855,12 +4736,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4887,10 +4768,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122720127</v>
+        <v>122715739</v>
       </c>
       <c r="B34" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4903,51 +4784,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452123</v>
+        <v>452142</v>
       </c>
       <c r="R34" t="n">
-        <v>7029202</v>
+        <v>7029004</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4976,7 +4843,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4986,12 +4853,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5018,7 +4885,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715131</v>
+        <v>122717199</v>
       </c>
       <c r="B35" t="n">
         <v>77699</v>
@@ -5058,13 +4925,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452147</v>
+        <v>451981</v>
       </c>
       <c r="R35" t="n">
-        <v>7029041</v>
+        <v>7029020</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5093,7 +4960,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5103,12 +4970,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5119,26 +4986,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122717199</v>
+        <v>122715921</v>
       </c>
       <c r="B36" t="n">
-        <v>77699</v>
+        <v>79807</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5147,38 +5029,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451981</v>
+        <v>452116</v>
       </c>
       <c r="R36" t="n">
-        <v>7029020</v>
+        <v>7028982</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5210,7 +5097,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5220,12 +5107,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5239,17 +5126,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5267,7 +5154,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122717893</v>
+        <v>122717554</v>
       </c>
       <c r="B37" t="n">
         <v>79718</v>
@@ -5302,7 +5189,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5312,7 +5199,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5321,10 +5208,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452029</v>
+        <v>452007</v>
       </c>
       <c r="R37" t="n">
-        <v>7029076</v>
+        <v>7029050</v>
       </c>
       <c r="S37" t="n">
         <v>6</v>
@@ -5356,7 +5243,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5366,12 +5253,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5413,10 +5300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122716182</v>
+        <v>122719813</v>
       </c>
       <c r="B38" t="n">
-        <v>57499</v>
+        <v>79876</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5429,46 +5316,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100110</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452106</v>
+        <v>452159</v>
       </c>
       <c r="R38" t="n">
-        <v>7028976</v>
+        <v>7029305</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5497,7 +5375,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5507,7 +5385,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5518,26 +5401,41 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715191</v>
+        <v>122716868</v>
       </c>
       <c r="B39" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5546,41 +5444,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452150</v>
+        <v>451931</v>
       </c>
       <c r="R39" t="n">
-        <v>7029062</v>
+        <v>7029005</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5609,7 +5512,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5619,12 +5522,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5635,6 +5538,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5651,10 +5569,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122719902</v>
+        <v>122716182</v>
       </c>
       <c r="B40" t="n">
-        <v>79848</v>
+        <v>57499</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5663,50 +5581,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100110</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452150</v>
+        <v>452106</v>
       </c>
       <c r="R40" t="n">
-        <v>7029301</v>
+        <v>7028976</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5735,7 +5653,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5745,12 +5663,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5761,41 +5674,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122720379</v>
+        <v>122720532</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>78850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5808,26 +5706,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5835,19 +5733,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452127</v>
+        <v>452156</v>
       </c>
       <c r="R41" t="n">
-        <v>7029209</v>
+        <v>7029109</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5876,7 +5779,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5886,12 +5789,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5902,6 +5805,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5918,10 +5836,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122717356</v>
+        <v>122720354</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5934,46 +5852,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452001</v>
+        <v>452114</v>
       </c>
       <c r="R42" t="n">
-        <v>7029043</v>
+        <v>7029211</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6002,7 +5911,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6012,12 +5921,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6028,41 +5937,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122717157</v>
+        <v>122717356</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6075,27 +5969,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6104,10 +6002,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451983</v>
+        <v>452001</v>
       </c>
       <c r="R43" t="n">
-        <v>7029027</v>
+        <v>7029043</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6139,7 +6037,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6149,12 +6047,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6165,6 +6063,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6181,7 +6094,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122717676</v>
+        <v>122717632</v>
       </c>
       <c r="B44" t="n">
         <v>79718</v>
@@ -6235,13 +6148,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452027</v>
+        <v>452015</v>
       </c>
       <c r="R44" t="n">
-        <v>7029091</v>
+        <v>7029092</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6270,7 +6183,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6280,12 +6193,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6327,10 +6240,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122715007</v>
+        <v>122715337</v>
       </c>
       <c r="B45" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6339,41 +6252,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452170</v>
+        <v>452138</v>
       </c>
       <c r="R45" t="n">
-        <v>7029085</v>
+        <v>7029066</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6402,7 +6324,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6412,12 +6334,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6431,17 +6353,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6459,7 +6381,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122715067</v>
+        <v>122716759</v>
       </c>
       <c r="B46" t="n">
         <v>79751</v>
@@ -6492,20 +6414,29 @@
           <t>(Dicks.) Nyl.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452163</v>
+        <v>451898</v>
       </c>
       <c r="R46" t="n">
-        <v>7029067</v>
+        <v>7028975</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6534,7 +6465,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6544,12 +6475,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6560,41 +6491,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122715370</v>
+        <v>122720266</v>
       </c>
       <c r="B47" t="n">
-        <v>79302</v>
+        <v>77699</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6607,51 +6523,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1352</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452135</v>
+        <v>452125</v>
       </c>
       <c r="R47" t="n">
-        <v>7029012</v>
+        <v>7029254</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6680,7 +6582,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6690,12 +6592,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6722,10 +6624,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122720261</v>
+        <v>122715547</v>
       </c>
       <c r="B48" t="n">
-        <v>74863</v>
+        <v>79882</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6734,25 +6636,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6762,13 +6664,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452124</v>
+        <v>452141</v>
       </c>
       <c r="R48" t="n">
-        <v>7029259</v>
+        <v>7028992</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6797,7 +6699,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6807,12 +6709,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6823,41 +6725,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122715650</v>
+        <v>122717731</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6866,41 +6753,55 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452125</v>
+        <v>452035</v>
       </c>
       <c r="R49" t="n">
-        <v>7028994</v>
+        <v>7029085</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6929,7 +6830,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6939,7 +6840,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6950,26 +6856,41 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122714976</v>
+        <v>122715877</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6978,50 +6899,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452178</v>
+        <v>452106</v>
       </c>
       <c r="R50" t="n">
-        <v>7029092</v>
+        <v>7028977</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7050,7 +6962,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7060,7 +6972,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7071,26 +6988,41 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122719930</v>
+        <v>122716633</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7099,35 +7031,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7136,13 +7064,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452148</v>
+        <v>451941</v>
       </c>
       <c r="R51" t="n">
-        <v>7029296</v>
+        <v>7028960</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7171,7 +7099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7181,12 +7109,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7197,6 +7125,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -7213,7 +7156,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122717724</v>
+        <v>122717990</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -7248,7 +7191,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7262,13 +7205,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452034</v>
+        <v>452063</v>
       </c>
       <c r="R52" t="n">
-        <v>7029103</v>
+        <v>7029079</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7297,7 +7240,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7307,12 +7250,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7339,10 +7282,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715120</v>
+        <v>122715859</v>
       </c>
       <c r="B53" t="n">
-        <v>79807</v>
+        <v>74863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7351,25 +7294,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7379,10 +7322,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452148</v>
+        <v>452106</v>
       </c>
       <c r="R53" t="n">
-        <v>7029055</v>
+        <v>7028976</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -7414,7 +7357,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7424,12 +7367,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7444,22 +7387,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122717632</v>
+        <v>122720127</v>
       </c>
       <c r="B54" t="n">
-        <v>79718</v>
+        <v>79848</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7468,30 +7411,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>389</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7501,7 +7444,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7510,13 +7453,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452015</v>
+        <v>452123</v>
       </c>
       <c r="R54" t="n">
-        <v>7029092</v>
+        <v>7029202</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7545,7 +7488,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7555,12 +7498,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7571,41 +7514,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122717834</v>
+        <v>122715131</v>
       </c>
       <c r="B55" t="n">
-        <v>79718</v>
+        <v>77699</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7614,55 +7542,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>389</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452029</v>
+        <v>452147</v>
       </c>
       <c r="R55" t="n">
-        <v>7029079</v>
+        <v>7029041</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7691,7 +7605,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7701,12 +7615,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7717,41 +7631,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122715859</v>
+        <v>122720194</v>
       </c>
       <c r="B56" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7764,37 +7663,46 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452106</v>
+        <v>452133</v>
       </c>
       <c r="R56" t="n">
-        <v>7028976</v>
+        <v>7029299</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7823,7 +7731,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7833,12 +7741,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7865,10 +7773,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122716787</v>
+        <v>122715650</v>
       </c>
       <c r="B57" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7877,46 +7785,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451914</v>
+        <v>452125</v>
       </c>
       <c r="R57" t="n">
-        <v>7028996</v>
+        <v>7028994</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7945,7 +7848,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7955,12 +7858,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7971,41 +7869,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122720084</v>
+        <v>122714976</v>
       </c>
       <c r="B58" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8018,26 +7901,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8051,13 +7934,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452101</v>
+        <v>452178</v>
       </c>
       <c r="R58" t="n">
-        <v>7029256</v>
+        <v>7029092</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8086,7 +7969,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8096,12 +7979,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8128,10 +8006,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719742</v>
+        <v>122719982</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>79022</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8140,35 +8018,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8177,10 +8051,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452167</v>
+        <v>452143</v>
       </c>
       <c r="R59" t="n">
-        <v>7029292</v>
+        <v>7029283</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8212,7 +8086,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8222,12 +8096,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8238,6 +8112,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -8254,7 +8143,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715784</v>
+        <v>122720303</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -8289,7 +8178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8303,10 +8192,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452116</v>
+        <v>452124</v>
       </c>
       <c r="R60" t="n">
-        <v>7029000</v>
+        <v>7029259</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8338,7 +8227,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8348,12 +8237,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8364,6 +8253,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8380,10 +8284,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715130</v>
+        <v>122716428</v>
       </c>
       <c r="B61" t="n">
-        <v>90955</v>
+        <v>74863</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8392,25 +8296,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1205</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8420,13 +8324,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452148</v>
+        <v>451979</v>
       </c>
       <c r="R61" t="n">
-        <v>7029055</v>
+        <v>7029020</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8455,7 +8359,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8465,12 +8369,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8485,22 +8389,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715592</v>
+        <v>122718273</v>
       </c>
       <c r="B62" t="n">
-        <v>79807</v>
+        <v>57589</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8513,36 +8417,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med isidier</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8551,13 +8450,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452141</v>
+        <v>452012</v>
       </c>
       <c r="R62" t="n">
-        <v>7028992</v>
+        <v>7029081</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8586,7 +8485,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8596,12 +8495,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8616,22 +8515,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716262</v>
+        <v>122720150</v>
       </c>
       <c r="B63" t="n">
-        <v>79718</v>
+        <v>77699</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8640,55 +8539,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>389</v>
+        <v>228579</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452093</v>
+        <v>452132</v>
       </c>
       <c r="R63" t="n">
-        <v>7029013</v>
+        <v>7029266</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8717,7 +8602,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8727,12 +8612,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8743,6 +8628,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8759,10 +8659,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122716759</v>
+        <v>122719668</v>
       </c>
       <c r="B64" t="n">
-        <v>79751</v>
+        <v>79883</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8775,31 +8675,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8808,10 +8704,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451898</v>
+        <v>452187</v>
       </c>
       <c r="R64" t="n">
-        <v>7028975</v>
+        <v>7029250</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8843,7 +8739,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8853,12 +8749,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8869,26 +8765,41 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122717325</v>
+        <v>122715671</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>79718</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8897,30 +8808,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8928,19 +8839,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452006</v>
+        <v>452132</v>
       </c>
       <c r="R65" t="n">
-        <v>7029026</v>
+        <v>7028982</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8969,7 +8885,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8979,12 +8895,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9026,10 +8942,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122715547</v>
+        <v>122717893</v>
       </c>
       <c r="B66" t="n">
-        <v>79882</v>
+        <v>79718</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9038,41 +8954,55 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>389</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452141</v>
+        <v>452029</v>
       </c>
       <c r="R66" t="n">
-        <v>7028992</v>
+        <v>7029076</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9101,7 +9031,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9111,12 +9041,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9127,26 +9057,41 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122715877</v>
+        <v>122715130</v>
       </c>
       <c r="B67" t="n">
-        <v>79751</v>
+        <v>90955</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9159,21 +9104,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9183,13 +9128,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452106</v>
+        <v>452148</v>
       </c>
       <c r="R67" t="n">
-        <v>7028977</v>
+        <v>7029055</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9218,7 +9163,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9228,12 +9173,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9244,21 +9189,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -9275,10 +9205,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122715391</v>
+        <v>122716262</v>
       </c>
       <c r="B68" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9287,38 +9217,52 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452136</v>
+        <v>452093</v>
       </c>
       <c r="R68" t="n">
-        <v>7029025</v>
+        <v>7029013</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9350,7 +9294,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9360,12 +9304,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9392,10 +9336,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122716428</v>
+        <v>122719912</v>
       </c>
       <c r="B69" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9408,37 +9352,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451979</v>
+        <v>452222</v>
       </c>
       <c r="R69" t="n">
-        <v>7029020</v>
+        <v>7029287</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9467,7 +9420,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9477,12 +9430,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9509,10 +9462,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122715104</v>
+        <v>122717676</v>
       </c>
       <c r="B70" t="n">
-        <v>91389</v>
+        <v>79718</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9525,37 +9478,51 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>389</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452162</v>
+        <v>452027</v>
       </c>
       <c r="R70" t="n">
-        <v>7029063</v>
+        <v>7029091</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9584,7 +9551,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9594,12 +9561,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9610,6 +9577,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9626,10 +9608,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122715921</v>
+        <v>122719701</v>
       </c>
       <c r="B71" t="n">
-        <v>79807</v>
+        <v>79751</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9642,27 +9624,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med isidier</t>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9671,13 +9657,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452116</v>
+        <v>452180</v>
       </c>
       <c r="R71" t="n">
-        <v>7028982</v>
+        <v>7029296</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9706,7 +9692,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9716,12 +9702,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9732,41 +9718,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122719822</v>
+        <v>122715140</v>
       </c>
       <c r="B72" t="n">
-        <v>79751</v>
+        <v>57631</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9775,41 +9746,50 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452152</v>
+        <v>452148</v>
       </c>
       <c r="R72" t="n">
-        <v>7029283</v>
+        <v>7029055</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9838,7 +9818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9848,12 +9828,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9868,22 +9848,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122715739</v>
+        <v>122719902</v>
       </c>
       <c r="B73" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9896,37 +9876,46 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452142</v>
+        <v>452150</v>
       </c>
       <c r="R73" t="n">
-        <v>7029004</v>
+        <v>7029301</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9955,7 +9944,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9965,12 +9954,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9981,26 +9970,41 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122716396</v>
+        <v>122717157</v>
       </c>
       <c r="B74" t="n">
-        <v>78850</v>
+        <v>57478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10013,31 +10017,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -10046,10 +10046,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451975</v>
+        <v>451983</v>
       </c>
       <c r="R74" t="n">
-        <v>7029033</v>
+        <v>7029027</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10123,10 +10123,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122718456</v>
+        <v>122716081</v>
       </c>
       <c r="B75" t="n">
-        <v>57478</v>
+        <v>78959</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10135,49 +10135,52 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>230552</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452038</v>
+        <v>452077</v>
       </c>
       <c r="R75" t="n">
-        <v>7029084</v>
+        <v>7029012</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10206,7 +10209,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10216,12 +10219,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10230,8 +10233,24 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10248,7 +10267,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122716494</v>
+        <v>122717285</v>
       </c>
       <c r="B76" t="n">
         <v>57478</v>
@@ -10296,10 +10315,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451971</v>
+        <v>452000</v>
       </c>
       <c r="R76" t="n">
-        <v>7029000</v>
+        <v>7029026</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10331,7 +10350,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10341,12 +10360,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10357,21 +10376,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10388,7 +10392,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122717285</v>
+        <v>122718456</v>
       </c>
       <c r="B77" t="n">
         <v>57478</v>
@@ -10432,14 +10436,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452000</v>
+        <v>452038</v>
       </c>
       <c r="R77" t="n">
-        <v>7029026</v>
+        <v>7029084</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10471,7 +10475,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10481,12 +10485,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10638,10 +10642,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122716081</v>
+        <v>122716494</v>
       </c>
       <c r="B79" t="n">
-        <v>78959</v>
+        <v>57478</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10650,38 +10654,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>230552</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10689,13 +10690,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452077</v>
+        <v>451971</v>
       </c>
       <c r="R79" t="n">
-        <v>7029012</v>
+        <v>7029000</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10724,7 +10725,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10734,12 +10735,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10748,7 +10749,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122720088</v>
+        <v>122715370</v>
       </c>
       <c r="B2" t="n">
-        <v>79876</v>
+        <v>79302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1352</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452118</v>
+        <v>452135</v>
       </c>
       <c r="R2" t="n">
-        <v>7029273</v>
+        <v>7029012</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,41 +790,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122717254</v>
+        <v>122720088</v>
       </c>
       <c r="B3" t="n">
-        <v>74868</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451981</v>
+        <v>452118</v>
       </c>
       <c r="R3" t="n">
-        <v>7029020</v>
+        <v>7029273</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,17 +910,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715370</v>
+        <v>122717254</v>
       </c>
       <c r="B4" t="n">
-        <v>79302</v>
+        <v>74868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,51 +954,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1352</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452135</v>
+        <v>451981</v>
       </c>
       <c r="R4" t="n">
-        <v>7029012</v>
+        <v>7029020</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1038,12 +1023,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,16 +1039,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715838</v>
+        <v>122719742</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1329,34 +1329,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452109</v>
+        <v>452167</v>
       </c>
       <c r="R7" t="n">
-        <v>7029006</v>
+        <v>7029292</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1397,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,12 +1407,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,21 +1423,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1445,10 +1439,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122716396</v>
+        <v>122717724</v>
       </c>
       <c r="B8" t="n">
-        <v>78850</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,21 +1455,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>283</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1494,13 +1488,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451975</v>
+        <v>452034</v>
       </c>
       <c r="R8" t="n">
-        <v>7029033</v>
+        <v>7029103</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1529,7 +1523,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1539,12 +1533,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,22 +1553,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719742</v>
+        <v>122716396</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>78850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1587,21 +1581,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1620,10 +1614,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452167</v>
+        <v>451975</v>
       </c>
       <c r="R9" t="n">
-        <v>7029292</v>
+        <v>7029033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1665,12 +1659,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122717724</v>
+        <v>122715838</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1713,46 +1707,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452034</v>
+        <v>452109</v>
       </c>
       <c r="R10" t="n">
-        <v>7029103</v>
+        <v>7029006</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1781,7 +1766,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1791,12 +1776,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1807,16 +1792,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122715877</v>
+        <v>122716633</v>
       </c>
       <c r="B50" t="n">
-        <v>79751</v>
+        <v>79876</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6903,34 +6903,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452106</v>
+        <v>451941</v>
       </c>
       <c r="R50" t="n">
-        <v>7028977</v>
+        <v>7028960</v>
       </c>
       <c r="S50" t="n">
         <v>8</v>
@@ -6962,7 +6967,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6972,12 +6977,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6991,17 +6996,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7019,10 +7024,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122716633</v>
+        <v>122717990</v>
       </c>
       <c r="B51" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7031,31 +7036,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7064,13 +7073,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451941</v>
+        <v>452063</v>
       </c>
       <c r="R51" t="n">
-        <v>7028960</v>
+        <v>7029079</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7099,7 +7108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7109,12 +7118,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7125,41 +7134,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122717990</v>
+        <v>122715877</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7168,50 +7162,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452063</v>
+        <v>452106</v>
       </c>
       <c r="R52" t="n">
-        <v>7029079</v>
+        <v>7028977</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7240,7 +7225,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7250,12 +7235,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7266,16 +7251,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -3463,10 +3463,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122716687</v>
+        <v>122715592</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>79807</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3475,31 +3475,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3508,13 +3517,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451933</v>
+        <v>452141</v>
       </c>
       <c r="R24" t="n">
-        <v>7028984</v>
+        <v>7028992</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3543,7 +3552,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3553,12 +3562,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3585,10 +3594,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122717325</v>
+        <v>122717834</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>79718</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3597,30 +3606,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3628,19 +3637,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452006</v>
+        <v>452029</v>
       </c>
       <c r="R25" t="n">
-        <v>7029026</v>
+        <v>7029079</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3669,7 +3683,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,12 +3693,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3726,10 +3740,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720084</v>
+        <v>122716687</v>
       </c>
       <c r="B26" t="n">
-        <v>79848</v>
+        <v>90944</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3742,31 +3756,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3775,13 +3785,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452101</v>
+        <v>451933</v>
       </c>
       <c r="R26" t="n">
-        <v>7029256</v>
+        <v>7028984</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3810,7 +3820,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3820,12 +3830,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3852,10 +3862,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715592</v>
+        <v>122720261</v>
       </c>
       <c r="B27" t="n">
-        <v>79807</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3864,55 +3874,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452141</v>
+        <v>452124</v>
       </c>
       <c r="R27" t="n">
-        <v>7028992</v>
+        <v>7029259</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3941,7 +3937,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3951,12 +3947,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3967,26 +3963,41 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122717834</v>
+        <v>122717325</v>
       </c>
       <c r="B28" t="n">
-        <v>79718</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3995,30 +4006,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4026,24 +4037,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452029</v>
+        <v>452006</v>
       </c>
       <c r="R28" t="n">
-        <v>7029079</v>
+        <v>7029026</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4072,7 +4078,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4082,12 +4088,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4129,10 +4135,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122720261</v>
+        <v>122720084</v>
       </c>
       <c r="B29" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4145,37 +4151,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452124</v>
+        <v>452101</v>
       </c>
       <c r="R29" t="n">
-        <v>7029259</v>
+        <v>7029256</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4204,7 +4219,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4214,12 +4229,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4230,41 +4245,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719770</v>
+        <v>122715007</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4273,50 +4273,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452163</v>
+        <v>452170</v>
       </c>
       <c r="R30" t="n">
-        <v>7029302</v>
+        <v>7029085</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4345,7 +4336,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4355,12 +4346,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4371,26 +4362,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122716346</v>
+        <v>122715391</v>
       </c>
       <c r="B31" t="n">
-        <v>74868</v>
+        <v>79807</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4399,25 +4405,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4427,13 +4433,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451984</v>
+        <v>452136</v>
       </c>
       <c r="R31" t="n">
-        <v>7029029</v>
+        <v>7029025</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4462,7 +4468,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4472,12 +4478,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4488,21 +4494,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4519,10 +4510,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715007</v>
+        <v>122715739</v>
       </c>
       <c r="B32" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4531,25 +4522,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4559,13 +4550,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452170</v>
+        <v>452142</v>
       </c>
       <c r="R32" t="n">
-        <v>7029085</v>
+        <v>7029004</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4594,7 +4585,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4604,12 +4595,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4620,41 +4611,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122715391</v>
+        <v>122719770</v>
       </c>
       <c r="B33" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4663,41 +4639,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452136</v>
+        <v>452163</v>
       </c>
       <c r="R33" t="n">
-        <v>7029025</v>
+        <v>7029302</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4726,7 +4711,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4736,12 +4721,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4756,22 +4741,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715739</v>
+        <v>122716346</v>
       </c>
       <c r="B34" t="n">
-        <v>77699</v>
+        <v>74868</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4784,21 +4769,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4808,13 +4793,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452142</v>
+        <v>451984</v>
       </c>
       <c r="R34" t="n">
-        <v>7029004</v>
+        <v>7029029</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4843,7 +4828,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4853,12 +4838,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4869,16 +4854,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122717632</v>
+        <v>122720266</v>
       </c>
       <c r="B44" t="n">
-        <v>79718</v>
+        <v>77699</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6106,52 +6106,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>389</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452015</v>
+        <v>452125</v>
       </c>
       <c r="R44" t="n">
-        <v>7029092</v>
+        <v>7029254</v>
       </c>
       <c r="S44" t="n">
         <v>7</v>
@@ -6183,7 +6169,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6193,12 +6179,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6209,41 +6195,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122715337</v>
+        <v>122717632</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6252,30 +6223,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6283,19 +6254,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452138</v>
+        <v>452015</v>
       </c>
       <c r="R45" t="n">
-        <v>7029066</v>
+        <v>7029092</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6324,7 +6300,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6334,12 +6310,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6353,17 +6329,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6381,10 +6357,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122716759</v>
+        <v>122715337</v>
       </c>
       <c r="B46" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6393,30 +6369,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6430,13 +6406,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451898</v>
+        <v>452138</v>
       </c>
       <c r="R46" t="n">
-        <v>7028975</v>
+        <v>7029066</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6465,7 +6441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6475,12 +6451,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6491,26 +6467,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720266</v>
+        <v>122716759</v>
       </c>
       <c r="B47" t="n">
-        <v>77699</v>
+        <v>79751</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6519,41 +6510,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452125</v>
+        <v>451898</v>
       </c>
       <c r="R47" t="n">
-        <v>7029254</v>
+        <v>7028975</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7530,10 +7530,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122715131</v>
+        <v>122720303</v>
       </c>
       <c r="B55" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7546,37 +7546,46 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452147</v>
+        <v>452124</v>
       </c>
       <c r="R55" t="n">
-        <v>7029041</v>
+        <v>7029259</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7605,7 +7614,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7615,12 +7624,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7631,26 +7640,41 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720194</v>
+        <v>122719982</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79022</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7659,35 +7683,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7696,13 +7716,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452133</v>
+        <v>452143</v>
       </c>
       <c r="R56" t="n">
-        <v>7029299</v>
+        <v>7029283</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7731,7 +7751,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7741,12 +7761,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7757,23 +7777,38 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122715650</v>
+        <v>122720194</v>
       </c>
       <c r="B57" t="n">
         <v>78766</v>
@@ -7806,20 +7841,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452125</v>
+        <v>452133</v>
       </c>
       <c r="R57" t="n">
-        <v>7028994</v>
+        <v>7029299</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7848,7 +7892,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7858,7 +7902,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7885,7 +7934,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122714976</v>
+        <v>122715650</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -7918,29 +7967,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452178</v>
+        <v>452125</v>
       </c>
       <c r="R58" t="n">
-        <v>7029092</v>
+        <v>7028994</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7969,7 +8009,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7979,7 +8019,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8006,10 +8046,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719982</v>
+        <v>122714976</v>
       </c>
       <c r="B59" t="n">
-        <v>79022</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8018,31 +8058,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8051,13 +8095,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452143</v>
+        <v>452178</v>
       </c>
       <c r="R59" t="n">
-        <v>7029283</v>
+        <v>7029092</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8086,7 +8130,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8096,12 +8140,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På sälg i gammal granskog</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8112,41 +8151,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720303</v>
+        <v>122715131</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8159,46 +8183,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452124</v>
+        <v>452147</v>
       </c>
       <c r="R60" t="n">
-        <v>7029259</v>
+        <v>7029041</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8227,7 +8242,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8237,12 +8252,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8253,31 +8268,16 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -3463,10 +3463,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715592</v>
+        <v>122716687</v>
       </c>
       <c r="B24" t="n">
-        <v>79807</v>
+        <v>90944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3475,40 +3475,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3517,13 +3508,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452141</v>
+        <v>451933</v>
       </c>
       <c r="R24" t="n">
-        <v>7028992</v>
+        <v>7028984</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3552,7 +3543,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3562,12 +3553,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3594,10 +3585,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122717834</v>
+        <v>122717325</v>
       </c>
       <c r="B25" t="n">
-        <v>79718</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3606,30 +3597,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3637,24 +3628,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452029</v>
+        <v>452006</v>
       </c>
       <c r="R25" t="n">
-        <v>7029079</v>
+        <v>7029026</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3683,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3693,12 +3679,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3740,10 +3726,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122716687</v>
+        <v>122720084</v>
       </c>
       <c r="B26" t="n">
-        <v>90944</v>
+        <v>79848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3756,27 +3742,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3785,13 +3775,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451933</v>
+        <v>452101</v>
       </c>
       <c r="R26" t="n">
-        <v>7028984</v>
+        <v>7029256</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3820,7 +3810,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3830,12 +3820,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3862,10 +3852,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720261</v>
+        <v>122715592</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>79807</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3874,41 +3864,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452124</v>
+        <v>452141</v>
       </c>
       <c r="R27" t="n">
-        <v>7029259</v>
+        <v>7028992</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3937,7 +3941,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3947,12 +3951,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3963,41 +3967,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122717325</v>
+        <v>122717834</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>79718</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4006,30 +3995,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4037,19 +4026,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452006</v>
+        <v>452029</v>
       </c>
       <c r="R28" t="n">
-        <v>7029026</v>
+        <v>7029079</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4078,7 +4072,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4088,12 +4082,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4135,10 +4129,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122720084</v>
+        <v>122720261</v>
       </c>
       <c r="B29" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4151,46 +4145,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452101</v>
+        <v>452124</v>
       </c>
       <c r="R29" t="n">
-        <v>7029256</v>
+        <v>7029259</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4219,7 +4204,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4229,12 +4214,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4245,16 +4230,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715370</v>
+        <v>122715191</v>
       </c>
       <c r="B2" t="n">
-        <v>79302</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1352</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452135</v>
+        <v>452150</v>
       </c>
       <c r="R2" t="n">
-        <v>7029012</v>
+        <v>7029062</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122720088</v>
+        <v>122720354</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452118</v>
+        <v>452114</v>
       </c>
       <c r="R3" t="n">
-        <v>7029273</v>
+        <v>7029211</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,41 +893,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122717254</v>
+        <v>122716416</v>
       </c>
       <c r="B4" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,37 +925,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451981</v>
+        <v>451964</v>
       </c>
       <c r="R4" t="n">
-        <v>7029020</v>
+        <v>7029026</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122714960</v>
+        <v>122715650</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1110,13 +1090,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452178</v>
+        <v>452125</v>
       </c>
       <c r="R5" t="n">
-        <v>7029093</v>
+        <v>7028994</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1145,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,12 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,22 +1150,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719605</v>
+        <v>122720088</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,50 +1174,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452187</v>
+        <v>452118</v>
       </c>
       <c r="R6" t="n">
-        <v>7029250</v>
+        <v>7029273</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1281,12 +1247,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,6 +1263,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1313,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122719742</v>
+        <v>122720266</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1329,46 +1310,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452167</v>
+        <v>452125</v>
       </c>
       <c r="R7" t="n">
-        <v>7029292</v>
+        <v>7029254</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1407,12 +1379,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,22 +1399,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122717724</v>
+        <v>122715391</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,50 +1423,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452034</v>
+        <v>452136</v>
       </c>
       <c r="R8" t="n">
-        <v>7029103</v>
+        <v>7029025</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1523,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1533,12 +1496,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,22 +1516,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122716396</v>
+        <v>122715784</v>
       </c>
       <c r="B9" t="n">
-        <v>78850</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1581,26 +1544,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1614,10 +1577,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451975</v>
+        <v>452116</v>
       </c>
       <c r="R9" t="n">
-        <v>7029033</v>
+        <v>7029000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1649,7 +1612,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,12 +1622,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1691,10 +1654,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122715838</v>
+        <v>122715140</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1707,37 +1670,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452109</v>
+        <v>452148</v>
       </c>
       <c r="R10" t="n">
-        <v>7029006</v>
+        <v>7029055</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1766,7 +1738,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1776,12 +1748,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,21 +1764,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1823,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122719970</v>
+        <v>122717834</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>79718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1835,30 +1792,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>389</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1866,19 +1823,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452133</v>
+        <v>452029</v>
       </c>
       <c r="R11" t="n">
-        <v>7029267</v>
+        <v>7029079</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1907,7 +1869,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1917,12 +1879,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,26 +1895,41 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122715067</v>
+        <v>122717401</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1961,41 +1938,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452163</v>
+        <v>452013</v>
       </c>
       <c r="R12" t="n">
-        <v>7029067</v>
+        <v>7029064</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2024,7 +2010,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2034,12 +2020,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,17 +2039,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2081,10 +2067,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122715104</v>
+        <v>122720150</v>
       </c>
       <c r="B13" t="n">
-        <v>91389</v>
+        <v>77699</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,25 +2079,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2121,13 +2107,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452162</v>
+        <v>452132</v>
       </c>
       <c r="R13" t="n">
-        <v>7029063</v>
+        <v>7029266</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2156,7 +2142,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2166,12 +2152,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2182,6 +2168,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2198,10 +2199,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122720379</v>
+        <v>122715921</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2210,35 +2211,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2247,13 +2244,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452127</v>
+        <v>452116</v>
       </c>
       <c r="R14" t="n">
-        <v>7029209</v>
+        <v>7028982</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2282,7 +2279,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2292,12 +2289,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2308,6 +2305,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2324,10 +2336,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716416</v>
+        <v>122715859</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2340,46 +2352,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451964</v>
+        <v>452106</v>
       </c>
       <c r="R15" t="n">
-        <v>7029026</v>
+        <v>7028976</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2408,7 +2411,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2418,12 +2421,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2434,41 +2437,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719930</v>
+        <v>122715547</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2477,20 +2465,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2498,29 +2486,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452148</v>
+        <v>452141</v>
       </c>
       <c r="R16" t="n">
-        <v>7029296</v>
+        <v>7028992</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2549,7 +2528,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2559,12 +2538,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,22 +2558,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715120</v>
+        <v>122717724</v>
       </c>
       <c r="B17" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2603,41 +2582,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452148</v>
+        <v>452034</v>
       </c>
       <c r="R17" t="n">
-        <v>7029055</v>
+        <v>7029103</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2666,7 +2654,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2676,12 +2664,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2696,22 +2684,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122716787</v>
+        <v>122717731</v>
       </c>
       <c r="B18" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2720,31 +2708,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2753,13 +2750,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451914</v>
+        <v>452035</v>
       </c>
       <c r="R18" t="n">
-        <v>7028996</v>
+        <v>7029085</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2788,7 +2785,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2798,12 +2795,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,17 +2814,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2845,10 +2842,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122715754</v>
+        <v>122717893</v>
       </c>
       <c r="B19" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2857,41 +2854,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452130</v>
+        <v>452029</v>
       </c>
       <c r="R19" t="n">
-        <v>7029002</v>
+        <v>7029076</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2920,7 +2931,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2930,12 +2941,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2946,6 +2957,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2962,10 +2988,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122715784</v>
+        <v>122719822</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2974,50 +3000,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452116</v>
+        <v>452152</v>
       </c>
       <c r="R20" t="n">
-        <v>7029000</v>
+        <v>7029283</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3046,7 +3063,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3056,12 +3073,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3076,22 +3093,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122717401</v>
+        <v>122717325</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3104,26 +3121,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3137,13 +3154,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452013</v>
+        <v>452006</v>
       </c>
       <c r="R21" t="n">
-        <v>7029064</v>
+        <v>7029026</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3172,7 +3189,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3182,12 +3199,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3201,17 +3218,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3229,10 +3246,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122719822</v>
+        <v>122719930</v>
       </c>
       <c r="B22" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3241,41 +3258,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452152</v>
+        <v>452148</v>
       </c>
       <c r="R22" t="n">
-        <v>7029283</v>
+        <v>7029296</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3304,7 +3330,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3314,12 +3340,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3334,22 +3360,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122715191</v>
+        <v>122720127</v>
       </c>
       <c r="B23" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3358,41 +3384,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452150</v>
+        <v>452123</v>
       </c>
       <c r="R23" t="n">
-        <v>7029062</v>
+        <v>7029202</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3421,7 +3461,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3431,12 +3471,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3451,22 +3491,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122716687</v>
+        <v>122717632</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>79718</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3475,31 +3515,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3508,13 +3557,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451933</v>
+        <v>452015</v>
       </c>
       <c r="R24" t="n">
-        <v>7028984</v>
+        <v>7029092</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3543,7 +3592,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3553,12 +3602,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3569,26 +3618,41 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122717325</v>
+        <v>122715739</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3601,46 +3665,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452006</v>
+        <v>452142</v>
       </c>
       <c r="R25" t="n">
-        <v>7029026</v>
+        <v>7029004</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3669,7 +3724,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,12 +3734,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3695,41 +3750,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720084</v>
+        <v>122720532</v>
       </c>
       <c r="B26" t="n">
-        <v>79848</v>
+        <v>78850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3742,26 +3782,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3769,19 +3809,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452101</v>
+        <v>452156</v>
       </c>
       <c r="R26" t="n">
-        <v>7029256</v>
+        <v>7029109</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3810,7 +3855,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3820,12 +3865,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3836,26 +3881,41 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715592</v>
+        <v>122716262</v>
       </c>
       <c r="B27" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3864,30 +3924,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3897,7 +3957,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3906,13 +3966,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452141</v>
+        <v>452093</v>
       </c>
       <c r="R27" t="n">
-        <v>7028992</v>
+        <v>7029013</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3941,7 +4001,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3951,12 +4011,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3971,22 +4031,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122717834</v>
+        <v>122716759</v>
       </c>
       <c r="B28" t="n">
-        <v>79718</v>
+        <v>79751</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3995,30 +4055,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>389</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4026,21 +4086,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452029</v>
+        <v>451898</v>
       </c>
       <c r="R28" t="n">
-        <v>7029079</v>
+        <v>7028975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4072,7 +4127,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4082,12 +4137,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4098,41 +4153,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122720261</v>
+        <v>122715337</v>
       </c>
       <c r="B29" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4145,37 +4185,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452124</v>
+        <v>452138</v>
       </c>
       <c r="R29" t="n">
-        <v>7029259</v>
+        <v>7029066</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4204,7 +4253,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4214,12 +4263,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4261,10 +4310,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122715007</v>
+        <v>122716633</v>
       </c>
       <c r="B30" t="n">
-        <v>79751</v>
+        <v>79876</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4277,37 +4326,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452170</v>
+        <v>451941</v>
       </c>
       <c r="R30" t="n">
-        <v>7029085</v>
+        <v>7028960</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4336,7 +4390,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4346,12 +4400,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4365,17 +4419,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4393,7 +4447,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122715391</v>
+        <v>122715120</v>
       </c>
       <c r="B31" t="n">
         <v>79807</v>
@@ -4433,13 +4487,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452136</v>
+        <v>452148</v>
       </c>
       <c r="R31" t="n">
-        <v>7029025</v>
+        <v>7029055</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4468,7 +4522,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4478,7 +4532,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4510,10 +4564,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715739</v>
+        <v>122716396</v>
       </c>
       <c r="B32" t="n">
-        <v>77699</v>
+        <v>78850</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4526,37 +4580,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452142</v>
+        <v>451975</v>
       </c>
       <c r="R32" t="n">
-        <v>7029004</v>
+        <v>7029033</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4585,7 +4648,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4595,12 +4658,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4615,22 +4678,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122719770</v>
+        <v>122719912</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4643,26 +4706,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4676,13 +4739,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452163</v>
+        <v>452222</v>
       </c>
       <c r="R33" t="n">
-        <v>7029302</v>
+        <v>7029287</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4711,7 +4774,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4721,12 +4784,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4746,17 +4809,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122716346</v>
+        <v>122715671</v>
       </c>
       <c r="B34" t="n">
-        <v>74868</v>
+        <v>79718</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4765,38 +4828,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>389</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451984</v>
+        <v>452132</v>
       </c>
       <c r="R34" t="n">
-        <v>7029029</v>
+        <v>7028982</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
@@ -4828,7 +4905,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4838,12 +4915,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4857,17 +4934,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4885,10 +4962,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122717199</v>
+        <v>122717254</v>
       </c>
       <c r="B35" t="n">
-        <v>77699</v>
+        <v>74868</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4901,21 +4978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4975,7 +5052,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5017,10 +5094,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122715921</v>
+        <v>122715838</v>
       </c>
       <c r="B36" t="n">
-        <v>79807</v>
+        <v>74863</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5029,43 +5106,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452116</v>
+        <v>452109</v>
       </c>
       <c r="R36" t="n">
-        <v>7028982</v>
+        <v>7029006</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5097,7 +5169,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5107,12 +5179,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5126,17 +5198,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5154,10 +5226,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122717554</v>
+        <v>122717990</v>
       </c>
       <c r="B37" t="n">
-        <v>79718</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5166,30 +5238,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5197,24 +5269,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452007</v>
+        <v>452063</v>
       </c>
       <c r="R37" t="n">
-        <v>7029050</v>
+        <v>7029079</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5243,7 +5310,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5253,12 +5320,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5269,41 +5336,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122719813</v>
+        <v>122719902</v>
       </c>
       <c r="B38" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5312,41 +5364,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452159</v>
+        <v>452150</v>
       </c>
       <c r="R38" t="n">
-        <v>7029305</v>
+        <v>7029301</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5375,7 +5436,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5385,12 +5446,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5432,10 +5493,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122716868</v>
+        <v>122719982</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79022</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5444,31 +5505,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5477,13 +5538,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451931</v>
+        <v>452143</v>
       </c>
       <c r="R39" t="n">
-        <v>7029005</v>
+        <v>7029283</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5512,7 +5573,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5522,12 +5583,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5541,17 +5602,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5569,10 +5630,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122716182</v>
+        <v>122716787</v>
       </c>
       <c r="B40" t="n">
-        <v>57499</v>
+        <v>79807</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5585,46 +5646,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100110</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452106</v>
+        <v>451914</v>
       </c>
       <c r="R40" t="n">
-        <v>7028976</v>
+        <v>7028996</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5653,7 +5710,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5663,7 +5720,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5674,26 +5736,41 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122720532</v>
+        <v>122719970</v>
       </c>
       <c r="B41" t="n">
-        <v>78850</v>
+        <v>79848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5706,26 +5783,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5733,24 +5810,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452156</v>
+        <v>452133</v>
       </c>
       <c r="R41" t="n">
-        <v>7029109</v>
+        <v>7029267</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5779,7 +5851,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5789,12 +5861,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5805,41 +5877,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122720354</v>
+        <v>122715877</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5848,25 +5905,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5876,13 +5933,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452114</v>
+        <v>452106</v>
       </c>
       <c r="R42" t="n">
-        <v>7029211</v>
+        <v>7028977</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5911,7 +5968,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5921,12 +5978,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5937,23 +5994,38 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122717356</v>
+        <v>122719742</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -5988,7 +6060,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6002,10 +6074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452001</v>
+        <v>452167</v>
       </c>
       <c r="R43" t="n">
-        <v>7029043</v>
+        <v>7029292</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6037,7 +6109,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6047,12 +6119,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6063,21 +6135,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6094,10 +6151,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122720266</v>
+        <v>122720379</v>
       </c>
       <c r="B44" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6110,37 +6167,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452125</v>
+        <v>452127</v>
       </c>
       <c r="R44" t="n">
-        <v>7029254</v>
+        <v>7029209</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6169,7 +6235,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6179,12 +6245,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6199,22 +6265,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717632</v>
+        <v>122719770</v>
       </c>
       <c r="B45" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6223,25 +6289,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6254,24 +6320,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452015</v>
+        <v>452163</v>
       </c>
       <c r="R45" t="n">
-        <v>7029092</v>
+        <v>7029302</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6300,7 +6361,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6310,12 +6371,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6326,41 +6387,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122715337</v>
+        <v>122717554</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6369,25 +6415,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6400,16 +6446,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452138</v>
+        <v>452007</v>
       </c>
       <c r="R46" t="n">
-        <v>7029066</v>
+        <v>7029050</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
@@ -6441,7 +6492,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6451,12 +6502,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6470,17 +6521,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6498,10 +6549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122716759</v>
+        <v>122719668</v>
       </c>
       <c r="B47" t="n">
-        <v>79751</v>
+        <v>79883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6514,31 +6565,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6547,10 +6594,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451898</v>
+        <v>452187</v>
       </c>
       <c r="R47" t="n">
-        <v>7028975</v>
+        <v>7029250</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6582,7 +6629,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6592,12 +6639,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6608,26 +6655,41 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122715547</v>
+        <v>122715592</v>
       </c>
       <c r="B48" t="n">
-        <v>79882</v>
+        <v>79807</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6640,24 +6702,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
@@ -6670,7 +6746,7 @@
         <v>7028992</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6699,7 +6775,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6709,12 +6785,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6741,10 +6817,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122717731</v>
+        <v>122715754</v>
       </c>
       <c r="B49" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6753,55 +6829,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452035</v>
+        <v>452130</v>
       </c>
       <c r="R49" t="n">
-        <v>7029085</v>
+        <v>7029002</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6830,7 +6892,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6840,12 +6902,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6856,21 +6918,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6887,10 +6934,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122716633</v>
+        <v>122717157</v>
       </c>
       <c r="B50" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6899,31 +6946,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6932,13 +6979,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451941</v>
+        <v>451983</v>
       </c>
       <c r="R50" t="n">
-        <v>7028960</v>
+        <v>7029027</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6967,7 +7014,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6977,12 +7024,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6993,21 +7040,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7024,10 +7056,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122717990</v>
+        <v>122720194</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7040,26 +7072,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7073,13 +7105,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452063</v>
+        <v>452133</v>
       </c>
       <c r="R51" t="n">
-        <v>7029079</v>
+        <v>7029299</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7108,7 +7140,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7118,12 +7150,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7150,10 +7182,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715877</v>
+        <v>122715130</v>
       </c>
       <c r="B52" t="n">
-        <v>79751</v>
+        <v>90955</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7166,21 +7198,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7190,13 +7222,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452106</v>
+        <v>452148</v>
       </c>
       <c r="R52" t="n">
-        <v>7028977</v>
+        <v>7029055</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7225,7 +7257,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7235,12 +7267,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7251,21 +7283,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7282,10 +7299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715859</v>
+        <v>122717199</v>
       </c>
       <c r="B53" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7298,21 +7315,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7322,13 +7339,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452106</v>
+        <v>451981</v>
       </c>
       <c r="R53" t="n">
-        <v>7028976</v>
+        <v>7029020</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7357,7 +7374,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7367,12 +7384,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7383,26 +7400,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720127</v>
+        <v>122715104</v>
       </c>
       <c r="B54" t="n">
-        <v>79848</v>
+        <v>91389</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7411,55 +7443,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452123</v>
+        <v>452162</v>
       </c>
       <c r="R54" t="n">
-        <v>7029202</v>
+        <v>7029063</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7488,7 +7506,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7498,12 +7516,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7518,22 +7536,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122720303</v>
+        <v>122716346</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7546,46 +7564,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452124</v>
+        <v>451984</v>
       </c>
       <c r="R55" t="n">
-        <v>7029259</v>
+        <v>7029029</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7614,7 +7623,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7624,12 +7633,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7671,10 +7680,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122719982</v>
+        <v>122715007</v>
       </c>
       <c r="B56" t="n">
-        <v>79022</v>
+        <v>79751</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7687,39 +7696,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6459</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452143</v>
+        <v>452170</v>
       </c>
       <c r="R56" t="n">
-        <v>7029283</v>
+        <v>7029085</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7751,7 +7755,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7761,12 +7765,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7780,17 +7784,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7808,10 +7812,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122720194</v>
+        <v>122716428</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7824,43 +7828,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452133</v>
+        <v>451979</v>
       </c>
       <c r="R57" t="n">
-        <v>7029299</v>
+        <v>7029020</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7892,7 +7887,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7902,12 +7897,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7934,10 +7929,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122715650</v>
+        <v>122714960</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7950,21 +7945,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7974,13 +7969,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452125</v>
+        <v>452178</v>
       </c>
       <c r="R58" t="n">
-        <v>7028994</v>
+        <v>7029093</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8009,7 +8004,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8019,7 +8014,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8034,19 +8034,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122714976</v>
+        <v>122719605</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -8095,13 +8095,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452178</v>
+        <v>452187</v>
       </c>
       <c r="R59" t="n">
-        <v>7029092</v>
+        <v>7029250</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8140,7 +8140,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8155,22 +8160,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715131</v>
+        <v>122720084</v>
       </c>
       <c r="B60" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8183,37 +8188,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452147</v>
+        <v>452101</v>
       </c>
       <c r="R60" t="n">
-        <v>7029041</v>
+        <v>7029256</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8242,7 +8256,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8252,12 +8266,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8284,10 +8298,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122716428</v>
+        <v>122715370</v>
       </c>
       <c r="B61" t="n">
-        <v>74863</v>
+        <v>79302</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8300,37 +8314,51 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>1352</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451979</v>
+        <v>452135</v>
       </c>
       <c r="R61" t="n">
-        <v>7029020</v>
+        <v>7029012</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8359,7 +8387,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8369,12 +8397,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8527,10 +8555,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122720150</v>
+        <v>122716182</v>
       </c>
       <c r="B63" t="n">
-        <v>77699</v>
+        <v>57499</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8539,41 +8567,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228579</v>
+        <v>100110</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452132</v>
+        <v>452106</v>
       </c>
       <c r="R63" t="n">
-        <v>7029266</v>
+        <v>7028976</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8602,7 +8639,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8612,12 +8649,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8628,41 +8660,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122719668</v>
+        <v>122719701</v>
       </c>
       <c r="B64" t="n">
-        <v>79883</v>
+        <v>79751</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8675,27 +8692,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8704,13 +8725,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452187</v>
+        <v>452180</v>
       </c>
       <c r="R64" t="n">
-        <v>7029250</v>
+        <v>7029296</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8739,7 +8760,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8749,12 +8770,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8765,38 +8786,23 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122715671</v>
+        <v>122717676</v>
       </c>
       <c r="B65" t="n">
         <v>79718</v>
@@ -8831,7 +8837,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8850,13 +8856,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452132</v>
+        <v>452027</v>
       </c>
       <c r="R65" t="n">
-        <v>7028982</v>
+        <v>7029091</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8885,7 +8891,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8895,12 +8901,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8942,10 +8948,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122717893</v>
+        <v>122720303</v>
       </c>
       <c r="B66" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8954,30 +8960,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8985,24 +8991,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452029</v>
+        <v>452124</v>
       </c>
       <c r="R66" t="n">
-        <v>7029076</v>
+        <v>7029259</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9031,7 +9032,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9041,12 +9042,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9060,17 +9061,17 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9088,10 +9089,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122715130</v>
+        <v>122714976</v>
       </c>
       <c r="B67" t="n">
-        <v>90955</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9100,41 +9101,50 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452148</v>
+        <v>452178</v>
       </c>
       <c r="R67" t="n">
-        <v>7029055</v>
+        <v>7029092</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9163,7 +9173,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9173,12 +9183,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9193,22 +9198,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122716262</v>
+        <v>122720261</v>
       </c>
       <c r="B68" t="n">
-        <v>79718</v>
+        <v>74863</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9217,52 +9222,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>389</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452093</v>
+        <v>452124</v>
       </c>
       <c r="R68" t="n">
-        <v>7029013</v>
+        <v>7029259</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9294,7 +9285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9304,12 +9295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9320,6 +9311,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9336,10 +9342,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122719912</v>
+        <v>122715131</v>
       </c>
       <c r="B69" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9352,46 +9358,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452222</v>
+        <v>452147</v>
       </c>
       <c r="R69" t="n">
-        <v>7029287</v>
+        <v>7029041</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9420,7 +9417,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9430,12 +9427,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9462,10 +9459,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122717676</v>
+        <v>122716687</v>
       </c>
       <c r="B70" t="n">
-        <v>79718</v>
+        <v>90944</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9474,40 +9471,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>389</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9516,13 +9504,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452027</v>
+        <v>451933</v>
       </c>
       <c r="R70" t="n">
-        <v>7029091</v>
+        <v>7028984</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9551,7 +9539,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9561,12 +9549,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9577,41 +9565,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122719701</v>
+        <v>122717356</v>
       </c>
       <c r="B71" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9620,30 +9593,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9657,13 +9630,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452180</v>
+        <v>452001</v>
       </c>
       <c r="R71" t="n">
-        <v>7029296</v>
+        <v>7029043</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9692,7 +9665,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9702,12 +9675,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9718,26 +9691,41 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122715140</v>
+        <v>122716868</v>
       </c>
       <c r="B72" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9750,31 +9738,27 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9783,13 +9767,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452148</v>
+        <v>451931</v>
       </c>
       <c r="R72" t="n">
-        <v>7029055</v>
+        <v>7029005</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9818,7 +9802,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9828,12 +9812,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9844,6 +9828,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9860,10 +9859,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122719902</v>
+        <v>122715067</v>
       </c>
       <c r="B73" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9872,50 +9871,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452150</v>
+        <v>452163</v>
       </c>
       <c r="R73" t="n">
-        <v>7029301</v>
+        <v>7029067</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9944,7 +9934,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9954,12 +9944,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9973,17 +9963,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10001,10 +9991,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122717157</v>
+        <v>122719813</v>
       </c>
       <c r="B74" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10013,43 +10003,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451983</v>
+        <v>452159</v>
       </c>
       <c r="R74" t="n">
-        <v>7029027</v>
+        <v>7029305</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10081,7 +10066,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10091,12 +10076,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10107,6 +10092,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -10123,10 +10123,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122716081</v>
+        <v>122717285</v>
       </c>
       <c r="B75" t="n">
-        <v>78959</v>
+        <v>57478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10135,38 +10135,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>230552</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10174,13 +10171,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452077</v>
+        <v>452000</v>
       </c>
       <c r="R75" t="n">
-        <v>7029012</v>
+        <v>7029026</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10209,7 +10206,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10219,12 +10216,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10233,24 +10230,8 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10267,10 +10248,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122717285</v>
+        <v>122716081</v>
       </c>
       <c r="B76" t="n">
-        <v>57478</v>
+        <v>78959</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10279,35 +10260,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>230552</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10315,13 +10299,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452000</v>
+        <v>452077</v>
       </c>
       <c r="R76" t="n">
-        <v>7029026</v>
+        <v>7029012</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10350,7 +10334,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10360,12 +10344,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10374,8 +10358,24 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10392,7 +10392,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122718456</v>
+        <v>122716494</v>
       </c>
       <c r="B77" t="n">
         <v>57478</v>
@@ -10436,14 +10436,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452038</v>
+        <v>451971</v>
       </c>
       <c r="R77" t="n">
-        <v>7029084</v>
+        <v>7029000</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
+          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10501,6 +10501,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10642,7 +10657,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122716494</v>
+        <v>122718456</v>
       </c>
       <c r="B79" t="n">
         <v>57478</v>
@@ -10686,14 +10701,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>451971</v>
+        <v>452038</v>
       </c>
       <c r="R79" t="n">
-        <v>7029000</v>
+        <v>7029084</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10725,7 +10740,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10735,12 +10750,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10751,21 +10766,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715191</v>
+        <v>122720266</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452150</v>
+        <v>452125</v>
       </c>
       <c r="R2" t="n">
-        <v>7029062</v>
+        <v>7029254</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122720354</v>
+        <v>122715191</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452114</v>
+        <v>452150</v>
       </c>
       <c r="R3" t="n">
-        <v>7029211</v>
+        <v>7029062</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122716416</v>
+        <v>122720354</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,46 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451964</v>
+        <v>452114</v>
       </c>
       <c r="R4" t="n">
-        <v>7029026</v>
+        <v>7029211</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,38 +1010,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122715650</v>
+        <v>122716416</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1083,20 +1059,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452125</v>
+        <v>451964</v>
       </c>
       <c r="R5" t="n">
-        <v>7028994</v>
+        <v>7029026</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,26 +1136,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122720088</v>
+        <v>122715650</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,25 +1179,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1202,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452118</v>
+        <v>452125</v>
       </c>
       <c r="R6" t="n">
-        <v>7029273</v>
+        <v>7028994</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,12 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,41 +1263,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122720266</v>
+        <v>122720088</v>
       </c>
       <c r="B7" t="n">
-        <v>77699</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,25 +1291,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1334,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452125</v>
+        <v>452118</v>
       </c>
       <c r="R7" t="n">
-        <v>7029254</v>
+        <v>7029273</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1369,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,12 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,16 +1380,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715739</v>
+        <v>122720532</v>
       </c>
       <c r="B25" t="n">
-        <v>77699</v>
+        <v>78850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3665,37 +3665,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452142</v>
+        <v>452156</v>
       </c>
       <c r="R25" t="n">
-        <v>7029004</v>
+        <v>7029109</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3724,7 +3738,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3734,12 +3748,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3750,26 +3764,41 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720532</v>
+        <v>122715739</v>
       </c>
       <c r="B26" t="n">
-        <v>78850</v>
+        <v>77699</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3782,51 +3811,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452156</v>
+        <v>452142</v>
       </c>
       <c r="R26" t="n">
-        <v>7029109</v>
+        <v>7029004</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3855,7 +3870,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3865,12 +3880,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3881,31 +3896,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122715120</v>
+        <v>122719912</v>
       </c>
       <c r="B31" t="n">
-        <v>79807</v>
+        <v>79848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4459,41 +4459,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452148</v>
+        <v>452222</v>
       </c>
       <c r="R31" t="n">
-        <v>7029055</v>
+        <v>7029287</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4522,7 +4531,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4532,12 +4541,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4552,12 +4561,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4690,10 +4699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122719912</v>
+        <v>122715671</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>79718</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4702,30 +4711,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>389</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4733,19 +4742,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452222</v>
+        <v>452132</v>
       </c>
       <c r="R33" t="n">
-        <v>7029287</v>
+        <v>7028982</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4774,7 +4788,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4784,12 +4798,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4800,26 +4814,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715671</v>
+        <v>122717254</v>
       </c>
       <c r="B34" t="n">
-        <v>79718</v>
+        <v>74868</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4828,55 +4857,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>389</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452132</v>
+        <v>451981</v>
       </c>
       <c r="R34" t="n">
-        <v>7028982</v>
+        <v>7029020</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4905,7 +4920,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4915,12 +4930,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4934,17 +4949,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4962,10 +4977,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122717254</v>
+        <v>122715838</v>
       </c>
       <c r="B35" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4978,21 +4993,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5002,10 +5017,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451981</v>
+        <v>452109</v>
       </c>
       <c r="R35" t="n">
-        <v>7029020</v>
+        <v>7029006</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5037,7 +5052,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5047,12 +5062,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5094,10 +5109,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122715838</v>
+        <v>122717990</v>
       </c>
       <c r="B36" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5110,34 +5125,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452109</v>
+        <v>452063</v>
       </c>
       <c r="R36" t="n">
-        <v>7029006</v>
+        <v>7029079</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5169,7 +5193,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5179,12 +5203,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5195,41 +5219,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122717990</v>
+        <v>122715120</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5238,50 +5247,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452063</v>
+        <v>452148</v>
       </c>
       <c r="R37" t="n">
-        <v>7029079</v>
+        <v>7029055</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5340,12 +5340,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122717199</v>
+        <v>122715104</v>
       </c>
       <c r="B53" t="n">
-        <v>77699</v>
+        <v>91389</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7311,25 +7311,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7339,13 +7339,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451981</v>
+        <v>452162</v>
       </c>
       <c r="R53" t="n">
-        <v>7029020</v>
+        <v>7029063</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7384,12 +7384,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7400,21 +7400,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7431,10 +7416,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122715104</v>
+        <v>122716346</v>
       </c>
       <c r="B54" t="n">
-        <v>91389</v>
+        <v>74868</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7443,25 +7428,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1467</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7471,10 +7456,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452162</v>
+        <v>451984</v>
       </c>
       <c r="R54" t="n">
-        <v>7029063</v>
+        <v>7029029</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -7506,7 +7491,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7516,12 +7501,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7532,6 +7517,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7548,10 +7548,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122716346</v>
+        <v>122715007</v>
       </c>
       <c r="B55" t="n">
-        <v>74868</v>
+        <v>79751</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7560,25 +7560,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1467</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451984</v>
+        <v>452170</v>
       </c>
       <c r="R55" t="n">
-        <v>7029029</v>
+        <v>7029085</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7652,17 +7652,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7680,10 +7680,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122715007</v>
+        <v>122716428</v>
       </c>
       <c r="B56" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7692,25 +7692,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7720,13 +7720,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452170</v>
+        <v>451979</v>
       </c>
       <c r="R56" t="n">
-        <v>7029085</v>
+        <v>7029020</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7781,38 +7781,23 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122716428</v>
+        <v>122714960</v>
       </c>
       <c r="B57" t="n">
         <v>74863</v>
@@ -7852,13 +7837,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451979</v>
+        <v>452178</v>
       </c>
       <c r="R57" t="n">
-        <v>7029020</v>
+        <v>7029093</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7887,7 +7872,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7897,12 +7882,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7917,22 +7902,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122714960</v>
+        <v>122719605</v>
       </c>
       <c r="B58" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7945,37 +7930,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452178</v>
+        <v>452187</v>
       </c>
       <c r="R58" t="n">
-        <v>7029093</v>
+        <v>7029250</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8004,7 +7998,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8014,12 +8008,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8046,10 +8040,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719605</v>
+        <v>122717199</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8062,43 +8056,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452187</v>
+        <v>451981</v>
       </c>
       <c r="R59" t="n">
-        <v>7029250</v>
+        <v>7029020</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8130,7 +8115,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8140,12 +8125,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8156,6 +8141,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -8555,10 +8555,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716182</v>
+        <v>122719701</v>
       </c>
       <c r="B63" t="n">
-        <v>57499</v>
+        <v>79751</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8571,21 +8571,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100110</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8593,24 +8593,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452106</v>
+        <v>452180</v>
       </c>
       <c r="R63" t="n">
-        <v>7028976</v>
+        <v>7029296</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8649,7 +8649,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8669,17 +8674,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122719701</v>
+        <v>122717676</v>
       </c>
       <c r="B64" t="n">
-        <v>79751</v>
+        <v>79718</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8688,30 +8693,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6456</v>
+        <v>389</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8719,19 +8724,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452180</v>
+        <v>452027</v>
       </c>
       <c r="R64" t="n">
-        <v>7029296</v>
+        <v>7029091</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8760,7 +8770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8770,12 +8780,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8786,26 +8796,41 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122717676</v>
+        <v>122720261</v>
       </c>
       <c r="B65" t="n">
-        <v>79718</v>
+        <v>74863</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8814,52 +8839,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>389</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452027</v>
+        <v>452124</v>
       </c>
       <c r="R65" t="n">
-        <v>7029091</v>
+        <v>7029259</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8891,7 +8902,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8901,12 +8912,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8920,17 +8931,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9210,10 +9221,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122720261</v>
+        <v>122715131</v>
       </c>
       <c r="B68" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9226,21 +9237,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9250,13 +9261,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452124</v>
+        <v>452147</v>
       </c>
       <c r="R68" t="n">
-        <v>7029259</v>
+        <v>7029041</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9285,7 +9296,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9295,12 +9306,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9311,41 +9322,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122715131</v>
+        <v>122715067</v>
       </c>
       <c r="B69" t="n">
-        <v>77699</v>
+        <v>79751</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9354,25 +9350,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9382,13 +9378,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452147</v>
+        <v>452163</v>
       </c>
       <c r="R69" t="n">
-        <v>7029041</v>
+        <v>7029067</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9417,7 +9413,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9427,12 +9423,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9443,26 +9439,41 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122716687</v>
+        <v>122716868</v>
       </c>
       <c r="B70" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9475,27 +9486,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9504,13 +9515,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451933</v>
+        <v>451931</v>
       </c>
       <c r="R70" t="n">
-        <v>7028984</v>
+        <v>7029005</v>
       </c>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9539,7 +9550,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9549,12 +9560,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9565,26 +9576,41 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122717356</v>
+        <v>122716687</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9597,31 +9623,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9630,13 +9652,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452001</v>
+        <v>451933</v>
       </c>
       <c r="R71" t="n">
-        <v>7029043</v>
+        <v>7028984</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9665,7 +9687,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9675,12 +9697,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9691,41 +9713,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122716868</v>
+        <v>122717356</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9738,27 +9745,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9767,13 +9778,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>451931</v>
+        <v>452001</v>
       </c>
       <c r="R72" t="n">
-        <v>7029005</v>
+        <v>7029043</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9802,7 +9813,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9812,12 +9823,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9859,10 +9870,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122715067</v>
+        <v>122719813</v>
       </c>
       <c r="B73" t="n">
-        <v>79751</v>
+        <v>79876</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9875,21 +9886,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9899,13 +9910,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452163</v>
+        <v>452159</v>
       </c>
       <c r="R73" t="n">
-        <v>7029067</v>
+        <v>7029305</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9934,7 +9945,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9944,12 +9955,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9963,17 +9974,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9991,10 +10002,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122719813</v>
+        <v>122717285</v>
       </c>
       <c r="B74" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10003,38 +10014,46 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452159</v>
+        <v>452000</v>
       </c>
       <c r="R74" t="n">
-        <v>7029305</v>
+        <v>7029026</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10066,7 +10085,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10076,12 +10095,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10092,21 +10111,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -10123,10 +10127,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122717285</v>
+        <v>122716081</v>
       </c>
       <c r="B75" t="n">
-        <v>57478</v>
+        <v>78959</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10135,35 +10139,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>230552</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10171,13 +10178,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452000</v>
+        <v>452077</v>
       </c>
       <c r="R75" t="n">
-        <v>7029026</v>
+        <v>7029012</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10206,7 +10213,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10216,12 +10223,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10230,8 +10237,24 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10248,10 +10271,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122716081</v>
+        <v>122716494</v>
       </c>
       <c r="B76" t="n">
-        <v>78959</v>
+        <v>57478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10260,38 +10283,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>230552</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10299,13 +10319,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452077</v>
+        <v>451971</v>
       </c>
       <c r="R76" t="n">
-        <v>7029012</v>
+        <v>7029000</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10334,7 +10354,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10344,12 +10364,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10358,7 +10378,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -10392,7 +10411,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122716494</v>
+        <v>122716459</v>
       </c>
       <c r="B77" t="n">
         <v>57478</v>
@@ -10440,10 +10459,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451971</v>
+        <v>451969</v>
       </c>
       <c r="R77" t="n">
-        <v>7029000</v>
+        <v>7029008</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10475,7 +10494,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10485,12 +10504,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
+          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10501,21 +10520,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10532,7 +10536,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122716459</v>
+        <v>122718456</v>
       </c>
       <c r="B78" t="n">
         <v>57478</v>
@@ -10576,14 +10580,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>451969</v>
+        <v>452038</v>
       </c>
       <c r="R78" t="n">
-        <v>7029008</v>
+        <v>7029084</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10615,7 +10619,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10625,12 +10629,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10657,61 +10661,62 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122718456</v>
+        <v>122716182</v>
       </c>
       <c r="B79" t="n">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452038</v>
+        <v>452106</v>
       </c>
       <c r="R79" t="n">
-        <v>7029084</v>
+        <v>7028976</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10740,7 +10745,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10750,12 +10755,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10770,12 +10770,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715191</v>
+        <v>122715120</v>
       </c>
       <c r="B3" t="n">
-        <v>79751</v>
+        <v>79807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452150</v>
+        <v>452148</v>
       </c>
       <c r="R3" t="n">
-        <v>7029062</v>
+        <v>7029055</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122720354</v>
+        <v>122720084</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +925,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452114</v>
+        <v>452101</v>
       </c>
       <c r="R4" t="n">
-        <v>7029211</v>
+        <v>7029256</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122716416</v>
+        <v>122716633</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,35 +1047,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451964</v>
+        <v>451941</v>
       </c>
       <c r="R5" t="n">
-        <v>7029026</v>
+        <v>7028960</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,17 +1144,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1167,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715650</v>
+        <v>122716262</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,38 +1184,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452125</v>
+        <v>452093</v>
       </c>
       <c r="R6" t="n">
-        <v>7028994</v>
+        <v>7029013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1261,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1271,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,22 +1291,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122720088</v>
+        <v>122715754</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>79807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,21 +1319,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,13 +1343,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452118</v>
+        <v>452130</v>
       </c>
       <c r="R7" t="n">
-        <v>7029273</v>
+        <v>7029002</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1378,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1388,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,21 +1404,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1411,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122715391</v>
+        <v>122720150</v>
       </c>
       <c r="B8" t="n">
-        <v>79807</v>
+        <v>77699</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1423,25 +1432,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1451,13 +1460,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452136</v>
+        <v>452132</v>
       </c>
       <c r="R8" t="n">
-        <v>7029025</v>
+        <v>7029266</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1495,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,12 +1505,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,6 +1521,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1528,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122715784</v>
+        <v>122715140</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1544,31 +1568,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1577,13 +1601,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452116</v>
+        <v>452148</v>
       </c>
       <c r="R9" t="n">
-        <v>7029000</v>
+        <v>7029055</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1612,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1622,12 +1646,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122715140</v>
+        <v>122720127</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>79848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1670,31 +1694,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1703,13 +1732,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452148</v>
+        <v>452123</v>
       </c>
       <c r="R10" t="n">
-        <v>7029055</v>
+        <v>7029202</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1738,7 +1767,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,12 +1777,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,22 +1797,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122717834</v>
+        <v>122719982</v>
       </c>
       <c r="B11" t="n">
-        <v>79718</v>
+        <v>79022</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,37 +1821,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>389</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -1834,10 +1854,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452029</v>
+        <v>452143</v>
       </c>
       <c r="R11" t="n">
-        <v>7029079</v>
+        <v>7029283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1869,7 +1889,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1879,12 +1899,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,17 +1918,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1926,7 +1946,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122717401</v>
+        <v>122717356</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1975,13 +1995,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452013</v>
+        <v>452001</v>
       </c>
       <c r="R12" t="n">
-        <v>7029064</v>
+        <v>7029043</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2010,7 +2030,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2020,12 +2040,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,17 +2059,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2067,10 +2087,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720150</v>
+        <v>122716346</v>
       </c>
       <c r="B13" t="n">
-        <v>77699</v>
+        <v>74868</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2083,21 +2103,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2107,13 +2127,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452132</v>
+        <v>451984</v>
       </c>
       <c r="R13" t="n">
-        <v>7029266</v>
+        <v>7029029</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2142,7 +2162,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2152,12 +2172,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2199,10 +2219,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122715921</v>
+        <v>122716759</v>
       </c>
       <c r="B14" t="n">
-        <v>79807</v>
+        <v>79751</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2215,27 +2235,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med isidier</t>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2244,10 +2268,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452116</v>
+        <v>451898</v>
       </c>
       <c r="R14" t="n">
-        <v>7028982</v>
+        <v>7028975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2279,7 +2303,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2289,12 +2313,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,41 +2329,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122715859</v>
+        <v>122717157</v>
       </c>
       <c r="B15" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2352,37 +2361,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452106</v>
+        <v>451983</v>
       </c>
       <c r="R15" t="n">
-        <v>7028976</v>
+        <v>7029027</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2411,7 +2425,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2421,12 +2435,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2441,22 +2455,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122715547</v>
+        <v>122715007</v>
       </c>
       <c r="B16" t="n">
-        <v>79882</v>
+        <v>79751</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2469,21 +2483,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2493,13 +2507,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452141</v>
+        <v>452170</v>
       </c>
       <c r="R16" t="n">
-        <v>7028992</v>
+        <v>7029085</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2528,7 +2542,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2538,12 +2552,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2554,26 +2568,41 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122717724</v>
+        <v>122719605</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2586,26 +2615,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2619,13 +2648,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452034</v>
+        <v>452187</v>
       </c>
       <c r="R17" t="n">
-        <v>7029103</v>
+        <v>7029250</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2654,7 +2683,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2664,12 +2693,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2684,22 +2713,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122717731</v>
+        <v>122715391</v>
       </c>
       <c r="B18" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2708,55 +2737,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452035</v>
+        <v>452136</v>
       </c>
       <c r="R18" t="n">
-        <v>7029085</v>
+        <v>7029025</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2785,7 +2800,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2795,12 +2810,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2811,21 +2826,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122717893</v>
+        <v>122715592</v>
       </c>
       <c r="B19" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2854,30 +2854,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452029</v>
+        <v>452141</v>
       </c>
       <c r="R19" t="n">
-        <v>7029076</v>
+        <v>7028992</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2957,41 +2957,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122719822</v>
+        <v>122715784</v>
       </c>
       <c r="B20" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3000,41 +2985,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452152</v>
+        <v>452116</v>
       </c>
       <c r="R20" t="n">
-        <v>7029283</v>
+        <v>7029000</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3063,7 +3057,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3073,12 +3067,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3093,22 +3087,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122717325</v>
+        <v>122717199</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3121,46 +3115,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452006</v>
+        <v>451981</v>
       </c>
       <c r="R21" t="n">
-        <v>7029026</v>
+        <v>7029020</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3189,7 +3174,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3199,12 +3184,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3218,17 +3203,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3246,10 +3231,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122719930</v>
+        <v>122717632</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3258,30 +3243,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3289,19 +3274,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452148</v>
+        <v>452015</v>
       </c>
       <c r="R22" t="n">
-        <v>7029296</v>
+        <v>7029092</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3330,7 +3320,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3340,12 +3330,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3356,6 +3346,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3372,10 +3377,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720127</v>
+        <v>122715067</v>
       </c>
       <c r="B23" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3384,55 +3389,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452123</v>
+        <v>452163</v>
       </c>
       <c r="R23" t="n">
-        <v>7029202</v>
+        <v>7029067</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3461,7 +3452,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3471,12 +3462,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3487,26 +3478,41 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122717632</v>
+        <v>122717401</v>
       </c>
       <c r="B24" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3515,30 +3521,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3546,24 +3552,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452015</v>
+        <v>452013</v>
       </c>
       <c r="R24" t="n">
-        <v>7029092</v>
+        <v>7029064</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3592,7 +3593,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3602,12 +3603,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3621,17 +3622,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3649,10 +3650,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720532</v>
+        <v>122720194</v>
       </c>
       <c r="B25" t="n">
-        <v>78850</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3665,26 +3666,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3692,24 +3693,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452156</v>
+        <v>452133</v>
       </c>
       <c r="R25" t="n">
-        <v>7029109</v>
+        <v>7029299</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3738,7 +3734,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3748,12 +3744,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3764,41 +3760,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122715739</v>
+        <v>122719813</v>
       </c>
       <c r="B26" t="n">
-        <v>77699</v>
+        <v>79876</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3807,25 +3788,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3835,13 +3816,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452142</v>
+        <v>452159</v>
       </c>
       <c r="R26" t="n">
-        <v>7029004</v>
+        <v>7029305</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3870,7 +3851,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3880,12 +3861,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3896,26 +3877,41 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122716262</v>
+        <v>122720088</v>
       </c>
       <c r="B27" t="n">
-        <v>79718</v>
+        <v>79876</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3924,55 +3920,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>389</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452093</v>
+        <v>452118</v>
       </c>
       <c r="R27" t="n">
-        <v>7029013</v>
+        <v>7029273</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4001,7 +3983,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4011,12 +3993,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4027,6 +4009,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4043,10 +4040,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122716759</v>
+        <v>122719970</v>
       </c>
       <c r="B28" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4055,30 +4052,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4092,13 +4089,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451898</v>
+        <v>452133</v>
       </c>
       <c r="R28" t="n">
-        <v>7028975</v>
+        <v>7029267</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4127,7 +4124,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4137,12 +4134,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4169,10 +4166,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122715337</v>
+        <v>122719701</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4181,30 +4178,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4218,13 +4215,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452138</v>
+        <v>452180</v>
       </c>
       <c r="R29" t="n">
-        <v>7029066</v>
+        <v>7029296</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4253,7 +4250,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4263,12 +4260,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4279,41 +4276,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122716633</v>
+        <v>122716687</v>
       </c>
       <c r="B30" t="n">
-        <v>79876</v>
+        <v>90952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4322,31 +4304,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4355,13 +4337,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451941</v>
+        <v>451933</v>
       </c>
       <c r="R30" t="n">
-        <v>7028960</v>
+        <v>7028984</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4390,7 +4372,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4400,12 +4382,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4416,41 +4398,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122719912</v>
+        <v>122720303</v>
       </c>
       <c r="B31" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4463,26 +4430,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4496,13 +4463,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452222</v>
+        <v>452124</v>
       </c>
       <c r="R31" t="n">
-        <v>7029287</v>
+        <v>7029259</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4531,7 +4498,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4541,12 +4508,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4557,26 +4524,41 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122716396</v>
+        <v>122714960</v>
       </c>
       <c r="B32" t="n">
-        <v>78850</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4589,46 +4571,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451975</v>
+        <v>452178</v>
       </c>
       <c r="R32" t="n">
-        <v>7029033</v>
+        <v>7029093</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4657,7 +4630,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4667,12 +4640,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4699,10 +4672,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122715671</v>
+        <v>122717254</v>
       </c>
       <c r="B33" t="n">
-        <v>79718</v>
+        <v>74868</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4711,55 +4684,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>389</v>
+        <v>1467</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452132</v>
+        <v>451981</v>
       </c>
       <c r="R33" t="n">
-        <v>7028982</v>
+        <v>7029020</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4788,7 +4747,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4798,12 +4757,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4817,17 +4776,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4845,10 +4804,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122717254</v>
+        <v>122715921</v>
       </c>
       <c r="B34" t="n">
-        <v>74868</v>
+        <v>79807</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4857,38 +4816,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451981</v>
+        <v>452116</v>
       </c>
       <c r="R34" t="n">
-        <v>7029020</v>
+        <v>7028982</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4920,7 +4884,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4930,12 +4894,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4949,17 +4913,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4977,7 +4941,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715838</v>
+        <v>122720354</v>
       </c>
       <c r="B35" t="n">
         <v>74863</v>
@@ -5017,13 +4981,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452109</v>
+        <v>452114</v>
       </c>
       <c r="R35" t="n">
-        <v>7029006</v>
+        <v>7029211</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5052,7 +5016,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5062,12 +5026,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5078,41 +5042,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122717990</v>
+        <v>122715739</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5125,46 +5074,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452063</v>
+        <v>452142</v>
       </c>
       <c r="R36" t="n">
-        <v>7029079</v>
+        <v>7029004</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5193,7 +5133,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5203,12 +5143,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5235,10 +5175,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122715120</v>
+        <v>122719930</v>
       </c>
       <c r="B37" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5247,28 +5187,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
@@ -5278,10 +5227,10 @@
         <v>452148</v>
       </c>
       <c r="R37" t="n">
-        <v>7029055</v>
+        <v>7029296</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5310,7 +5259,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5320,12 +5269,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5352,10 +5301,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122719902</v>
+        <v>122715547</v>
       </c>
       <c r="B38" t="n">
-        <v>79848</v>
+        <v>79882</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5364,50 +5313,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452150</v>
+        <v>452141</v>
       </c>
       <c r="R38" t="n">
-        <v>7029301</v>
+        <v>7028992</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5436,7 +5376,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5446,12 +5386,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5462,41 +5402,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122719982</v>
+        <v>122715671</v>
       </c>
       <c r="B39" t="n">
-        <v>79022</v>
+        <v>79718</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5505,28 +5430,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6459</v>
+        <v>389</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -5538,13 +5472,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452143</v>
+        <v>452132</v>
       </c>
       <c r="R39" t="n">
-        <v>7029283</v>
+        <v>7028982</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5573,7 +5507,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5583,12 +5517,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5602,17 +5536,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5630,10 +5564,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122716787</v>
+        <v>122717325</v>
       </c>
       <c r="B40" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5642,31 +5576,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med isidier</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5675,13 +5613,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451914</v>
+        <v>452006</v>
       </c>
       <c r="R40" t="n">
-        <v>7028996</v>
+        <v>7029026</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5710,7 +5648,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5720,12 +5658,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5739,17 +5677,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5767,10 +5705,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122719970</v>
+        <v>122717990</v>
       </c>
       <c r="B41" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5783,26 +5721,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5816,13 +5754,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452133</v>
+        <v>452063</v>
       </c>
       <c r="R41" t="n">
-        <v>7029267</v>
+        <v>7029079</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5851,7 +5789,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5861,12 +5799,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5893,10 +5831,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122715877</v>
+        <v>122717724</v>
       </c>
       <c r="B42" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5905,41 +5843,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452106</v>
+        <v>452034</v>
       </c>
       <c r="R42" t="n">
-        <v>7028977</v>
+        <v>7029103</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5968,7 +5915,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5978,12 +5925,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5994,41 +5941,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122719742</v>
+        <v>122719668</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6037,35 +5969,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6074,10 +6002,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452167</v>
+        <v>452187</v>
       </c>
       <c r="R43" t="n">
-        <v>7029292</v>
+        <v>7029250</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6109,7 +6037,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6119,12 +6047,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6135,6 +6063,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6151,10 +6094,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122720379</v>
+        <v>122717893</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6163,30 +6106,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6194,16 +6137,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452127</v>
+        <v>452029</v>
       </c>
       <c r="R44" t="n">
-        <v>7029209</v>
+        <v>7029076</v>
       </c>
       <c r="S44" t="n">
         <v>6</v>
@@ -6235,7 +6183,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6245,12 +6193,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6261,6 +6209,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6277,10 +6240,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122719770</v>
+        <v>122717554</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6289,30 +6252,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6320,19 +6283,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452163</v>
+        <v>452007</v>
       </c>
       <c r="R45" t="n">
-        <v>7029302</v>
+        <v>7029050</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6361,7 +6329,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6371,12 +6339,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6387,26 +6355,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122717554</v>
+        <v>122715838</v>
       </c>
       <c r="B46" t="n">
-        <v>79718</v>
+        <v>74863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6415,55 +6398,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>389</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452007</v>
+        <v>452109</v>
       </c>
       <c r="R46" t="n">
-        <v>7029050</v>
+        <v>7029006</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6492,7 +6461,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6502,12 +6471,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6521,17 +6490,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6549,10 +6518,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122719668</v>
+        <v>122715877</v>
       </c>
       <c r="B47" t="n">
-        <v>79883</v>
+        <v>79751</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6565,42 +6534,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452187</v>
+        <v>452106</v>
       </c>
       <c r="R47" t="n">
-        <v>7029250</v>
+        <v>7028977</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6629,7 +6593,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6639,12 +6603,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6658,17 +6622,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6686,10 +6650,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122715592</v>
+        <v>122716396</v>
       </c>
       <c r="B48" t="n">
-        <v>79807</v>
+        <v>78850</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6698,30 +6662,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6729,24 +6693,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452141</v>
+        <v>451975</v>
       </c>
       <c r="R48" t="n">
-        <v>7028992</v>
+        <v>7029033</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6775,7 +6734,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6785,12 +6744,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6805,22 +6764,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122715754</v>
+        <v>122715104</v>
       </c>
       <c r="B49" t="n">
-        <v>79807</v>
+        <v>91397</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6829,25 +6788,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6857,13 +6816,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452130</v>
+        <v>452162</v>
       </c>
       <c r="R49" t="n">
-        <v>7029002</v>
+        <v>7029063</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6892,7 +6851,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6902,12 +6861,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6934,10 +6893,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122717157</v>
+        <v>122717731</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>79718</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6946,31 +6905,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>389</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6979,13 +6947,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451983</v>
+        <v>452035</v>
       </c>
       <c r="R50" t="n">
-        <v>7029027</v>
+        <v>7029085</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7014,7 +6982,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7024,12 +6992,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7040,6 +7008,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7056,10 +7039,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122720194</v>
+        <v>122717676</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7068,30 +7051,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7099,19 +7082,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452133</v>
+        <v>452027</v>
       </c>
       <c r="R51" t="n">
-        <v>7029299</v>
+        <v>7029091</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7140,7 +7128,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7150,12 +7138,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7166,26 +7154,41 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715130</v>
+        <v>122715859</v>
       </c>
       <c r="B52" t="n">
-        <v>90955</v>
+        <v>74863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7194,25 +7197,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1205</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7222,13 +7225,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452148</v>
+        <v>452106</v>
       </c>
       <c r="R52" t="n">
-        <v>7029055</v>
+        <v>7028976</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7257,7 +7260,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7267,12 +7270,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7287,22 +7290,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715104</v>
+        <v>122719770</v>
       </c>
       <c r="B53" t="n">
-        <v>91389</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7311,41 +7314,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452162</v>
+        <v>452163</v>
       </c>
       <c r="R53" t="n">
-        <v>7029063</v>
+        <v>7029302</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7374,7 +7386,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7384,12 +7396,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7404,22 +7416,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122716346</v>
+        <v>122720532</v>
       </c>
       <c r="B54" t="n">
-        <v>74868</v>
+        <v>78850</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7432,34 +7444,48 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1467</v>
+        <v>283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451984</v>
+        <v>452156</v>
       </c>
       <c r="R54" t="n">
-        <v>7029029</v>
+        <v>7029109</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -7491,7 +7517,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7501,12 +7527,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7548,10 +7574,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122715007</v>
+        <v>122719912</v>
       </c>
       <c r="B55" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7560,41 +7586,50 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452170</v>
+        <v>452222</v>
       </c>
       <c r="R55" t="n">
-        <v>7029085</v>
+        <v>7029287</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7623,7 +7658,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7633,12 +7668,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7649,41 +7684,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122716428</v>
+        <v>122719822</v>
       </c>
       <c r="B56" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7692,25 +7712,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7720,13 +7740,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451979</v>
+        <v>452152</v>
       </c>
       <c r="R56" t="n">
-        <v>7029020</v>
+        <v>7029283</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7755,7 +7775,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7765,12 +7785,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7797,10 +7817,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122714960</v>
+        <v>122715191</v>
       </c>
       <c r="B57" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7809,25 +7829,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7837,13 +7857,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452178</v>
+        <v>452150</v>
       </c>
       <c r="R57" t="n">
-        <v>7029093</v>
+        <v>7029062</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7872,7 +7892,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7882,12 +7902,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7914,10 +7934,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122719605</v>
+        <v>122716868</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7930,31 +7950,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7963,13 +7979,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452187</v>
+        <v>451931</v>
       </c>
       <c r="R58" t="n">
-        <v>7029250</v>
+        <v>7029005</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7998,7 +8014,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8008,12 +8024,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8024,6 +8040,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -8040,7 +8071,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122717199</v>
+        <v>122715131</v>
       </c>
       <c r="B59" t="n">
         <v>77699</v>
@@ -8080,13 +8111,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451981</v>
+        <v>452147</v>
       </c>
       <c r="R59" t="n">
-        <v>7029020</v>
+        <v>7029041</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8115,7 +8146,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8125,12 +8156,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8141,41 +8172,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720084</v>
+        <v>122719742</v>
       </c>
       <c r="B60" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8188,26 +8204,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8221,13 +8237,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452101</v>
+        <v>452167</v>
       </c>
       <c r="R60" t="n">
-        <v>7029256</v>
+        <v>7029292</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8256,7 +8272,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8266,12 +8282,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8286,22 +8302,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715370</v>
+        <v>122720261</v>
       </c>
       <c r="B61" t="n">
-        <v>79302</v>
+        <v>74863</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8314,51 +8330,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1352</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452135</v>
+        <v>452124</v>
       </c>
       <c r="R61" t="n">
-        <v>7029012</v>
+        <v>7029259</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8387,7 +8389,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8397,12 +8399,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8413,26 +8415,41 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122718273</v>
+        <v>122715370</v>
       </c>
       <c r="B62" t="n">
-        <v>57589</v>
+        <v>79302</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8441,35 +8458,40 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>1352</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8478,13 +8500,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452012</v>
+        <v>452135</v>
       </c>
       <c r="R62" t="n">
-        <v>7029081</v>
+        <v>7029012</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8513,7 +8535,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8523,12 +8545,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8543,22 +8565,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122719701</v>
+        <v>122720379</v>
       </c>
       <c r="B63" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8567,30 +8589,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8604,13 +8626,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452180</v>
+        <v>452127</v>
       </c>
       <c r="R63" t="n">
-        <v>7029296</v>
+        <v>7029209</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8639,7 +8661,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8649,12 +8671,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8669,22 +8691,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122717676</v>
+        <v>122718273</v>
       </c>
       <c r="B64" t="n">
-        <v>79718</v>
+        <v>57589</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8693,40 +8715,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>389</v>
+        <v>103031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8735,10 +8752,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452027</v>
+        <v>452012</v>
       </c>
       <c r="R64" t="n">
-        <v>7029091</v>
+        <v>7029081</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8770,7 +8787,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8780,12 +8797,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8796,21 +8813,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8827,10 +8829,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122720261</v>
+        <v>122716787</v>
       </c>
       <c r="B65" t="n">
-        <v>74863</v>
+        <v>79807</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8839,41 +8841,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452124</v>
+        <v>451914</v>
       </c>
       <c r="R65" t="n">
-        <v>7029259</v>
+        <v>7028996</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8902,7 +8909,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8912,12 +8919,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8959,7 +8966,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122720303</v>
+        <v>122714976</v>
       </c>
       <c r="B66" t="n">
         <v>78766</v>
@@ -8994,7 +9001,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9008,13 +9015,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452124</v>
+        <v>452178</v>
       </c>
       <c r="R66" t="n">
-        <v>7029259</v>
+        <v>7029092</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9043,7 +9050,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9053,12 +9060,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9069,38 +9071,23 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122714976</v>
+        <v>122716416</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -9135,7 +9122,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9149,13 +9136,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452178</v>
+        <v>451964</v>
       </c>
       <c r="R67" t="n">
-        <v>7029092</v>
+        <v>7029026</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9184,7 +9171,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9194,7 +9181,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9205,26 +9197,41 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122715131</v>
+        <v>122717834</v>
       </c>
       <c r="B68" t="n">
-        <v>77699</v>
+        <v>79718</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9233,41 +9240,55 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>389</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452147</v>
+        <v>452029</v>
       </c>
       <c r="R68" t="n">
-        <v>7029041</v>
+        <v>7029079</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9296,7 +9317,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9306,12 +9327,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9322,26 +9343,41 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122715067</v>
+        <v>122715130</v>
       </c>
       <c r="B69" t="n">
-        <v>79751</v>
+        <v>90963</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9354,21 +9390,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9378,13 +9414,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452163</v>
+        <v>452148</v>
       </c>
       <c r="R69" t="n">
-        <v>7029067</v>
+        <v>7029055</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9413,7 +9449,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9423,12 +9459,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9439,21 +9475,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9470,10 +9491,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122716868</v>
+        <v>122715337</v>
       </c>
       <c r="B70" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9486,27 +9507,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9515,13 +9540,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451931</v>
+        <v>452138</v>
       </c>
       <c r="R70" t="n">
-        <v>7029005</v>
+        <v>7029066</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9550,7 +9575,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9560,12 +9585,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9607,10 +9632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122716687</v>
+        <v>122715650</v>
       </c>
       <c r="B71" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9623,42 +9648,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451933</v>
+        <v>452125</v>
       </c>
       <c r="R71" t="n">
-        <v>7028984</v>
+        <v>7028994</v>
       </c>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9687,7 +9707,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9697,12 +9717,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9729,10 +9744,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122717356</v>
+        <v>122716428</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9745,46 +9760,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452001</v>
+        <v>451979</v>
       </c>
       <c r="R72" t="n">
-        <v>7029043</v>
+        <v>7029020</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9813,7 +9819,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9823,12 +9829,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9839,41 +9845,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122719813</v>
+        <v>122719902</v>
       </c>
       <c r="B73" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9882,41 +9873,50 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452159</v>
+        <v>452150</v>
       </c>
       <c r="R73" t="n">
-        <v>7029305</v>
+        <v>7029301</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10002,10 +10002,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122717285</v>
+        <v>122716081</v>
       </c>
       <c r="B74" t="n">
-        <v>57478</v>
+        <v>78959</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10014,35 +10014,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>230552</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10050,13 +10053,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452000</v>
+        <v>452077</v>
       </c>
       <c r="R74" t="n">
-        <v>7029026</v>
+        <v>7029012</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10085,7 +10088,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10095,12 +10098,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10109,8 +10112,24 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -10127,10 +10146,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122716081</v>
+        <v>122716459</v>
       </c>
       <c r="B75" t="n">
-        <v>78959</v>
+        <v>57478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10139,38 +10158,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>230552</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10178,13 +10194,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452077</v>
+        <v>451969</v>
       </c>
       <c r="R75" t="n">
-        <v>7029012</v>
+        <v>7029008</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10213,7 +10229,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10223,12 +10239,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10237,24 +10253,8 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122716494</v>
+        <v>122717285</v>
       </c>
       <c r="B76" t="n">
         <v>57478</v>
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451971</v>
+        <v>452000</v>
       </c>
       <c r="R76" t="n">
-        <v>7029000</v>
+        <v>7029026</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10380,21 +10380,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10411,7 +10396,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122716459</v>
+        <v>122716494</v>
       </c>
       <c r="B77" t="n">
         <v>57478</v>
@@ -10459,10 +10444,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451969</v>
+        <v>451971</v>
       </c>
       <c r="R77" t="n">
-        <v>7029008</v>
+        <v>7029000</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10494,7 +10479,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10504,12 +10489,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10520,6 +10505,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -1420,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122720150</v>
+        <v>122720127</v>
       </c>
       <c r="B8" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,37 +1436,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452132</v>
+        <v>452123</v>
       </c>
       <c r="R8" t="n">
-        <v>7029266</v>
+        <v>7029202</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1505,12 +1519,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,31 +1535,16 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1678,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122720127</v>
+        <v>122720150</v>
       </c>
       <c r="B10" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1694,51 +1693,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452123</v>
+        <v>452132</v>
       </c>
       <c r="R10" t="n">
-        <v>7029202</v>
+        <v>7029266</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1767,7 +1752,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1777,12 +1762,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1793,26 +1778,41 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122719982</v>
+        <v>122717157</v>
       </c>
       <c r="B11" t="n">
-        <v>79022</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,31 +1821,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452143</v>
+        <v>451983</v>
       </c>
       <c r="R11" t="n">
-        <v>7029283</v>
+        <v>7029027</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,21 +1915,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2087,10 +2072,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122716346</v>
+        <v>122719982</v>
       </c>
       <c r="B13" t="n">
-        <v>74868</v>
+        <v>79022</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2099,41 +2084,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>6459</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451984</v>
+        <v>452143</v>
       </c>
       <c r="R13" t="n">
-        <v>7029029</v>
+        <v>7029283</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2162,7 +2152,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2172,12 +2162,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2191,17 +2181,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2219,10 +2209,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122716759</v>
+        <v>122716346</v>
       </c>
       <c r="B14" t="n">
-        <v>79751</v>
+        <v>74868</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2231,50 +2221,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451898</v>
+        <v>451984</v>
       </c>
       <c r="R14" t="n">
-        <v>7028975</v>
+        <v>7029029</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2303,7 +2284,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2313,12 +2294,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2329,26 +2310,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122717157</v>
+        <v>122716759</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2357,31 +2353,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451983</v>
+        <v>451898</v>
       </c>
       <c r="R15" t="n">
-        <v>7029027</v>
+        <v>7028975</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2455,22 +2455,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122715007</v>
+        <v>122719605</v>
       </c>
       <c r="B16" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2479,38 +2479,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452170</v>
+        <v>452187</v>
       </c>
       <c r="R16" t="n">
-        <v>7029085</v>
+        <v>7029250</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2542,7 +2551,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2552,12 +2561,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2568,21 +2577,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2599,10 +2593,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719605</v>
+        <v>122715007</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2611,47 +2605,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452187</v>
+        <v>452170</v>
       </c>
       <c r="R17" t="n">
-        <v>7029250</v>
+        <v>7029085</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2683,7 +2668,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2693,12 +2678,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2709,6 +2694,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -3099,10 +3099,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122717199</v>
+        <v>122715067</v>
       </c>
       <c r="B21" t="n">
-        <v>77699</v>
+        <v>79751</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3111,25 +3111,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451981</v>
+        <v>452163</v>
       </c>
       <c r="R21" t="n">
-        <v>7029020</v>
+        <v>7029067</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3203,17 +3203,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122717632</v>
+        <v>122717199</v>
       </c>
       <c r="B22" t="n">
-        <v>79718</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3243,55 +3243,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>389</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452015</v>
+        <v>451981</v>
       </c>
       <c r="R22" t="n">
-        <v>7029092</v>
+        <v>7029020</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3320,7 +3306,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3330,12 +3316,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3349,17 +3335,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3377,10 +3363,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122715067</v>
+        <v>122717632</v>
       </c>
       <c r="B23" t="n">
-        <v>79751</v>
+        <v>79718</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3389,41 +3375,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>389</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452163</v>
+        <v>452015</v>
       </c>
       <c r="R23" t="n">
-        <v>7029067</v>
+        <v>7029092</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3509,10 +3509,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122717401</v>
+        <v>122719813</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3521,50 +3521,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452013</v>
+        <v>452159</v>
       </c>
       <c r="R24" t="n">
-        <v>7029064</v>
+        <v>7029305</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3593,7 +3584,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3603,12 +3594,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3622,17 +3613,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3650,10 +3641,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720194</v>
+        <v>122720088</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3662,50 +3653,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452133</v>
+        <v>452118</v>
       </c>
       <c r="R25" t="n">
-        <v>7029299</v>
+        <v>7029273</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3734,7 +3716,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3744,12 +3726,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3760,26 +3742,41 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122719813</v>
+        <v>122717401</v>
       </c>
       <c r="B26" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3788,41 +3785,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452159</v>
+        <v>452013</v>
       </c>
       <c r="R26" t="n">
-        <v>7029305</v>
+        <v>7029064</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3851,7 +3857,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3861,12 +3867,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3880,17 +3886,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3908,10 +3914,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720088</v>
+        <v>122720194</v>
       </c>
       <c r="B27" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3920,41 +3926,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452118</v>
+        <v>452133</v>
       </c>
       <c r="R27" t="n">
-        <v>7029273</v>
+        <v>7029299</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3983,7 +3998,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3993,12 +4008,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4009,31 +4024,16 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720354</v>
+        <v>122715739</v>
       </c>
       <c r="B35" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4957,21 +4957,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452114</v>
+        <v>452142</v>
       </c>
       <c r="R35" t="n">
-        <v>7029211</v>
+        <v>7029004</v>
       </c>
       <c r="S35" t="n">
         <v>11</v>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5058,10 +5058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122715739</v>
+        <v>122720354</v>
       </c>
       <c r="B36" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5074,21 +5074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452142</v>
+        <v>452114</v>
       </c>
       <c r="R36" t="n">
-        <v>7029004</v>
+        <v>7029211</v>
       </c>
       <c r="S36" t="n">
         <v>11</v>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5175,10 +5175,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122719930</v>
+        <v>122715547</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5187,20 +5187,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5208,29 +5208,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452148</v>
+        <v>452141</v>
       </c>
       <c r="R37" t="n">
-        <v>7029296</v>
+        <v>7028992</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5259,7 +5250,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5269,12 +5260,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5289,22 +5280,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715547</v>
+        <v>122715671</v>
       </c>
       <c r="B38" t="n">
-        <v>79882</v>
+        <v>79718</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5313,41 +5304,55 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>389</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452141</v>
+        <v>452132</v>
       </c>
       <c r="R38" t="n">
-        <v>7028992</v>
+        <v>7028982</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5376,7 +5381,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5386,12 +5391,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5402,26 +5407,41 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715671</v>
+        <v>122717325</v>
       </c>
       <c r="B39" t="n">
-        <v>79718</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5430,30 +5450,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5461,24 +5481,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452132</v>
+        <v>452006</v>
       </c>
       <c r="R39" t="n">
-        <v>7028982</v>
+        <v>7029026</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5507,7 +5522,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5517,12 +5532,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5564,7 +5579,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122717325</v>
+        <v>122717990</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -5599,7 +5614,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5613,13 +5628,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452006</v>
+        <v>452063</v>
       </c>
       <c r="R40" t="n">
-        <v>7029026</v>
+        <v>7029079</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5648,7 +5663,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5658,12 +5673,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5674,38 +5689,23 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122717990</v>
+        <v>122717724</v>
       </c>
       <c r="B41" t="n">
         <v>79847</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452063</v>
+        <v>452034</v>
       </c>
       <c r="R41" t="n">
-        <v>7029079</v>
+        <v>7029103</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122717724</v>
+        <v>122719930</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5847,26 +5847,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452034</v>
+        <v>452148</v>
       </c>
       <c r="R42" t="n">
-        <v>7029103</v>
+        <v>7029296</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5945,22 +5945,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122719668</v>
+        <v>122715838</v>
       </c>
       <c r="B43" t="n">
-        <v>79883</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5969,43 +5969,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452187</v>
+        <v>452109</v>
       </c>
       <c r="R43" t="n">
-        <v>7029250</v>
+        <v>7029006</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6037,7 +6032,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6047,12 +6042,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6066,17 +6061,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6094,10 +6089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122717893</v>
+        <v>122719668</v>
       </c>
       <c r="B44" t="n">
-        <v>79718</v>
+        <v>79883</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6106,37 +6101,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>389</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -6148,13 +6134,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452029</v>
+        <v>452187</v>
       </c>
       <c r="R44" t="n">
-        <v>7029076</v>
+        <v>7029250</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6183,7 +6169,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6193,12 +6179,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6212,17 +6198,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6240,7 +6226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717554</v>
+        <v>122717893</v>
       </c>
       <c r="B45" t="n">
         <v>79718</v>
@@ -6275,7 +6261,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6285,7 +6271,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6294,10 +6280,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452007</v>
+        <v>452029</v>
       </c>
       <c r="R45" t="n">
-        <v>7029050</v>
+        <v>7029076</v>
       </c>
       <c r="S45" t="n">
         <v>6</v>
@@ -6329,7 +6315,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6339,12 +6325,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6386,10 +6372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122715838</v>
+        <v>122717554</v>
       </c>
       <c r="B46" t="n">
-        <v>74863</v>
+        <v>79718</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6398,41 +6384,55 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>389</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452109</v>
+        <v>452007</v>
       </c>
       <c r="R46" t="n">
-        <v>7029006</v>
+        <v>7029050</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6490,17 +6490,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6893,10 +6893,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122717731</v>
+        <v>122715859</v>
       </c>
       <c r="B50" t="n">
-        <v>79718</v>
+        <v>74863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6905,52 +6905,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>389</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452035</v>
+        <v>452106</v>
       </c>
       <c r="R50" t="n">
-        <v>7029085</v>
+        <v>7028976</v>
       </c>
       <c r="S50" t="n">
         <v>8</v>
@@ -6982,7 +6968,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6992,12 +6978,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7008,38 +6994,23 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122717676</v>
+        <v>122717731</v>
       </c>
       <c r="B51" t="n">
         <v>79718</v>
@@ -7074,7 +7045,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7093,13 +7064,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452027</v>
+        <v>452035</v>
       </c>
       <c r="R51" t="n">
-        <v>7029091</v>
+        <v>7029085</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7128,7 +7099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7138,12 +7109,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7185,10 +7156,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715859</v>
+        <v>122717676</v>
       </c>
       <c r="B52" t="n">
-        <v>74863</v>
+        <v>79718</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7197,41 +7168,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>389</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452106</v>
+        <v>452027</v>
       </c>
       <c r="R52" t="n">
-        <v>7028976</v>
+        <v>7029091</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7260,7 +7245,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7270,12 +7255,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7286,16 +7271,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122720266</v>
+        <v>122715131</v>
       </c>
       <c r="B2" t="n">
         <v>77699</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452125</v>
+        <v>452147</v>
       </c>
       <c r="R2" t="n">
-        <v>7029254</v>
+        <v>7029041</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715120</v>
+        <v>122715671</v>
       </c>
       <c r="B3" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +804,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452148</v>
+        <v>452132</v>
       </c>
       <c r="R3" t="n">
-        <v>7029055</v>
+        <v>7028982</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +907,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122720084</v>
+        <v>122716687</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>90952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +954,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,13 +983,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452101</v>
+        <v>451933</v>
       </c>
       <c r="R4" t="n">
-        <v>7029256</v>
+        <v>7028984</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122716633</v>
+        <v>122720303</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,31 +1072,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451941</v>
+        <v>452124</v>
       </c>
       <c r="R5" t="n">
-        <v>7028960</v>
+        <v>7029259</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1154,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,17 +1173,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1172,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122716262</v>
+        <v>122719822</v>
       </c>
       <c r="B6" t="n">
-        <v>79718</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,55 +1213,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>389</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452093</v>
+        <v>452152</v>
       </c>
       <c r="R6" t="n">
-        <v>7029013</v>
+        <v>7029283</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,7 +1276,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1271,12 +1286,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,22 +1306,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715754</v>
+        <v>122715140</v>
       </c>
       <c r="B7" t="n">
-        <v>79807</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,41 +1330,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452130</v>
+        <v>452148</v>
       </c>
       <c r="R7" t="n">
-        <v>7029002</v>
+        <v>7029055</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,7 +1402,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1388,12 +1412,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1444,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122720127</v>
+        <v>122716428</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,51 +1460,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452123</v>
+        <v>451979</v>
       </c>
       <c r="R8" t="n">
-        <v>7029202</v>
+        <v>7029020</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1519,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,12 +1529,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1551,10 +1561,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122715140</v>
+        <v>122714960</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1567,46 +1577,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452148</v>
+        <v>452178</v>
       </c>
       <c r="R9" t="n">
-        <v>7029055</v>
+        <v>7029093</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1645,12 +1646,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122720150</v>
+        <v>122717254</v>
       </c>
       <c r="B10" t="n">
-        <v>77699</v>
+        <v>74868</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,21 +1694,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,13 +1718,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452132</v>
+        <v>451981</v>
       </c>
       <c r="R10" t="n">
-        <v>7029266</v>
+        <v>7029020</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1752,7 +1753,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1762,12 +1763,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,10 +1810,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122717157</v>
+        <v>122715007</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,43 +1822,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451983</v>
+        <v>452170</v>
       </c>
       <c r="R11" t="n">
-        <v>7029027</v>
+        <v>7029085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,7 +1885,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1899,12 +1895,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,6 +1911,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1931,10 +1942,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122717356</v>
+        <v>122715877</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1943,50 +1954,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452001</v>
+        <v>452106</v>
       </c>
       <c r="R12" t="n">
-        <v>7029043</v>
+        <v>7028977</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2015,7 +2017,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2025,12 +2027,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,17 +2046,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2072,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122719982</v>
+        <v>122719970</v>
       </c>
       <c r="B13" t="n">
-        <v>79022</v>
+        <v>79848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2084,31 +2086,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6459</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2117,13 +2123,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452143</v>
+        <v>452133</v>
       </c>
       <c r="R13" t="n">
-        <v>7029283</v>
+        <v>7029267</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2152,7 +2158,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2162,12 +2168,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,31 +2184,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2341,7 +2332,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716759</v>
+        <v>122719701</v>
       </c>
       <c r="B15" t="n">
         <v>79751</v>
@@ -2376,7 +2367,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2390,13 +2381,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451898</v>
+        <v>452180</v>
       </c>
       <c r="R15" t="n">
-        <v>7028975</v>
+        <v>7029296</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2425,7 +2416,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2435,12 +2426,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2460,17 +2451,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719605</v>
+        <v>122715547</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2479,20 +2470,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2500,29 +2491,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452187</v>
+        <v>452141</v>
       </c>
       <c r="R16" t="n">
-        <v>7029250</v>
+        <v>7028992</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2551,7 +2533,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2561,12 +2543,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2581,22 +2563,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715007</v>
+        <v>122715739</v>
       </c>
       <c r="B17" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2605,25 +2587,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2633,13 +2615,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452170</v>
+        <v>452142</v>
       </c>
       <c r="R17" t="n">
-        <v>7029085</v>
+        <v>7029004</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2668,7 +2650,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2678,12 +2660,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2694,41 +2676,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122715391</v>
+        <v>122720088</v>
       </c>
       <c r="B18" t="n">
-        <v>79807</v>
+        <v>79876</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2741,21 +2708,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2765,13 +2732,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452136</v>
+        <v>452118</v>
       </c>
       <c r="R18" t="n">
-        <v>7029025</v>
+        <v>7029273</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2800,7 +2767,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2810,12 +2777,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2826,6 +2793,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2842,10 +2824,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122715592</v>
+        <v>122715650</v>
       </c>
       <c r="B19" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2854,55 +2836,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452141</v>
+        <v>452125</v>
       </c>
       <c r="R19" t="n">
-        <v>7028992</v>
+        <v>7028994</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2931,7 +2899,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2941,12 +2909,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2973,10 +2936,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122715784</v>
+        <v>122720127</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2989,26 +2952,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3016,16 +2979,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452116</v>
+        <v>452123</v>
       </c>
       <c r="R20" t="n">
-        <v>7029000</v>
+        <v>7029202</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3057,7 +3025,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3067,12 +3035,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3087,22 +3055,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122715067</v>
+        <v>122720532</v>
       </c>
       <c r="B21" t="n">
-        <v>79751</v>
+        <v>78847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3111,41 +3079,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452163</v>
+        <v>452156</v>
       </c>
       <c r="R21" t="n">
-        <v>7029067</v>
+        <v>7029109</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3174,7 +3156,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3184,12 +3166,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3203,17 +3185,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3231,10 +3213,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122717199</v>
+        <v>122719770</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3247,37 +3229,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451981</v>
+        <v>452163</v>
       </c>
       <c r="R22" t="n">
-        <v>7029020</v>
+        <v>7029302</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3306,7 +3297,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3316,12 +3307,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3332,41 +3323,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122717632</v>
+        <v>122719930</v>
       </c>
       <c r="B23" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3375,30 +3351,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3406,24 +3382,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452015</v>
+        <v>452148</v>
       </c>
       <c r="R23" t="n">
-        <v>7029092</v>
+        <v>7029296</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3452,7 +3423,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3462,12 +3433,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3478,21 +3449,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3509,10 +3465,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122719813</v>
+        <v>122720354</v>
       </c>
       <c r="B24" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3521,25 +3477,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3549,13 +3505,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452159</v>
+        <v>452114</v>
       </c>
       <c r="R24" t="n">
-        <v>7029305</v>
+        <v>7029211</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3584,7 +3540,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3594,12 +3550,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3610,41 +3566,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720088</v>
+        <v>122715191</v>
       </c>
       <c r="B25" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3657,21 +3598,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3681,13 +3622,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452118</v>
+        <v>452150</v>
       </c>
       <c r="R25" t="n">
-        <v>7029273</v>
+        <v>7029062</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3716,7 +3657,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3726,12 +3667,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3742,21 +3683,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3773,10 +3699,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122717401</v>
+        <v>122716759</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3785,25 +3711,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3822,13 +3748,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452013</v>
+        <v>451898</v>
       </c>
       <c r="R26" t="n">
-        <v>7029064</v>
+        <v>7028975</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3857,7 +3783,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3867,12 +3793,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,41 +3809,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>granar</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720194</v>
+        <v>122717157</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3930,31 +3841,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3963,13 +3870,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452133</v>
+        <v>451983</v>
       </c>
       <c r="R27" t="n">
-        <v>7029299</v>
+        <v>7029027</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3998,7 +3905,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4008,12 +3915,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4028,22 +3935,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122719970</v>
+        <v>122717724</v>
       </c>
       <c r="B28" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4056,26 +3963,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4089,13 +3996,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452133</v>
+        <v>452034</v>
       </c>
       <c r="R28" t="n">
-        <v>7029267</v>
+        <v>7029103</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4124,7 +4031,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4134,12 +4041,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,10 +4073,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719701</v>
+        <v>122715592</v>
       </c>
       <c r="B29" t="n">
-        <v>79751</v>
+        <v>79807</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4182,26 +4089,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4209,19 +4116,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452180</v>
+        <v>452141</v>
       </c>
       <c r="R29" t="n">
-        <v>7029296</v>
+        <v>7028992</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4250,7 +4162,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4260,12 +4172,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4285,17 +4197,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122716687</v>
+        <v>122720150</v>
       </c>
       <c r="B30" t="n">
-        <v>90952</v>
+        <v>77699</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4308,42 +4220,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451933</v>
+        <v>452132</v>
       </c>
       <c r="R30" t="n">
-        <v>7028984</v>
+        <v>7029266</v>
       </c>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4372,7 +4279,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4382,12 +4289,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4398,23 +4305,38 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122720303</v>
+        <v>122714976</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -4449,7 +4371,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4463,13 +4385,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452124</v>
+        <v>452178</v>
       </c>
       <c r="R31" t="n">
-        <v>7029259</v>
+        <v>7029092</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4498,7 +4420,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4508,12 +4430,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4524,41 +4441,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122714960</v>
+        <v>122719668</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>79883</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4567,41 +4469,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452178</v>
+        <v>452187</v>
       </c>
       <c r="R32" t="n">
-        <v>7029093</v>
+        <v>7029250</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4630,7 +4537,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4640,12 +4547,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4656,6 +4563,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4672,10 +4594,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122717254</v>
+        <v>122720084</v>
       </c>
       <c r="B33" t="n">
-        <v>74868</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4688,37 +4610,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451981</v>
+        <v>452101</v>
       </c>
       <c r="R33" t="n">
-        <v>7029020</v>
+        <v>7029256</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4747,7 +4678,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4757,12 +4688,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4773,38 +4704,23 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715921</v>
+        <v>122715391</v>
       </c>
       <c r="B34" t="n">
         <v>79807</v>
@@ -4838,21 +4754,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452116</v>
+        <v>452136</v>
       </c>
       <c r="R34" t="n">
-        <v>7028982</v>
+        <v>7029025</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4884,7 +4795,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4894,12 +4805,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4910,21 +4821,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4941,10 +4837,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715739</v>
+        <v>122715921</v>
       </c>
       <c r="B35" t="n">
-        <v>77699</v>
+        <v>79807</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4953,41 +4849,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452142</v>
+        <v>452116</v>
       </c>
       <c r="R35" t="n">
-        <v>7029004</v>
+        <v>7028982</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5016,7 +4917,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5026,12 +4927,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5042,26 +4943,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122720354</v>
+        <v>122716633</v>
       </c>
       <c r="B36" t="n">
-        <v>74863</v>
+        <v>79876</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5070,41 +4986,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452114</v>
+        <v>451941</v>
       </c>
       <c r="R36" t="n">
-        <v>7029211</v>
+        <v>7028960</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5133,7 +5054,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5143,12 +5064,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5159,26 +5080,41 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122715547</v>
+        <v>122719902</v>
       </c>
       <c r="B37" t="n">
-        <v>79882</v>
+        <v>79848</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5187,41 +5123,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452141</v>
+        <v>452150</v>
       </c>
       <c r="R37" t="n">
-        <v>7028992</v>
+        <v>7029301</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5250,7 +5195,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5260,12 +5205,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5276,26 +5221,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715671</v>
+        <v>122716787</v>
       </c>
       <c r="B38" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5304,40 +5264,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5346,10 +5297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452132</v>
+        <v>451914</v>
       </c>
       <c r="R38" t="n">
-        <v>7028982</v>
+        <v>7028996</v>
       </c>
       <c r="S38" t="n">
         <v>7</v>
@@ -5381,7 +5332,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5391,12 +5342,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5410,17 +5361,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5438,10 +5389,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122717325</v>
+        <v>122717199</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5454,46 +5405,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452006</v>
+        <v>451981</v>
       </c>
       <c r="R39" t="n">
-        <v>7029026</v>
+        <v>7029020</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5522,7 +5464,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5532,12 +5474,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5551,17 +5493,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5579,10 +5521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122717990</v>
+        <v>122715370</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>79302</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5595,26 +5537,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1352</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5622,19 +5564,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452063</v>
+        <v>452135</v>
       </c>
       <c r="R40" t="n">
-        <v>7029079</v>
+        <v>7029012</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5663,7 +5610,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5673,12 +5620,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5705,10 +5652,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122717724</v>
+        <v>122719605</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5721,26 +5668,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5754,13 +5701,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452034</v>
+        <v>452187</v>
       </c>
       <c r="R41" t="n">
-        <v>7029103</v>
+        <v>7029250</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5789,7 +5736,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5799,12 +5746,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5819,22 +5766,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122719930</v>
+        <v>122715838</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5847,43 +5794,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452148</v>
+        <v>452109</v>
       </c>
       <c r="R42" t="n">
-        <v>7029296</v>
+        <v>7029006</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5915,7 +5853,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5925,12 +5863,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5941,6 +5879,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5957,10 +5910,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122715838</v>
+        <v>122717356</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5973,34 +5926,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452109</v>
+        <v>452001</v>
       </c>
       <c r="R43" t="n">
-        <v>7029006</v>
+        <v>7029043</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6032,7 +5994,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6042,12 +6004,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6089,10 +6051,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122719668</v>
+        <v>122718273</v>
       </c>
       <c r="B44" t="n">
-        <v>79883</v>
+        <v>57589</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6105,27 +6067,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6134,10 +6100,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452187</v>
+        <v>452012</v>
       </c>
       <c r="R44" t="n">
-        <v>7029250</v>
+        <v>7029081</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6169,7 +6135,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6179,12 +6145,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6195,21 +6161,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6226,10 +6177,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717893</v>
+        <v>122720266</v>
       </c>
       <c r="B45" t="n">
-        <v>79718</v>
+        <v>77699</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6238,55 +6189,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>389</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452029</v>
+        <v>452125</v>
       </c>
       <c r="R45" t="n">
-        <v>7029076</v>
+        <v>7029254</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6315,7 +6252,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6325,12 +6262,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6341,38 +6278,23 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122717554</v>
+        <v>122717731</v>
       </c>
       <c r="B46" t="n">
         <v>79718</v>
@@ -6407,7 +6329,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6417,7 +6339,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6426,13 +6348,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452007</v>
+        <v>452035</v>
       </c>
       <c r="R46" t="n">
-        <v>7029050</v>
+        <v>7029085</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6461,7 +6383,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6471,12 +6393,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6518,10 +6440,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122715877</v>
+        <v>122719742</v>
       </c>
       <c r="B47" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6530,41 +6452,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452106</v>
+        <v>452167</v>
       </c>
       <c r="R47" t="n">
-        <v>7028977</v>
+        <v>7029292</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6593,7 +6524,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6603,12 +6534,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6619,21 +6550,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6650,10 +6566,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122716396</v>
+        <v>122715104</v>
       </c>
       <c r="B48" t="n">
-        <v>78850</v>
+        <v>91397</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6662,50 +6578,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>283</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451975</v>
+        <v>452162</v>
       </c>
       <c r="R48" t="n">
-        <v>7029033</v>
+        <v>7029063</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6734,7 +6641,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6744,12 +6651,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6776,10 +6683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122715104</v>
+        <v>122716416</v>
       </c>
       <c r="B49" t="n">
-        <v>91397</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6788,41 +6695,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452162</v>
+        <v>451964</v>
       </c>
       <c r="R49" t="n">
-        <v>7029063</v>
+        <v>7029026</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6851,7 +6767,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6861,12 +6777,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6877,6 +6793,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6893,10 +6824,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122715859</v>
+        <v>122719982</v>
       </c>
       <c r="B50" t="n">
-        <v>74863</v>
+        <v>79022</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6905,41 +6836,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6459</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452106</v>
+        <v>452143</v>
       </c>
       <c r="R50" t="n">
-        <v>7028976</v>
+        <v>7029283</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6968,7 +6904,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6978,12 +6914,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6994,23 +6930,38 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122717731</v>
+        <v>122717893</v>
       </c>
       <c r="B51" t="n">
         <v>79718</v>
@@ -7045,7 +6996,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7064,13 +7015,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452035</v>
+        <v>452029</v>
       </c>
       <c r="R51" t="n">
-        <v>7029085</v>
+        <v>7029076</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7099,7 +7050,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7109,12 +7060,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7156,10 +7107,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122717676</v>
+        <v>122715130</v>
       </c>
       <c r="B52" t="n">
-        <v>79718</v>
+        <v>90963</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7168,52 +7119,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>389</v>
+        <v>1205</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452027</v>
+        <v>452148</v>
       </c>
       <c r="R52" t="n">
-        <v>7029091</v>
+        <v>7029055</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7245,7 +7182,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7255,12 +7192,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7271,21 +7208,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7302,10 +7224,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122719770</v>
+        <v>122720261</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7318,46 +7240,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452163</v>
+        <v>452124</v>
       </c>
       <c r="R53" t="n">
-        <v>7029302</v>
+        <v>7029259</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7386,7 +7299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7396,12 +7309,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7412,26 +7325,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720532</v>
+        <v>122720194</v>
       </c>
       <c r="B54" t="n">
-        <v>78850</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7444,26 +7372,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7471,24 +7399,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452156</v>
+        <v>452133</v>
       </c>
       <c r="R54" t="n">
-        <v>7029109</v>
+        <v>7029299</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7517,7 +7440,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7527,12 +7450,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7543,41 +7466,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122719912</v>
+        <v>122719813</v>
       </c>
       <c r="B55" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7586,50 +7494,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452222</v>
+        <v>452159</v>
       </c>
       <c r="R55" t="n">
-        <v>7029287</v>
+        <v>7029305</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7658,7 +7557,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7668,12 +7567,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7684,26 +7583,41 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122719822</v>
+        <v>122719912</v>
       </c>
       <c r="B56" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7712,41 +7626,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452152</v>
+        <v>452222</v>
       </c>
       <c r="R56" t="n">
-        <v>7029283</v>
+        <v>7029287</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7775,7 +7698,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7785,12 +7708,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7817,10 +7740,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122715191</v>
+        <v>122716868</v>
       </c>
       <c r="B57" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7829,41 +7752,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452150</v>
+        <v>451931</v>
       </c>
       <c r="R57" t="n">
-        <v>7029062</v>
+        <v>7029005</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7892,7 +7820,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7902,12 +7830,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7918,6 +7846,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7934,10 +7877,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122716868</v>
+        <v>122717990</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7950,27 +7893,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7979,13 +7926,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451931</v>
+        <v>452063</v>
       </c>
       <c r="R58" t="n">
-        <v>7029005</v>
+        <v>7029079</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8014,7 +7961,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8024,12 +7971,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8040,41 +7987,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122715131</v>
+        <v>122715784</v>
       </c>
       <c r="B59" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8087,37 +8019,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452147</v>
+        <v>452116</v>
       </c>
       <c r="R59" t="n">
-        <v>7029041</v>
+        <v>7029000</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8146,7 +8087,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8156,12 +8097,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8176,19 +8117,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122719742</v>
+        <v>122715337</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -8223,7 +8164,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8237,13 +8178,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452167</v>
+        <v>452138</v>
       </c>
       <c r="R60" t="n">
-        <v>7029292</v>
+        <v>7029066</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8272,7 +8213,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8282,12 +8223,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8298,6 +8239,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8314,10 +8270,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122720261</v>
+        <v>122715754</v>
       </c>
       <c r="B61" t="n">
-        <v>74863</v>
+        <v>79807</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8326,25 +8282,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8354,10 +8310,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452124</v>
+        <v>452130</v>
       </c>
       <c r="R61" t="n">
-        <v>7029259</v>
+        <v>7029002</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8389,7 +8345,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8399,12 +8355,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8415,21 +8371,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8446,10 +8387,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715370</v>
+        <v>122715859</v>
       </c>
       <c r="B62" t="n">
-        <v>79302</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8462,48 +8403,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1352</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452135</v>
+        <v>452106</v>
       </c>
       <c r="R62" t="n">
-        <v>7029012</v>
+        <v>7028976</v>
       </c>
       <c r="S62" t="n">
         <v>8</v>
@@ -8535,7 +8462,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8545,12 +8472,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8577,10 +8504,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122720379</v>
+        <v>122715067</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8589,50 +8516,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452127</v>
+        <v>452163</v>
       </c>
       <c r="R63" t="n">
-        <v>7029209</v>
+        <v>7029067</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8661,7 +8579,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8671,12 +8589,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8687,6 +8605,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8703,10 +8636,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122718273</v>
+        <v>122717325</v>
       </c>
       <c r="B64" t="n">
-        <v>57589</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8715,25 +8648,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -8741,9 +8674,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8752,13 +8685,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452012</v>
+        <v>452006</v>
       </c>
       <c r="R64" t="n">
-        <v>7029081</v>
+        <v>7029026</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8787,7 +8720,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8797,12 +8730,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8813,6 +8746,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8829,10 +8777,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122716787</v>
+        <v>122717632</v>
       </c>
       <c r="B65" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8841,31 +8789,40 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8874,10 +8831,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451914</v>
+        <v>452015</v>
       </c>
       <c r="R65" t="n">
-        <v>7028996</v>
+        <v>7029092</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
@@ -8909,7 +8866,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8919,12 +8876,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8938,17 +8895,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8966,10 +8923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122714976</v>
+        <v>122716262</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8978,30 +8935,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9009,19 +8966,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452178</v>
+        <v>452093</v>
       </c>
       <c r="R66" t="n">
-        <v>7029092</v>
+        <v>7029013</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9050,7 +9012,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9060,7 +9022,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9075,19 +9042,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122716416</v>
+        <v>122717401</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -9136,13 +9103,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451964</v>
+        <v>452013</v>
       </c>
       <c r="R67" t="n">
-        <v>7029026</v>
+        <v>7029064</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9171,7 +9138,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9181,12 +9148,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9200,17 +9167,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9228,10 +9195,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122717834</v>
+        <v>122715120</v>
       </c>
       <c r="B68" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9240,55 +9207,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452029</v>
+        <v>452148</v>
       </c>
       <c r="R68" t="n">
-        <v>7029079</v>
+        <v>7029055</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9317,7 +9270,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9327,12 +9280,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9343,21 +9296,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9374,10 +9312,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122715130</v>
+        <v>122717676</v>
       </c>
       <c r="B69" t="n">
-        <v>90963</v>
+        <v>79718</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9386,38 +9324,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1205</v>
+        <v>389</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452148</v>
+        <v>452027</v>
       </c>
       <c r="R69" t="n">
-        <v>7029055</v>
+        <v>7029091</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9449,7 +9401,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9459,12 +9411,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9475,6 +9427,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9491,10 +9458,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122715337</v>
+        <v>122716396</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>78847</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9507,26 +9474,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9540,13 +9507,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452138</v>
+        <v>451975</v>
       </c>
       <c r="R70" t="n">
-        <v>7029066</v>
+        <v>7029033</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9575,7 +9542,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9585,12 +9552,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9601,21 +9568,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9632,10 +9584,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122715650</v>
+        <v>122717554</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9644,41 +9596,55 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452125</v>
+        <v>452007</v>
       </c>
       <c r="R71" t="n">
-        <v>7028994</v>
+        <v>7029050</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9707,7 +9673,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9717,7 +9683,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9728,26 +9699,41 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122716428</v>
+        <v>122717834</v>
       </c>
       <c r="B72" t="n">
-        <v>74863</v>
+        <v>79718</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9756,41 +9742,55 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>389</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>451979</v>
+        <v>452029</v>
       </c>
       <c r="R72" t="n">
-        <v>7029020</v>
+        <v>7029079</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9845,26 +9845,41 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122719902</v>
+        <v>122720379</v>
       </c>
       <c r="B73" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9877,31 +9892,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9910,10 +9925,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452150</v>
+        <v>452127</v>
       </c>
       <c r="R73" t="n">
-        <v>7029301</v>
+        <v>7029209</v>
       </c>
       <c r="S73" t="n">
         <v>6</v>
@@ -9945,7 +9960,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9955,12 +9970,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9971,21 +9986,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -10002,10 +10002,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122716081</v>
+        <v>122716459</v>
       </c>
       <c r="B74" t="n">
-        <v>78959</v>
+        <v>57478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10014,38 +10014,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>230552</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10053,13 +10050,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452077</v>
+        <v>451969</v>
       </c>
       <c r="R74" t="n">
-        <v>7029012</v>
+        <v>7029008</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10088,7 +10085,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10098,12 +10095,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10112,24 +10109,8 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -10146,7 +10127,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122716459</v>
+        <v>122718456</v>
       </c>
       <c r="B75" t="n">
         <v>57478</v>
@@ -10190,14 +10171,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>451969</v>
+        <v>452038</v>
       </c>
       <c r="R75" t="n">
-        <v>7029008</v>
+        <v>7029084</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10229,7 +10210,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10239,12 +10220,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10536,10 +10517,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122718456</v>
+        <v>122716081</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>78954</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10548,49 +10529,52 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>230552</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>452038</v>
+        <v>452077</v>
       </c>
       <c r="R78" t="n">
-        <v>7029084</v>
+        <v>7029012</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10619,7 +10603,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10629,12 +10613,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10643,8 +10627,24 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715131</v>
+        <v>122715140</v>
       </c>
       <c r="B2" t="n">
-        <v>77699</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452147</v>
+        <v>452148</v>
       </c>
       <c r="R2" t="n">
-        <v>7029041</v>
+        <v>7029055</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715671</v>
+        <v>122715131</v>
       </c>
       <c r="B3" t="n">
-        <v>79718</v>
+        <v>77699</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,55 +813,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>389</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452132</v>
+        <v>452147</v>
       </c>
       <c r="R3" t="n">
-        <v>7028982</v>
+        <v>7029041</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,31 +902,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1060,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720303</v>
+        <v>122715671</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,30 +1052,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1103,19 +1083,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452124</v>
+        <v>452132</v>
       </c>
       <c r="R5" t="n">
-        <v>7029259</v>
+        <v>7028982</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,12 +1139,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,17 +1158,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1201,10 +1186,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719822</v>
+        <v>122720303</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,41 +1198,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452152</v>
+        <v>452124</v>
       </c>
       <c r="R6" t="n">
-        <v>7029283</v>
+        <v>7029259</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,7 +1270,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,12 +1280,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,26 +1296,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715140</v>
+        <v>122719822</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>79751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,50 +1339,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452148</v>
+        <v>452152</v>
       </c>
       <c r="R7" t="n">
-        <v>7029055</v>
+        <v>7029283</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122720150</v>
+        <v>122714976</v>
       </c>
       <c r="B30" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4220,37 +4220,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452132</v>
+        <v>452178</v>
       </c>
       <c r="R30" t="n">
-        <v>7029266</v>
+        <v>7029092</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4279,7 +4288,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4289,12 +4298,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,41 +4309,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122714976</v>
+        <v>122719668</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4348,35 +4337,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4385,13 +4370,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452178</v>
+        <v>452187</v>
       </c>
       <c r="R31" t="n">
-        <v>7029092</v>
+        <v>7029250</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4420,7 +4405,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4430,7 +4415,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4441,26 +4431,41 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122719668</v>
+        <v>122720150</v>
       </c>
       <c r="B32" t="n">
-        <v>79883</v>
+        <v>77699</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4469,46 +4474,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452187</v>
+        <v>452132</v>
       </c>
       <c r="R32" t="n">
-        <v>7029250</v>
+        <v>7029266</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4566,17 +4566,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122715784</v>
+        <v>122715754</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8015,47 +8015,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452116</v>
+        <v>452130</v>
       </c>
       <c r="R59" t="n">
-        <v>7029000</v>
+        <v>7029002</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8087,7 +8078,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8097,12 +8088,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8129,7 +8120,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715337</v>
+        <v>122715784</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -8164,7 +8155,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8178,13 +8169,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452138</v>
+        <v>452116</v>
       </c>
       <c r="R60" t="n">
-        <v>7029066</v>
+        <v>7029000</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8213,7 +8204,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8223,12 +8214,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8239,21 +8230,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8270,10 +8246,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715754</v>
+        <v>122715337</v>
       </c>
       <c r="B61" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8282,41 +8258,50 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452130</v>
+        <v>452138</v>
       </c>
       <c r="R61" t="n">
-        <v>7029002</v>
+        <v>7029066</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8345,7 +8330,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8355,12 +8340,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8371,6 +8356,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715140</v>
+        <v>122715131</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>77699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452148</v>
+        <v>452147</v>
       </c>
       <c r="R2" t="n">
-        <v>7029055</v>
+        <v>7029041</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715131</v>
+        <v>122715671</v>
       </c>
       <c r="B3" t="n">
-        <v>77699</v>
+        <v>79718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,41 +804,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>389</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452147</v>
+        <v>452132</v>
       </c>
       <c r="R3" t="n">
-        <v>7029041</v>
+        <v>7028982</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +907,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1040,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122715671</v>
+        <v>122720303</v>
       </c>
       <c r="B5" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,30 +1072,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,24 +1103,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452132</v>
+        <v>452124</v>
       </c>
       <c r="R5" t="n">
-        <v>7028982</v>
+        <v>7029259</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1154,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,17 +1173,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1186,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122720303</v>
+        <v>122719822</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,50 +1213,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452124</v>
+        <v>452152</v>
       </c>
       <c r="R6" t="n">
-        <v>7029259</v>
+        <v>7029283</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,7 +1276,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1280,12 +1286,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,41 +1302,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122719822</v>
+        <v>122715140</v>
       </c>
       <c r="B7" t="n">
-        <v>79751</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1339,41 +1330,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452152</v>
+        <v>452148</v>
       </c>
       <c r="R7" t="n">
-        <v>7029283</v>
+        <v>7029055</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715191</v>
+        <v>122715592</v>
       </c>
       <c r="B25" t="n">
-        <v>79751</v>
+        <v>79807</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3598,37 +3598,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452150</v>
+        <v>452141</v>
       </c>
       <c r="R25" t="n">
-        <v>7029062</v>
+        <v>7028992</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3657,7 +3671,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3667,12 +3681,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3687,22 +3701,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122716759</v>
+        <v>122717724</v>
       </c>
       <c r="B26" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3711,30 +3725,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3748,13 +3762,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451898</v>
+        <v>452034</v>
       </c>
       <c r="R26" t="n">
-        <v>7028975</v>
+        <v>7029103</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3783,7 +3797,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3793,12 +3807,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3825,10 +3839,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122717157</v>
+        <v>122715191</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3837,46 +3851,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451983</v>
+        <v>452150</v>
       </c>
       <c r="R27" t="n">
-        <v>7029027</v>
+        <v>7029062</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3905,7 +3914,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3915,12 +3924,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3947,10 +3956,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122717724</v>
+        <v>122716759</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3959,30 +3968,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3996,13 +4005,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452034</v>
+        <v>451898</v>
       </c>
       <c r="R28" t="n">
-        <v>7029103</v>
+        <v>7028975</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4031,7 +4040,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4041,12 +4050,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4073,10 +4082,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122715592</v>
+        <v>122717157</v>
       </c>
       <c r="B29" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4085,40 +4094,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med isidier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452141</v>
+        <v>451983</v>
       </c>
       <c r="R29" t="n">
-        <v>7028992</v>
+        <v>7029027</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4192,12 +4192,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122717893</v>
+        <v>122716868</v>
       </c>
       <c r="B51" t="n">
-        <v>79718</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6973,40 +6973,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>389</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7015,13 +7006,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452029</v>
+        <v>451931</v>
       </c>
       <c r="R51" t="n">
-        <v>7029076</v>
+        <v>7029005</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7050,7 +7041,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7060,12 +7051,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7079,17 +7070,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7107,10 +7098,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715130</v>
+        <v>122717893</v>
       </c>
       <c r="B52" t="n">
-        <v>90963</v>
+        <v>79718</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7119,41 +7110,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1205</v>
+        <v>389</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452148</v>
+        <v>452029</v>
       </c>
       <c r="R52" t="n">
-        <v>7029055</v>
+        <v>7029076</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7182,7 +7187,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7192,12 +7197,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7208,6 +7213,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7224,10 +7244,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720261</v>
+        <v>122715130</v>
       </c>
       <c r="B53" t="n">
-        <v>74863</v>
+        <v>90963</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7236,25 +7256,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>1205</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7264,10 +7284,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452124</v>
+        <v>452148</v>
       </c>
       <c r="R53" t="n">
-        <v>7029259</v>
+        <v>7029055</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7299,7 +7319,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7309,12 +7329,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7325,21 +7345,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7356,10 +7361,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720194</v>
+        <v>122720261</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7372,46 +7377,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452133</v>
+        <v>452124</v>
       </c>
       <c r="R54" t="n">
-        <v>7029299</v>
+        <v>7029259</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7440,7 +7436,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7450,12 +7446,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7466,26 +7462,41 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122719813</v>
+        <v>122720194</v>
       </c>
       <c r="B55" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7494,41 +7505,50 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452159</v>
+        <v>452133</v>
       </c>
       <c r="R55" t="n">
-        <v>7029305</v>
+        <v>7029299</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7557,7 +7577,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7567,12 +7587,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7583,41 +7603,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122719912</v>
+        <v>122719813</v>
       </c>
       <c r="B56" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7626,50 +7631,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452222</v>
+        <v>452159</v>
       </c>
       <c r="R56" t="n">
-        <v>7029287</v>
+        <v>7029305</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7698,7 +7694,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7708,12 +7704,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7724,26 +7720,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122716868</v>
+        <v>122717990</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7756,27 +7767,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7785,13 +7800,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451931</v>
+        <v>452063</v>
       </c>
       <c r="R57" t="n">
-        <v>7029005</v>
+        <v>7029079</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7820,7 +7835,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7830,12 +7845,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7846,41 +7861,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122717990</v>
+        <v>122719912</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7893,26 +7893,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7926,13 +7926,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452063</v>
+        <v>452222</v>
       </c>
       <c r="R58" t="n">
-        <v>7029079</v>
+        <v>7029287</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8387,10 +8387,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715859</v>
+        <v>122715067</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8399,25 +8399,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452106</v>
+        <v>452163</v>
       </c>
       <c r="R62" t="n">
-        <v>7028976</v>
+        <v>7029067</v>
       </c>
       <c r="S62" t="n">
         <v>8</v>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8488,26 +8488,41 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122715067</v>
+        <v>122717325</v>
       </c>
       <c r="B63" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8516,38 +8531,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452163</v>
+        <v>452006</v>
       </c>
       <c r="R63" t="n">
-        <v>7029067</v>
+        <v>7029026</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
@@ -8579,7 +8603,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8589,12 +8613,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8636,10 +8660,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122717325</v>
+        <v>122715859</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8652,43 +8676,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452006</v>
+        <v>452106</v>
       </c>
       <c r="R64" t="n">
-        <v>7029026</v>
+        <v>7028976</v>
       </c>
       <c r="S64" t="n">
         <v>8</v>
@@ -8720,7 +8735,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8730,12 +8745,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8746,31 +8761,16 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715131</v>
+        <v>122715859</v>
       </c>
       <c r="B2" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452147</v>
+        <v>452106</v>
       </c>
       <c r="R2" t="n">
-        <v>7029041</v>
+        <v>7028976</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715671</v>
+        <v>122720088</v>
       </c>
       <c r="B3" t="n">
-        <v>79718</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,52 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>389</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452132</v>
+        <v>452118</v>
       </c>
       <c r="R3" t="n">
-        <v>7028982</v>
+        <v>7029273</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
@@ -881,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,17 +896,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122716687</v>
+        <v>122716416</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,27 +940,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,13 +973,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451933</v>
+        <v>451964</v>
       </c>
       <c r="R4" t="n">
-        <v>7028984</v>
+        <v>7029026</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,12 +1018,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,26 +1034,41 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720303</v>
+        <v>122716396</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,26 +1081,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1109,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452124</v>
+        <v>451975</v>
       </c>
       <c r="R5" t="n">
-        <v>7029259</v>
+        <v>7029033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,12 +1159,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,21 +1175,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1201,7 +1191,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719822</v>
+        <v>122719701</v>
       </c>
       <c r="B6" t="n">
         <v>79751</v>
@@ -1234,17 +1224,26 @@
           <t>(Dicks.) Nyl.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452152</v>
+        <v>452180</v>
       </c>
       <c r="R6" t="n">
-        <v>7029283</v>
+        <v>7029296</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1276,7 +1275,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,12 +1285,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,17 +1310,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715140</v>
+        <v>122715191</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>79751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,50 +1329,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452148</v>
+        <v>452150</v>
       </c>
       <c r="R7" t="n">
-        <v>7029055</v>
+        <v>7029062</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1402,7 +1392,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1412,12 +1402,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,10 +1434,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122716428</v>
+        <v>122717356</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1460,37 +1450,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451979</v>
+        <v>452001</v>
       </c>
       <c r="R8" t="n">
-        <v>7029020</v>
+        <v>7029043</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1519,7 +1518,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1529,12 +1528,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,26 +1544,41 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122714960</v>
+        <v>122717157</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1577,37 +1591,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452178</v>
+        <v>451983</v>
       </c>
       <c r="R9" t="n">
-        <v>7029093</v>
+        <v>7029027</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1636,7 +1655,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1646,12 +1665,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1678,10 +1697,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122717254</v>
+        <v>122717990</v>
       </c>
       <c r="B10" t="n">
-        <v>74868</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1694,34 +1713,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451981</v>
+        <v>452063</v>
       </c>
       <c r="R10" t="n">
-        <v>7029020</v>
+        <v>7029079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1753,7 +1781,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1763,12 +1791,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,38 +1807,23 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122715007</v>
+        <v>122715877</v>
       </c>
       <c r="B11" t="n">
         <v>79751</v>
@@ -1850,13 +1863,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452170</v>
+        <v>452106</v>
       </c>
       <c r="R11" t="n">
-        <v>7029085</v>
+        <v>7028977</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1895,12 +1908,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1942,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122715877</v>
+        <v>122720532</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
+        <v>78847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1954,41 +1967,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452106</v>
+        <v>452156</v>
       </c>
       <c r="R12" t="n">
-        <v>7028977</v>
+        <v>7029109</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2017,7 +2044,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2027,12 +2054,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,17 +2073,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2074,10 +2101,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122719970</v>
+        <v>122717554</v>
       </c>
       <c r="B13" t="n">
-        <v>79848</v>
+        <v>79718</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2086,30 +2113,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>389</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2117,19 +2144,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452133</v>
+        <v>452007</v>
       </c>
       <c r="R13" t="n">
-        <v>7029267</v>
+        <v>7029050</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2158,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2168,12 +2200,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2184,26 +2216,41 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122716346</v>
+        <v>122719902</v>
       </c>
       <c r="B14" t="n">
-        <v>74868</v>
+        <v>79848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,37 +2263,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451984</v>
+        <v>452150</v>
       </c>
       <c r="R14" t="n">
-        <v>7029029</v>
+        <v>7029301</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2275,7 +2331,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2285,12 +2341,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2304,17 +2360,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2332,7 +2388,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122719701</v>
+        <v>122719822</v>
       </c>
       <c r="B15" t="n">
         <v>79751</v>
@@ -2365,26 +2421,17 @@
           <t>(Dicks.) Nyl.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452180</v>
+        <v>452152</v>
       </c>
       <c r="R15" t="n">
-        <v>7029296</v>
+        <v>7029283</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2416,7 +2463,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2426,12 +2473,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2451,17 +2498,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122715547</v>
+        <v>122717199</v>
       </c>
       <c r="B16" t="n">
-        <v>79882</v>
+        <v>77699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2470,25 +2517,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2498,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452141</v>
+        <v>451981</v>
       </c>
       <c r="R16" t="n">
-        <v>7028992</v>
+        <v>7029020</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2533,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2543,12 +2590,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2559,26 +2606,41 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715739</v>
+        <v>122716428</v>
       </c>
       <c r="B17" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2591,21 +2653,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2615,13 +2677,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452142</v>
+        <v>451979</v>
       </c>
       <c r="R17" t="n">
-        <v>7029004</v>
+        <v>7029020</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,7 +2712,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2660,7 +2722,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2692,10 +2754,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122720088</v>
+        <v>122717325</v>
       </c>
       <c r="B18" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2704,41 +2766,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452118</v>
+        <v>452006</v>
       </c>
       <c r="R18" t="n">
-        <v>7029273</v>
+        <v>7029026</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,7 +2838,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2777,12 +2848,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2796,17 +2867,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2824,10 +2895,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122715650</v>
+        <v>122715007</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2836,25 +2907,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2864,10 +2935,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452125</v>
+        <v>452170</v>
       </c>
       <c r="R19" t="n">
-        <v>7028994</v>
+        <v>7029085</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2899,7 +2970,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2909,7 +2980,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2920,26 +2996,41 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122720127</v>
+        <v>122719813</v>
       </c>
       <c r="B20" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2948,52 +3039,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452123</v>
+        <v>452159</v>
       </c>
       <c r="R20" t="n">
-        <v>7029202</v>
+        <v>7029305</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3025,7 +3102,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3035,12 +3112,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3051,26 +3128,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720532</v>
+        <v>122714960</v>
       </c>
       <c r="B21" t="n">
-        <v>78847</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3083,51 +3175,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452156</v>
+        <v>452178</v>
       </c>
       <c r="R21" t="n">
-        <v>7029109</v>
+        <v>7029093</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3156,7 +3234,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3166,12 +3244,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3182,21 +3260,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3213,7 +3276,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122719770</v>
+        <v>122719742</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3248,7 +3311,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3262,13 +3325,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452163</v>
+        <v>452167</v>
       </c>
       <c r="R22" t="n">
-        <v>7029302</v>
+        <v>7029292</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3312,7 +3375,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3327,19 +3390,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122719930</v>
+        <v>122715337</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -3388,13 +3451,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452148</v>
+        <v>452138</v>
       </c>
       <c r="R23" t="n">
-        <v>7029296</v>
+        <v>7029066</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3423,7 +3486,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3433,12 +3496,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3449,6 +3512,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3465,10 +3543,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122720354</v>
+        <v>122715547</v>
       </c>
       <c r="B24" t="n">
-        <v>74863</v>
+        <v>79882</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3477,25 +3555,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3505,13 +3583,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452114</v>
+        <v>452141</v>
       </c>
       <c r="R24" t="n">
-        <v>7029211</v>
+        <v>7028992</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3540,7 +3618,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3550,12 +3628,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3582,10 +3660,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715592</v>
+        <v>122717401</v>
       </c>
       <c r="B25" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3594,30 +3672,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3625,24 +3703,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452141</v>
+        <v>452013</v>
       </c>
       <c r="R25" t="n">
-        <v>7028992</v>
+        <v>7029064</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3671,7 +3744,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3681,12 +3754,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3697,26 +3770,41 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>granar</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122717724</v>
+        <v>122715391</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3725,50 +3813,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452034</v>
+        <v>452136</v>
       </c>
       <c r="R26" t="n">
-        <v>7029103</v>
+        <v>7029025</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3797,7 +3876,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3807,12 +3886,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3827,22 +3906,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715191</v>
+        <v>122715838</v>
       </c>
       <c r="B27" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3851,25 +3930,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3879,13 +3958,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452150</v>
+        <v>452109</v>
       </c>
       <c r="R27" t="n">
-        <v>7029062</v>
+        <v>7029006</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3914,7 +3993,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3924,12 +4003,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3940,6 +4019,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3956,10 +4050,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122716759</v>
+        <v>122715739</v>
       </c>
       <c r="B28" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3968,50 +4062,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451898</v>
+        <v>452142</v>
       </c>
       <c r="R28" t="n">
-        <v>7028975</v>
+        <v>7029004</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4040,7 +4125,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4050,12 +4135,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4082,10 +4167,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122717157</v>
+        <v>122715592</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4094,31 +4179,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4127,13 +4221,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451983</v>
+        <v>452141</v>
       </c>
       <c r="R29" t="n">
-        <v>7029027</v>
+        <v>7028992</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4162,7 +4256,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4172,12 +4266,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4192,22 +4286,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122714976</v>
+        <v>122720261</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4220,46 +4314,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452178</v>
+        <v>452124</v>
       </c>
       <c r="R30" t="n">
-        <v>7029092</v>
+        <v>7029259</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4288,7 +4373,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4298,7 +4383,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4309,26 +4399,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122719668</v>
+        <v>122720127</v>
       </c>
       <c r="B31" t="n">
-        <v>79883</v>
+        <v>79848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4337,31 +4442,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4370,10 +4484,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452187</v>
+        <v>452123</v>
       </c>
       <c r="R31" t="n">
-        <v>7029250</v>
+        <v>7029202</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4405,7 +4519,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4415,12 +4529,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4431,41 +4545,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122720150</v>
+        <v>122717632</v>
       </c>
       <c r="B32" t="n">
-        <v>77699</v>
+        <v>79718</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4474,41 +4573,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>389</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452132</v>
+        <v>452015</v>
       </c>
       <c r="R32" t="n">
-        <v>7029266</v>
+        <v>7029092</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4537,7 +4650,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4547,12 +4660,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4566,17 +4679,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4594,10 +4707,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122720084</v>
+        <v>122717676</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>79718</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4606,30 +4719,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>389</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4637,19 +4750,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452101</v>
+        <v>452027</v>
       </c>
       <c r="R33" t="n">
-        <v>7029256</v>
+        <v>7029091</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4678,7 +4796,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4688,12 +4806,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4704,26 +4822,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715391</v>
+        <v>122716346</v>
       </c>
       <c r="B34" t="n">
-        <v>79807</v>
+        <v>74868</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4732,25 +4865,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4760,13 +4893,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452136</v>
+        <v>451984</v>
       </c>
       <c r="R34" t="n">
-        <v>7029025</v>
+        <v>7029029</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4795,7 +4928,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4805,12 +4938,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4821,6 +4954,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4837,10 +4985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715921</v>
+        <v>122720303</v>
       </c>
       <c r="B35" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4849,31 +4997,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med isidier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4882,10 +5034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452116</v>
+        <v>452124</v>
       </c>
       <c r="R35" t="n">
-        <v>7028982</v>
+        <v>7029259</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4917,7 +5069,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4927,12 +5079,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4946,17 +5098,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4974,10 +5126,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122716633</v>
+        <v>122715784</v>
       </c>
       <c r="B36" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4986,31 +5138,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5019,13 +5175,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451941</v>
+        <v>452116</v>
       </c>
       <c r="R36" t="n">
-        <v>7028960</v>
+        <v>7029000</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5054,7 +5210,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5064,12 +5220,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5080,21 +5236,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5111,10 +5252,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122719902</v>
+        <v>122720194</v>
       </c>
       <c r="B37" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5127,31 +5268,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5160,13 +5301,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452150</v>
+        <v>452133</v>
       </c>
       <c r="R37" t="n">
-        <v>7029301</v>
+        <v>7029299</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5195,7 +5336,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5205,12 +5346,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5221,41 +5362,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122716787</v>
+        <v>122717254</v>
       </c>
       <c r="B38" t="n">
-        <v>79807</v>
+        <v>74868</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5264,46 +5390,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>1467</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451914</v>
+        <v>451981</v>
       </c>
       <c r="R38" t="n">
-        <v>7028996</v>
+        <v>7029020</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5332,7 +5453,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5342,12 +5463,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5389,10 +5510,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122717199</v>
+        <v>122717724</v>
       </c>
       <c r="B39" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5405,37 +5526,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451981</v>
+        <v>452034</v>
       </c>
       <c r="R39" t="n">
-        <v>7029020</v>
+        <v>7029103</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5464,7 +5594,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5474,12 +5604,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5490,41 +5620,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122715370</v>
+        <v>122719605</v>
       </c>
       <c r="B40" t="n">
-        <v>79302</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5537,26 +5652,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5564,24 +5679,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452135</v>
+        <v>452187</v>
       </c>
       <c r="R40" t="n">
-        <v>7029012</v>
+        <v>7029250</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5610,7 +5720,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5620,12 +5730,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5640,22 +5750,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122719605</v>
+        <v>122715131</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5668,46 +5778,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452187</v>
+        <v>452147</v>
       </c>
       <c r="R41" t="n">
-        <v>7029250</v>
+        <v>7029041</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5736,7 +5837,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5746,12 +5847,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5766,22 +5867,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122715838</v>
+        <v>122715370</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>79302</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5794,37 +5895,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>1352</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452109</v>
+        <v>452135</v>
       </c>
       <c r="R42" t="n">
-        <v>7029006</v>
+        <v>7029012</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5853,7 +5968,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5863,12 +5978,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5879,38 +5994,23 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122717356</v>
+        <v>122720379</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -5945,7 +6045,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5959,13 +6059,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452001</v>
+        <v>452127</v>
       </c>
       <c r="R43" t="n">
-        <v>7029043</v>
+        <v>7029209</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5994,7 +6094,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6004,12 +6104,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6020,21 +6120,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6051,10 +6136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122718273</v>
+        <v>122719770</v>
       </c>
       <c r="B44" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6063,35 +6148,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6100,13 +6185,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452012</v>
+        <v>452163</v>
       </c>
       <c r="R44" t="n">
-        <v>7029081</v>
+        <v>7029302</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6135,7 +6220,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6145,12 +6230,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6165,22 +6250,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122720266</v>
+        <v>122715104</v>
       </c>
       <c r="B45" t="n">
-        <v>77699</v>
+        <v>91397</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6189,25 +6274,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6217,10 +6302,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452125</v>
+        <v>452162</v>
       </c>
       <c r="R45" t="n">
-        <v>7029254</v>
+        <v>7029063</v>
       </c>
       <c r="S45" t="n">
         <v>7</v>
@@ -6252,7 +6337,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6262,12 +6347,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6282,19 +6367,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122717731</v>
+        <v>122717893</v>
       </c>
       <c r="B46" t="n">
         <v>79718</v>
@@ -6329,7 +6414,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6348,13 +6433,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452035</v>
+        <v>452029</v>
       </c>
       <c r="R46" t="n">
-        <v>7029085</v>
+        <v>7029076</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6383,7 +6468,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6393,12 +6478,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6440,10 +6525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122719742</v>
+        <v>122719668</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6452,35 +6537,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6489,10 +6570,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452167</v>
+        <v>452187</v>
       </c>
       <c r="R47" t="n">
-        <v>7029292</v>
+        <v>7029250</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6524,7 +6605,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6534,12 +6615,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6550,6 +6631,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6566,10 +6662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122715104</v>
+        <v>122714976</v>
       </c>
       <c r="B48" t="n">
-        <v>91397</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6578,41 +6674,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452162</v>
+        <v>452178</v>
       </c>
       <c r="R48" t="n">
-        <v>7029063</v>
+        <v>7029092</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6641,7 +6746,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6651,12 +6756,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6671,22 +6771,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122716416</v>
+        <v>122720150</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6699,46 +6799,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451964</v>
+        <v>452132</v>
       </c>
       <c r="R49" t="n">
-        <v>7029026</v>
+        <v>7029266</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6767,7 +6858,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6777,12 +6868,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6824,10 +6915,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122719982</v>
+        <v>122720266</v>
       </c>
       <c r="B50" t="n">
-        <v>79022</v>
+        <v>77699</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6836,46 +6927,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452143</v>
+        <v>452125</v>
       </c>
       <c r="R50" t="n">
-        <v>7029283</v>
+        <v>7029254</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6904,7 +6990,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6914,12 +7000,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6930,41 +7016,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122716868</v>
+        <v>122716787</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6973,31 +7044,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7006,13 +7077,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451931</v>
+        <v>451914</v>
       </c>
       <c r="R51" t="n">
-        <v>7029005</v>
+        <v>7028996</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7041,7 +7112,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7051,12 +7122,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7098,10 +7169,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122717893</v>
+        <v>122715921</v>
       </c>
       <c r="B52" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7110,40 +7181,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7152,13 +7214,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452029</v>
+        <v>452116</v>
       </c>
       <c r="R52" t="n">
-        <v>7029076</v>
+        <v>7028982</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7187,7 +7249,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7197,12 +7259,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7244,10 +7306,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715130</v>
+        <v>122715671</v>
       </c>
       <c r="B53" t="n">
-        <v>90963</v>
+        <v>79718</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7256,41 +7318,55 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1205</v>
+        <v>389</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452148</v>
+        <v>452132</v>
       </c>
       <c r="R53" t="n">
-        <v>7029055</v>
+        <v>7028982</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7319,7 +7395,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7329,12 +7405,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7345,6 +7421,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7361,10 +7452,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720261</v>
+        <v>122716262</v>
       </c>
       <c r="B54" t="n">
-        <v>74863</v>
+        <v>79718</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7373,38 +7464,52 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>389</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452124</v>
+        <v>452093</v>
       </c>
       <c r="R54" t="n">
-        <v>7029259</v>
+        <v>7029013</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7436,7 +7541,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7446,12 +7551,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7462,21 +7567,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7493,10 +7583,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122720194</v>
+        <v>122717834</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7505,30 +7595,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7536,19 +7626,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452133</v>
+        <v>452029</v>
       </c>
       <c r="R55" t="n">
-        <v>7029299</v>
+        <v>7029079</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7577,7 +7672,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7587,12 +7682,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7603,26 +7698,41 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122719813</v>
+        <v>122718273</v>
       </c>
       <c r="B56" t="n">
-        <v>79876</v>
+        <v>57589</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7635,34 +7745,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452159</v>
+        <v>452012</v>
       </c>
       <c r="R56" t="n">
-        <v>7029305</v>
+        <v>7029081</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7694,7 +7813,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7704,12 +7823,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7720,21 +7839,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7751,10 +7855,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122717990</v>
+        <v>122719970</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7767,26 +7871,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7800,13 +7904,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452063</v>
+        <v>452133</v>
       </c>
       <c r="R57" t="n">
-        <v>7029079</v>
+        <v>7029267</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7835,7 +7939,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7845,12 +7949,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7877,10 +7981,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122719912</v>
+        <v>122717731</v>
       </c>
       <c r="B58" t="n">
-        <v>79848</v>
+        <v>79718</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7889,30 +7993,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>389</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7920,19 +8024,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452222</v>
+        <v>452035</v>
       </c>
       <c r="R58" t="n">
-        <v>7029287</v>
+        <v>7029085</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7961,7 +8070,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7971,12 +8080,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7987,26 +8096,41 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122715754</v>
+        <v>122715650</v>
       </c>
       <c r="B59" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8015,25 +8139,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8043,10 +8167,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452130</v>
+        <v>452125</v>
       </c>
       <c r="R59" t="n">
-        <v>7029002</v>
+        <v>7028994</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8078,7 +8202,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8088,12 +8212,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8108,22 +8227,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715784</v>
+        <v>122715754</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8132,47 +8251,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452116</v>
+        <v>452130</v>
       </c>
       <c r="R60" t="n">
-        <v>7029000</v>
+        <v>7029002</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8204,7 +8314,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8214,12 +8324,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8246,10 +8356,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715337</v>
+        <v>122720084</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8262,26 +8372,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8295,13 +8405,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452138</v>
+        <v>452101</v>
       </c>
       <c r="R61" t="n">
-        <v>7029066</v>
+        <v>7029256</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8330,7 +8440,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8340,12 +8450,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8356,41 +8466,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715067</v>
+        <v>122715130</v>
       </c>
       <c r="B62" t="n">
-        <v>79751</v>
+        <v>90963</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8403,21 +8498,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8427,13 +8522,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452163</v>
+        <v>452148</v>
       </c>
       <c r="R62" t="n">
-        <v>7029067</v>
+        <v>7029055</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8462,7 +8557,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8472,12 +8567,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8488,21 +8583,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8519,10 +8599,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122717325</v>
+        <v>122716687</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8535,31 +8615,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8568,13 +8644,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452006</v>
+        <v>451933</v>
       </c>
       <c r="R63" t="n">
-        <v>7029026</v>
+        <v>7028984</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8603,7 +8679,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8613,12 +8689,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8629,38 +8705,23 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122715859</v>
+        <v>122720354</v>
       </c>
       <c r="B64" t="n">
         <v>74863</v>
@@ -8700,13 +8761,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452106</v>
+        <v>452114</v>
       </c>
       <c r="R64" t="n">
-        <v>7028976</v>
+        <v>7029211</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8735,7 +8796,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8745,7 +8806,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8777,10 +8838,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122717632</v>
+        <v>122716868</v>
       </c>
       <c r="B65" t="n">
-        <v>79718</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8789,40 +8850,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>389</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8831,13 +8883,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452015</v>
+        <v>451931</v>
       </c>
       <c r="R65" t="n">
-        <v>7029092</v>
+        <v>7029005</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8866,7 +8918,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8876,12 +8928,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8895,17 +8947,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8923,10 +8975,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122716262</v>
+        <v>122719912</v>
       </c>
       <c r="B66" t="n">
-        <v>79718</v>
+        <v>79848</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8935,30 +8987,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>389</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8966,24 +9018,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452093</v>
+        <v>452222</v>
       </c>
       <c r="R66" t="n">
-        <v>7029013</v>
+        <v>7029287</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9012,7 +9059,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9022,12 +9069,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9042,22 +9089,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122717401</v>
+        <v>122716759</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9066,25 +9113,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -9103,13 +9150,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452013</v>
+        <v>451898</v>
       </c>
       <c r="R67" t="n">
-        <v>7029064</v>
+        <v>7028975</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9138,7 +9185,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9148,12 +9195,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9164,41 +9211,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>granar</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122715120</v>
+        <v>122716633</v>
       </c>
       <c r="B68" t="n">
-        <v>79807</v>
+        <v>79876</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9211,34 +9243,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452148</v>
+        <v>451941</v>
       </c>
       <c r="R68" t="n">
-        <v>7029055</v>
+        <v>7028960</v>
       </c>
       <c r="S68" t="n">
         <v>8</v>
@@ -9270,7 +9307,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9280,12 +9317,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9296,6 +9333,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9312,10 +9364,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122717676</v>
+        <v>122719930</v>
       </c>
       <c r="B69" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9324,30 +9376,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9355,21 +9407,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452027</v>
+        <v>452148</v>
       </c>
       <c r="R69" t="n">
-        <v>7029091</v>
+        <v>7029296</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9401,7 +9448,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9411,12 +9458,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9427,21 +9474,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9458,10 +9490,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122716396</v>
+        <v>122715067</v>
       </c>
       <c r="B70" t="n">
-        <v>78847</v>
+        <v>79751</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9470,50 +9502,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>283</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451975</v>
+        <v>452163</v>
       </c>
       <c r="R70" t="n">
-        <v>7029033</v>
+        <v>7029067</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9542,7 +9565,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9552,12 +9575,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9568,6 +9591,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9584,10 +9622,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122717554</v>
+        <v>122719982</v>
       </c>
       <c r="B71" t="n">
-        <v>79718</v>
+        <v>79022</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9596,40 +9634,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>389</v>
+        <v>6459</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9638,13 +9667,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452007</v>
+        <v>452143</v>
       </c>
       <c r="R71" t="n">
-        <v>7029050</v>
+        <v>7029283</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9673,7 +9702,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9683,12 +9712,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9702,17 +9731,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9730,10 +9759,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122717834</v>
+        <v>122715140</v>
       </c>
       <c r="B72" t="n">
-        <v>79718</v>
+        <v>57631</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9742,40 +9771,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>389</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9784,13 +9808,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452029</v>
+        <v>452148</v>
       </c>
       <c r="R72" t="n">
-        <v>7029079</v>
+        <v>7029055</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9819,7 +9843,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9829,12 +9853,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9845,21 +9869,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9876,10 +9885,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122720379</v>
+        <v>122715120</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9888,50 +9897,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452127</v>
+        <v>452148</v>
       </c>
       <c r="R73" t="n">
-        <v>7029209</v>
+        <v>7029055</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9970,12 +9970,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10002,7 +10002,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122716459</v>
+        <v>122716494</v>
       </c>
       <c r="B74" t="n">
         <v>57478</v>
@@ -10050,10 +10050,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451969</v>
+        <v>451971</v>
       </c>
       <c r="R74" t="n">
-        <v>7029008</v>
+        <v>7029000</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10111,6 +10111,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -10127,7 +10142,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122718456</v>
+        <v>122717285</v>
       </c>
       <c r="B75" t="n">
         <v>57478</v>
@@ -10171,14 +10186,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
+          <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452038</v>
+        <v>452000</v>
       </c>
       <c r="R75" t="n">
-        <v>7029084</v>
+        <v>7029026</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10210,7 +10225,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10220,12 +10235,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10252,7 +10267,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122717285</v>
+        <v>122718456</v>
       </c>
       <c r="B76" t="n">
         <v>57478</v>
@@ -10296,14 +10311,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hallägden, Hallägden, Jmt</t>
+          <t>Hallägden, Alsen, Hallägden, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452000</v>
+        <v>452038</v>
       </c>
       <c r="R76" t="n">
-        <v>7029026</v>
+        <v>7029084</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10335,7 +10350,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10345,12 +10360,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10377,10 +10392,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122716494</v>
+        <v>122716081</v>
       </c>
       <c r="B77" t="n">
-        <v>57478</v>
+        <v>78954</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10389,35 +10404,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>230552</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10425,13 +10443,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451971</v>
+        <v>452077</v>
       </c>
       <c r="R77" t="n">
-        <v>7029000</v>
+        <v>7029012</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10460,7 +10478,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10470,12 +10488,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10484,6 +10502,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10517,10 +10536,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122716081</v>
+        <v>122716459</v>
       </c>
       <c r="B78" t="n">
-        <v>78954</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10529,38 +10548,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>230552</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10568,13 +10584,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>452077</v>
+        <v>451969</v>
       </c>
       <c r="R78" t="n">
-        <v>7029012</v>
+        <v>7029008</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10603,7 +10619,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10613,12 +10629,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10627,24 +10643,8 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715859</v>
+        <v>122716633</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>79876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452106</v>
+        <v>451941</v>
       </c>
       <c r="R2" t="n">
-        <v>7028976</v>
+        <v>7028960</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +781,41 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122720088</v>
+        <v>122719982</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>79022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +828,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452118</v>
+        <v>452143</v>
       </c>
       <c r="R3" t="n">
-        <v>7029273</v>
+        <v>7029283</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122716416</v>
+        <v>122715067</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,50 +961,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451964</v>
+        <v>452163</v>
       </c>
       <c r="R4" t="n">
-        <v>7029026</v>
+        <v>7029067</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,17 +1053,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1065,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122716396</v>
+        <v>122717157</v>
       </c>
       <c r="B5" t="n">
-        <v>78847</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,31 +1097,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1126,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451975</v>
+        <v>451983</v>
       </c>
       <c r="R5" t="n">
-        <v>7029033</v>
+        <v>7029027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,12 +1171,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719701</v>
+        <v>122715838</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,50 +1215,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452180</v>
+        <v>452109</v>
       </c>
       <c r="R6" t="n">
-        <v>7029296</v>
+        <v>7029006</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1275,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1285,12 +1288,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,26 +1304,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715191</v>
+        <v>122720150</v>
       </c>
       <c r="B7" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1329,25 +1347,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1357,13 +1375,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452150</v>
+        <v>452132</v>
       </c>
       <c r="R7" t="n">
-        <v>7029062</v>
+        <v>7029266</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1392,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,12 +1420,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,6 +1436,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122717356</v>
+        <v>122716346</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1450,46 +1483,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452001</v>
+        <v>451984</v>
       </c>
       <c r="R8" t="n">
-        <v>7029043</v>
+        <v>7029029</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1518,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1528,12 +1552,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1575,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122717157</v>
+        <v>122720303</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1591,27 +1615,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1620,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451983</v>
+        <v>452124</v>
       </c>
       <c r="R9" t="n">
-        <v>7029027</v>
+        <v>7029259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,7 +1683,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1665,12 +1693,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,6 +1709,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1697,10 +1740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122717990</v>
+        <v>122715140</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1713,31 +1756,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1746,13 +1789,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452063</v>
+        <v>452148</v>
       </c>
       <c r="R10" t="n">
-        <v>7029079</v>
+        <v>7029055</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1781,7 +1824,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1791,12 +1834,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran bredvid asp</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,22 +1854,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122715877</v>
+        <v>122719912</v>
       </c>
       <c r="B11" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1835,41 +1878,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452106</v>
+        <v>452222</v>
       </c>
       <c r="R11" t="n">
-        <v>7028977</v>
+        <v>7029287</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1950,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,12 +1960,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
+          <t>På gran bredvid sälj</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,41 +1976,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720532</v>
+        <v>122717401</v>
       </c>
       <c r="B12" t="n">
-        <v>78847</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,26 +2008,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1998,24 +2035,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452156</v>
+        <v>452013</v>
       </c>
       <c r="R12" t="n">
-        <v>7029109</v>
+        <v>7029064</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2044,7 +2076,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2054,12 +2086,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2073,17 +2105,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2101,10 +2133,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122717554</v>
+        <v>122715754</v>
       </c>
       <c r="B13" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2113,55 +2145,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452007</v>
+        <v>452130</v>
       </c>
       <c r="R13" t="n">
-        <v>7029050</v>
+        <v>7029002</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2208,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,12 +2218,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2216,21 +2234,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2247,10 +2250,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122719902</v>
+        <v>122715130</v>
       </c>
       <c r="B14" t="n">
-        <v>79848</v>
+        <v>90963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2259,50 +2262,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452150</v>
+        <v>452148</v>
       </c>
       <c r="R14" t="n">
-        <v>7029301</v>
+        <v>7029055</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2341,12 +2335,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2357,21 +2351,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2388,10 +2367,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122719822</v>
+        <v>122717834</v>
       </c>
       <c r="B15" t="n">
-        <v>79751</v>
+        <v>79718</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2400,41 +2379,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>389</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452152</v>
+        <v>452029</v>
       </c>
       <c r="R15" t="n">
-        <v>7029283</v>
+        <v>7029079</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2463,7 +2456,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2473,12 +2466,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På sälj</t>
+          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,26 +2482,41 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122717199</v>
+        <v>122720084</v>
       </c>
       <c r="B16" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,37 +2529,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451981</v>
+        <v>452101</v>
       </c>
       <c r="R16" t="n">
-        <v>7029020</v>
+        <v>7029256</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2597,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,12 +2607,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2606,41 +2623,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122716428</v>
+        <v>122717990</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2653,37 +2655,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451979</v>
+        <v>452063</v>
       </c>
       <c r="R17" t="n">
-        <v>7029020</v>
+        <v>7029079</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2712,7 +2723,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2722,12 +2733,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran bredvid asp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2754,7 +2765,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122717325</v>
+        <v>122717724</v>
       </c>
       <c r="B18" t="n">
         <v>79847</v>
@@ -2803,13 +2814,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452006</v>
+        <v>452034</v>
       </c>
       <c r="R18" t="n">
-        <v>7029026</v>
+        <v>7029103</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2838,7 +2849,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2848,12 +2859,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2864,41 +2875,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122715007</v>
+        <v>122714976</v>
       </c>
       <c r="B19" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2907,41 +2903,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452170</v>
+        <v>452178</v>
       </c>
       <c r="R19" t="n">
-        <v>7029085</v>
+        <v>7029092</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2970,7 +2975,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2980,12 +2985,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2996,41 +2996,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122719813</v>
+        <v>122715859</v>
       </c>
       <c r="B20" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3039,25 +3024,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3067,13 +3052,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452159</v>
+        <v>452106</v>
       </c>
       <c r="R20" t="n">
-        <v>7029305</v>
+        <v>7028976</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3102,7 +3087,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3112,12 +3097,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På sälg i ädre granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3128,41 +3113,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122714960</v>
+        <v>122719701</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3171,38 +3141,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452178</v>
+        <v>452180</v>
       </c>
       <c r="R21" t="n">
-        <v>7029093</v>
+        <v>7029296</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3234,7 +3213,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3244,12 +3223,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3264,19 +3243,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122719742</v>
+        <v>122720379</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3311,7 +3290,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3325,13 +3304,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452167</v>
+        <v>452127</v>
       </c>
       <c r="R22" t="n">
-        <v>7029292</v>
+        <v>7029209</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3360,7 +3339,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3370,12 +3349,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3402,7 +3381,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122715337</v>
+        <v>122715784</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -3437,7 +3416,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3451,13 +3430,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452138</v>
+        <v>452116</v>
       </c>
       <c r="R23" t="n">
-        <v>7029066</v>
+        <v>7029000</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3486,7 +3465,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3496,12 +3475,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3512,21 +3491,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3543,10 +3507,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715547</v>
+        <v>122715921</v>
       </c>
       <c r="B24" t="n">
-        <v>79882</v>
+        <v>79807</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3559,37 +3523,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452141</v>
+        <v>452116</v>
       </c>
       <c r="R24" t="n">
-        <v>7028992</v>
+        <v>7028982</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3618,7 +3587,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3628,12 +3597,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3644,26 +3613,41 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122717401</v>
+        <v>122720261</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3676,46 +3660,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452013</v>
+        <v>452124</v>
       </c>
       <c r="R25" t="n">
-        <v>7029064</v>
+        <v>7029259</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3744,7 +3719,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3754,12 +3729,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, längsta bål 50 cm lång</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3773,17 +3748,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3801,10 +3776,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122715391</v>
+        <v>122714960</v>
       </c>
       <c r="B26" t="n">
-        <v>79807</v>
+        <v>74863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3813,25 +3788,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3841,13 +3816,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452136</v>
+        <v>452178</v>
       </c>
       <c r="R26" t="n">
-        <v>7029025</v>
+        <v>7029093</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3876,7 +3851,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3886,12 +3861,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3918,10 +3893,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715838</v>
+        <v>122715104</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>91397</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3930,25 +3905,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3958,13 +3933,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452109</v>
+        <v>452162</v>
       </c>
       <c r="R27" t="n">
-        <v>7029006</v>
+        <v>7029063</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3993,7 +3968,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4003,12 +3978,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4019,21 +3994,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4050,10 +4010,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122715739</v>
+        <v>122715671</v>
       </c>
       <c r="B28" t="n">
-        <v>77699</v>
+        <v>79718</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4062,41 +4022,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>389</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452142</v>
+        <v>452132</v>
       </c>
       <c r="R28" t="n">
-        <v>7029004</v>
+        <v>7028982</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4125,7 +4099,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4135,12 +4109,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4151,26 +4125,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122715592</v>
+        <v>122716262</v>
       </c>
       <c r="B29" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4179,30 +4168,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4212,7 +4201,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4221,13 +4210,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452141</v>
+        <v>452093</v>
       </c>
       <c r="R29" t="n">
-        <v>7028992</v>
+        <v>7029013</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4256,7 +4245,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4266,12 +4255,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4286,22 +4275,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122720261</v>
+        <v>122717893</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>79718</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4310,41 +4299,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>389</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452124</v>
+        <v>452029</v>
       </c>
       <c r="R30" t="n">
-        <v>7029259</v>
+        <v>7029076</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4373,7 +4376,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4383,12 +4386,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4402,17 +4405,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4430,10 +4433,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122720127</v>
+        <v>122717356</v>
       </c>
       <c r="B31" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4446,26 +4449,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4473,21 +4476,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452123</v>
+        <v>452001</v>
       </c>
       <c r="R31" t="n">
-        <v>7029202</v>
+        <v>7029043</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4519,7 +4517,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4529,12 +4527,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Rikligt på gammal gran (22 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4545,26 +4543,41 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122717632</v>
+        <v>122716416</v>
       </c>
       <c r="B32" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4573,30 +4586,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4604,24 +4617,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452015</v>
+        <v>451964</v>
       </c>
       <c r="R32" t="n">
-        <v>7029092</v>
+        <v>7029026</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4650,7 +4658,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4660,12 +4668,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
+          <t>På gammal levande gran (13 cm dbh, ca 140 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4679,17 +4687,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4707,10 +4715,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122717676</v>
+        <v>122720194</v>
       </c>
       <c r="B33" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4719,30 +4727,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4750,24 +4758,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452027</v>
+        <v>452133</v>
       </c>
       <c r="R33" t="n">
-        <v>7029091</v>
+        <v>7029299</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4796,7 +4799,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4806,12 +4809,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
+          <t>På gammal gran/granar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4822,41 +4825,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122716346</v>
+        <v>122715592</v>
       </c>
       <c r="B34" t="n">
-        <v>74868</v>
+        <v>79807</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4865,41 +4853,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451984</v>
+        <v>452141</v>
       </c>
       <c r="R34" t="n">
-        <v>7029029</v>
+        <v>7028992</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4928,7 +4930,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4938,12 +4940,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4954,41 +4956,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720303</v>
+        <v>122719970</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5001,26 +4988,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5034,13 +5021,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452124</v>
+        <v>452133</v>
       </c>
       <c r="R35" t="n">
-        <v>7029259</v>
+        <v>7029267</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5069,7 +5056,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5079,12 +5066,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5095,41 +5082,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122715784</v>
+        <v>122720088</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5138,50 +5110,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452116</v>
+        <v>452118</v>
       </c>
       <c r="R36" t="n">
-        <v>7029000</v>
+        <v>7029273</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5210,7 +5173,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5220,12 +5183,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i öppet läge i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,6 +5199,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5252,10 +5230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720194</v>
+        <v>122715007</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5264,50 +5242,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452133</v>
+        <v>452170</v>
       </c>
       <c r="R37" t="n">
-        <v>7029299</v>
+        <v>7029085</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5336,7 +5305,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5346,12 +5315,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran/granar</t>
+          <t>På bark på stam av levande gammal asp (35 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5362,26 +5331,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122717254</v>
+        <v>122715120</v>
       </c>
       <c r="B38" t="n">
-        <v>74868</v>
+        <v>79807</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5390,25 +5374,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1467</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5418,13 +5402,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451981</v>
+        <v>452148</v>
       </c>
       <c r="R38" t="n">
-        <v>7029020</v>
+        <v>7029055</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5453,7 +5437,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5463,12 +5447,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5479,21 +5463,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5510,10 +5479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122717724</v>
+        <v>122716687</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5526,31 +5495,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5559,13 +5524,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452034</v>
+        <v>451933</v>
       </c>
       <c r="R39" t="n">
-        <v>7029103</v>
+        <v>7028984</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5594,7 +5559,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5604,12 +5569,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5636,10 +5601,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122719605</v>
+        <v>122717632</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79718</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5648,25 +5613,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5679,19 +5644,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452187</v>
+        <v>452015</v>
       </c>
       <c r="R40" t="n">
-        <v>7029250</v>
+        <v>7029092</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5720,7 +5690,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5730,12 +5700,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På bark på stam av levande gammal asp (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5746,6 +5716,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5762,10 +5747,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122715131</v>
+        <v>122717731</v>
       </c>
       <c r="B41" t="n">
-        <v>77699</v>
+        <v>79718</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5774,41 +5759,55 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>389</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452147</v>
+        <v>452035</v>
       </c>
       <c r="R41" t="n">
-        <v>7029041</v>
+        <v>7029085</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5837,7 +5836,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5847,12 +5846,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5863,26 +5862,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122715370</v>
+        <v>122715337</v>
       </c>
       <c r="B42" t="n">
-        <v>79302</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5895,26 +5909,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5922,24 +5936,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452135</v>
+        <v>452138</v>
       </c>
       <c r="R42" t="n">
-        <v>7029012</v>
+        <v>7029066</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5968,7 +5977,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5978,12 +5987,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 5 på nedfallna grenar</t>
+          <t>Rikligt, max 30 cm långa, minst 25 exemplar på gammal gran (14 cm dbh, ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5994,26 +6003,41 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122720379</v>
+        <v>122719668</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6022,35 +6046,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6059,13 +6079,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452127</v>
+        <v>452187</v>
       </c>
       <c r="R43" t="n">
-        <v>7029209</v>
+        <v>7029250</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6094,7 +6114,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6104,12 +6124,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6120,6 +6140,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6136,10 +6171,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122719770</v>
+        <v>122719822</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6148,47 +6183,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452163</v>
+        <v>452152</v>
       </c>
       <c r="R44" t="n">
-        <v>7029302</v>
+        <v>7029283</v>
       </c>
       <c r="S44" t="n">
         <v>8</v>
@@ -6220,7 +6246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6230,12 +6256,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälj</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6255,17 +6281,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122715104</v>
+        <v>122717199</v>
       </c>
       <c r="B45" t="n">
-        <v>91397</v>
+        <v>77699</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6274,25 +6300,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6302,13 +6328,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452162</v>
+        <v>451981</v>
       </c>
       <c r="R45" t="n">
-        <v>7029063</v>
+        <v>7029020</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6337,7 +6363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6347,12 +6373,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6363,6 +6389,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6379,10 +6420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122717893</v>
+        <v>122715191</v>
       </c>
       <c r="B46" t="n">
-        <v>79718</v>
+        <v>79751</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6391,52 +6432,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>389</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452029</v>
+        <v>452150</v>
       </c>
       <c r="R46" t="n">
-        <v>7029076</v>
+        <v>7029062</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
@@ -6468,7 +6495,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6478,12 +6505,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6494,21 +6521,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6525,10 +6537,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122719668</v>
+        <v>122718273</v>
       </c>
       <c r="B47" t="n">
-        <v>79883</v>
+        <v>57589</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6541,27 +6553,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6570,10 +6586,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452187</v>
+        <v>452012</v>
       </c>
       <c r="R47" t="n">
-        <v>7029250</v>
+        <v>7029081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6605,7 +6621,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6615,12 +6631,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt på ovansidan av lutande sälg (35 cm dbh) i äldre asprik granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6631,21 +6647,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6662,10 +6663,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122714976</v>
+        <v>122719813</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6674,50 +6675,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452178</v>
+        <v>452159</v>
       </c>
       <c r="R48" t="n">
-        <v>7029092</v>
+        <v>7029305</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6746,7 +6738,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6756,7 +6748,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På sälg i ädre granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6767,26 +6764,41 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122720150</v>
+        <v>122717325</v>
       </c>
       <c r="B49" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6799,34 +6811,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452132</v>
+        <v>452006</v>
       </c>
       <c r="R49" t="n">
-        <v>7029266</v>
+        <v>7029026</v>
       </c>
       <c r="S49" t="n">
         <v>8</v>
@@ -6858,7 +6879,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6868,12 +6889,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>1 bål, 7x5 cm på bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6887,17 +6908,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6915,10 +6936,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122720266</v>
+        <v>122720354</v>
       </c>
       <c r="B50" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6931,21 +6952,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6955,13 +6976,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452125</v>
+        <v>452114</v>
       </c>
       <c r="R50" t="n">
-        <v>7029254</v>
+        <v>7029211</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6990,7 +7011,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7000,12 +7021,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7032,10 +7053,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122716787</v>
+        <v>122715370</v>
       </c>
       <c r="B51" t="n">
-        <v>79807</v>
+        <v>79302</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7044,31 +7065,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229497</v>
+        <v>1352</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7077,13 +7107,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451914</v>
+        <v>452135</v>
       </c>
       <c r="R51" t="n">
-        <v>7028996</v>
+        <v>7029012</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7112,7 +7142,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7122,12 +7152,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
+          <t>Minst 5 på nedfallna grenar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7138,41 +7168,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715921</v>
+        <v>122717676</v>
       </c>
       <c r="B52" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7181,31 +7196,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7214,10 +7238,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452116</v>
+        <v>452027</v>
       </c>
       <c r="R52" t="n">
-        <v>7028982</v>
+        <v>7029091</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7249,7 +7273,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7259,12 +7283,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (41 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7306,10 +7330,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715671</v>
+        <v>122716396</v>
       </c>
       <c r="B53" t="n">
-        <v>79718</v>
+        <v>78847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7318,30 +7342,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>389</v>
+        <v>283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7349,24 +7373,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452132</v>
+        <v>451975</v>
       </c>
       <c r="R53" t="n">
-        <v>7028982</v>
+        <v>7029033</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7395,7 +7414,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7405,12 +7424,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt (över 200 bålar) från 0,5 m till ca 6 m upp på gammal levande asp (37 cm dbh) i gammal granskog</t>
+          <t>På tunn levande gren på gammal levande gran (2 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7421,21 +7440,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7452,10 +7456,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122716262</v>
+        <v>122719742</v>
       </c>
       <c r="B54" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7464,30 +7468,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7495,21 +7499,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452093</v>
+        <v>452167</v>
       </c>
       <c r="R54" t="n">
-        <v>7029013</v>
+        <v>7029292</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7541,7 +7540,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7551,12 +7550,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På bark på stam, mest kring 4 meters höjd, av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>1 bål 30 cm lång på äldre gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7583,10 +7582,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122717834</v>
+        <v>122715650</v>
       </c>
       <c r="B55" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7595,52 +7594,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452029</v>
+        <v>452125</v>
       </c>
       <c r="R55" t="n">
-        <v>7029079</v>
+        <v>7028994</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7672,7 +7657,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7682,12 +7667,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mycket rikligt från 0,5 till 5 meters höjd på gammal levande asp (39 cm dbh) i gammal granskog</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7698,41 +7678,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122718273</v>
+        <v>122717254</v>
       </c>
       <c r="B56" t="n">
-        <v>57589</v>
+        <v>74868</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7741,47 +7706,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103031</v>
+        <v>1467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452012</v>
+        <v>451981</v>
       </c>
       <c r="R56" t="n">
-        <v>7029081</v>
+        <v>7029020</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7813,7 +7769,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7823,12 +7779,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7839,6 +7795,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7855,10 +7826,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122719970</v>
+        <v>122716759</v>
       </c>
       <c r="B57" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7867,30 +7838,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7904,13 +7875,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452133</v>
+        <v>451898</v>
       </c>
       <c r="R57" t="n">
-        <v>7029267</v>
+        <v>7028975</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7939,7 +7910,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7949,12 +7920,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran intill under jätteasp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7981,10 +7952,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122717731</v>
+        <v>122719605</v>
       </c>
       <c r="B58" t="n">
-        <v>79718</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7993,30 +7964,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8024,24 +7995,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452035</v>
+        <v>452187</v>
       </c>
       <c r="R58" t="n">
-        <v>7029085</v>
+        <v>7029250</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8070,7 +8036,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8080,12 +8046,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (25 cm dbh) i gammal granskog</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8096,21 +8062,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -8127,10 +8078,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122715650</v>
+        <v>122715739</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8143,21 +8094,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8167,13 +8118,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452125</v>
+        <v>452142</v>
       </c>
       <c r="R59" t="n">
-        <v>7028994</v>
+        <v>7029004</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8202,7 +8153,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8212,7 +8163,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8239,10 +8195,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715754</v>
+        <v>122715547</v>
       </c>
       <c r="B60" t="n">
-        <v>79807</v>
+        <v>79882</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8255,21 +8211,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8279,13 +8235,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452130</v>
+        <v>452141</v>
       </c>
       <c r="R60" t="n">
-        <v>7029002</v>
+        <v>7028992</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8314,7 +8270,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8324,12 +8280,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8344,22 +8300,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122720084</v>
+        <v>122719930</v>
       </c>
       <c r="B61" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8372,26 +8328,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8405,13 +8361,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452101</v>
+        <v>452148</v>
       </c>
       <c r="R61" t="n">
-        <v>7029256</v>
+        <v>7029296</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8440,7 +8396,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8450,12 +8406,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8470,22 +8426,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715130</v>
+        <v>122720266</v>
       </c>
       <c r="B62" t="n">
-        <v>90963</v>
+        <v>77699</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8494,25 +8450,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1205</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8522,13 +8478,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452148</v>
+        <v>452125</v>
       </c>
       <c r="R62" t="n">
-        <v>7029055</v>
+        <v>7029254</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8557,7 +8513,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8567,12 +8523,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8587,22 +8543,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716687</v>
+        <v>122720127</v>
       </c>
       <c r="B63" t="n">
-        <v>90952</v>
+        <v>79848</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8615,27 +8571,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8644,13 +8609,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451933</v>
+        <v>452123</v>
       </c>
       <c r="R63" t="n">
-        <v>7028984</v>
+        <v>7029202</v>
       </c>
       <c r="S63" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8679,7 +8644,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8689,12 +8654,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8721,7 +8686,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122720354</v>
+        <v>122716428</v>
       </c>
       <c r="B64" t="n">
         <v>74863</v>
@@ -8761,13 +8726,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452114</v>
+        <v>451979</v>
       </c>
       <c r="R64" t="n">
-        <v>7029211</v>
+        <v>7029020</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8796,7 +8761,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8806,7 +8771,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8838,10 +8803,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122716868</v>
+        <v>122719902</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8854,27 +8819,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8883,13 +8852,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451931</v>
+        <v>452150</v>
       </c>
       <c r="R65" t="n">
-        <v>7029005</v>
+        <v>7029301</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8918,7 +8887,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8928,12 +8897,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg (37 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8947,17 +8916,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8975,10 +8944,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122719912</v>
+        <v>122715877</v>
       </c>
       <c r="B66" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8987,50 +8956,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452222</v>
+        <v>452106</v>
       </c>
       <c r="R66" t="n">
-        <v>7029287</v>
+        <v>7028977</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9059,7 +9019,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9069,12 +9029,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gran bredvid sälj</t>
+          <t>På bark på stam av levande gammal asp 48 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9085,26 +9045,41 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122716759</v>
+        <v>122719770</v>
       </c>
       <c r="B67" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9113,30 +9088,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9150,13 +9125,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451898</v>
+        <v>452163</v>
       </c>
       <c r="R67" t="n">
-        <v>7028975</v>
+        <v>7029302</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9185,7 +9160,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9195,12 +9170,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gran intill under jätteasp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9220,17 +9195,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122716633</v>
+        <v>122716868</v>
       </c>
       <c r="B68" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9239,31 +9214,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9272,13 +9247,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>451941</v>
+        <v>451931</v>
       </c>
       <c r="R68" t="n">
-        <v>7028960</v>
+        <v>7029005</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9307,7 +9282,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9317,12 +9292,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (28 cm dbh ) i gammal granskog</t>
+          <t>Ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9336,17 +9311,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9364,10 +9339,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122719930</v>
+        <v>122720532</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>78847</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9380,26 +9355,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9407,19 +9382,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452148</v>
+        <v>452156</v>
       </c>
       <c r="R69" t="n">
-        <v>7029296</v>
+        <v>7029109</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9448,7 +9428,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9458,12 +9438,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9474,6 +9454,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9490,10 +9485,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122715067</v>
+        <v>122715131</v>
       </c>
       <c r="B70" t="n">
-        <v>79751</v>
+        <v>77699</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9502,25 +9497,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9530,13 +9525,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452163</v>
+        <v>452147</v>
       </c>
       <c r="R70" t="n">
-        <v>7029067</v>
+        <v>7029041</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9565,7 +9560,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9575,12 +9570,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9591,41 +9586,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122719982</v>
+        <v>122716787</v>
       </c>
       <c r="B71" t="n">
-        <v>79022</v>
+        <v>79807</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9638,27 +9618,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6459</v>
+        <v>229497</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9667,13 +9647,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452143</v>
+        <v>451914</v>
       </c>
       <c r="R71" t="n">
-        <v>7029283</v>
+        <v>7028996</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9702,7 +9682,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9712,12 +9692,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På grenar på levande gran stående under jätteasp (70 cm dbh)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9731,17 +9711,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9759,10 +9739,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122715140</v>
+        <v>122715391</v>
       </c>
       <c r="B72" t="n">
-        <v>57631</v>
+        <v>79807</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9771,50 +9751,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452148</v>
+        <v>452136</v>
       </c>
       <c r="R72" t="n">
-        <v>7029055</v>
+        <v>7029025</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9843,7 +9814,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9853,12 +9824,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9885,10 +9856,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122715120</v>
+        <v>122717554</v>
       </c>
       <c r="B73" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9897,41 +9868,55 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452148</v>
+        <v>452007</v>
       </c>
       <c r="R73" t="n">
-        <v>7029055</v>
+        <v>7029050</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9960,7 +9945,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9970,12 +9955,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9986,6 +9971,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -10002,7 +10002,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122716494</v>
+        <v>122716459</v>
       </c>
       <c r="B74" t="n">
         <v>57478</v>
@@ -10050,10 +10050,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451971</v>
+        <v>451969</v>
       </c>
       <c r="R74" t="n">
-        <v>7029000</v>
+        <v>7029008</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
+          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10111,21 +10111,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -10142,7 +10127,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122717285</v>
+        <v>122716494</v>
       </c>
       <c r="B75" t="n">
         <v>57478</v>
@@ -10190,10 +10175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452000</v>
+        <v>451971</v>
       </c>
       <c r="R75" t="n">
-        <v>7029026</v>
+        <v>7029000</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10225,7 +10210,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10235,12 +10220,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
+          <t>Relativt färska ringhack, från 1 till 8 meters höjd på gammal levande gran (27 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10251,6 +10236,21 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10392,10 +10392,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122716081</v>
+        <v>122717285</v>
       </c>
       <c r="B77" t="n">
-        <v>78954</v>
+        <v>57478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10404,38 +10404,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>230552</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10443,13 +10440,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452077</v>
+        <v>452000</v>
       </c>
       <c r="R77" t="n">
-        <v>7029012</v>
+        <v>7029026</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10478,7 +10475,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10488,12 +10485,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med relativt färska ringhack på gammal levande gran (39 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10502,24 +10499,8 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10536,10 +10517,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122716459</v>
+        <v>122716081</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>78954</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10548,35 +10529,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>230552</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10584,13 +10568,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>451969</v>
+        <v>452077</v>
       </c>
       <c r="R78" t="n">
-        <v>7029008</v>
+        <v>7029012</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10619,7 +10603,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10629,12 +10613,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, relativt färska, på gammal levande gran (40 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10643,8 +10627,24 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -1081,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122717157</v>
+        <v>122715838</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,39 +1097,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451983</v>
+        <v>452109</v>
       </c>
       <c r="R5" t="n">
-        <v>7029027</v>
+        <v>7029006</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,7 +1156,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1171,12 +1166,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,6 +1182,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1203,10 +1213,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715838</v>
+        <v>122717157</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,34 +1229,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452109</v>
+        <v>451983</v>
       </c>
       <c r="R6" t="n">
-        <v>7029006</v>
+        <v>7029027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1293,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,12 +1303,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,21 +1319,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122720150</v>
+        <v>122716346</v>
       </c>
       <c r="B7" t="n">
-        <v>77699</v>
+        <v>74868</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452132</v>
+        <v>451984</v>
       </c>
       <c r="R7" t="n">
-        <v>7029266</v>
+        <v>7029029</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122716346</v>
+        <v>122720303</v>
       </c>
       <c r="B8" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,37 +1483,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451984</v>
+        <v>452124</v>
       </c>
       <c r="R8" t="n">
-        <v>7029029</v>
+        <v>7029259</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1551,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,12 +1561,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande gran (44 cm dbh) i gammal granskog i fuktsvacka</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,10 +1608,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122720303</v>
+        <v>122720150</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,46 +1624,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452124</v>
+        <v>452132</v>
       </c>
       <c r="R9" t="n">
-        <v>7029259</v>
+        <v>7029266</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122719701</v>
+        <v>122720379</v>
       </c>
       <c r="B21" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3141,30 +3141,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452180</v>
+        <v>452127</v>
       </c>
       <c r="R21" t="n">
-        <v>7029296</v>
+        <v>7029209</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3243,19 +3243,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122720379</v>
+        <v>122715784</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452127</v>
+        <v>452116</v>
       </c>
       <c r="R22" t="n">
-        <v>7029209</v>
+        <v>7029000</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3381,10 +3381,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122715784</v>
+        <v>122719701</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3393,30 +3393,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452116</v>
+        <v>452180</v>
       </c>
       <c r="R23" t="n">
-        <v>7029000</v>
+        <v>7029296</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3495,12 +3495,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122719605</v>
+        <v>122715739</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7968,46 +7968,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452187</v>
+        <v>452142</v>
       </c>
       <c r="R58" t="n">
-        <v>7029250</v>
+        <v>7029004</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8036,7 +8027,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8046,12 +8037,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8066,22 +8057,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122715739</v>
+        <v>122719605</v>
       </c>
       <c r="B59" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8094,37 +8085,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452142</v>
+        <v>452187</v>
       </c>
       <c r="R59" t="n">
-        <v>7029004</v>
+        <v>7029250</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8183,12 +8183,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8438,10 +8438,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122720266</v>
+        <v>122716428</v>
       </c>
       <c r="B62" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8454,21 +8454,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8478,13 +8478,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452125</v>
+        <v>451979</v>
       </c>
       <c r="R62" t="n">
-        <v>7029254</v>
+        <v>7029020</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8686,10 +8686,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122716428</v>
+        <v>122720266</v>
       </c>
       <c r="B64" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8702,21 +8702,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451979</v>
+        <v>452125</v>
       </c>
       <c r="R64" t="n">
-        <v>7029020</v>
+        <v>7029254</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9739,10 +9739,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122715391</v>
+        <v>122717554</v>
       </c>
       <c r="B72" t="n">
-        <v>79807</v>
+        <v>79718</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9751,41 +9751,55 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>389</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452136</v>
+        <v>452007</v>
       </c>
       <c r="R72" t="n">
-        <v>7029025</v>
+        <v>7029050</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9814,7 +9828,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9824,12 +9838,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9840,6 +9854,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9856,10 +9885,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122717554</v>
+        <v>122715391</v>
       </c>
       <c r="B73" t="n">
-        <v>79718</v>
+        <v>79807</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9868,55 +9897,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>389</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452007</v>
+        <v>452136</v>
       </c>
       <c r="R73" t="n">
-        <v>7029050</v>
+        <v>7029025</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9945,7 +9960,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9955,12 +9970,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (40 cm dbh, ca 140 år) i gammal granskog. Med apothecier och lite isidier</t>
+          <t>På bark på stam av levande gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9971,21 +9986,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -6288,10 +6288,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717199</v>
+        <v>122715191</v>
       </c>
       <c r="B45" t="n">
-        <v>77699</v>
+        <v>79751</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6300,25 +6300,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6328,13 +6328,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451981</v>
+        <v>452150</v>
       </c>
       <c r="R45" t="n">
-        <v>7029020</v>
+        <v>7029062</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
+          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6389,21 +6389,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6420,10 +6405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122715191</v>
+        <v>122718273</v>
       </c>
       <c r="B46" t="n">
-        <v>79751</v>
+        <v>57589</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6436,37 +6421,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452150</v>
+        <v>452012</v>
       </c>
       <c r="R46" t="n">
-        <v>7029062</v>
+        <v>7029081</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6495,7 +6489,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6505,12 +6499,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal asp (45 cm dbh) i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6537,10 +6531,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122718273</v>
+        <v>122717199</v>
       </c>
       <c r="B47" t="n">
-        <v>57589</v>
+        <v>77699</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6549,47 +6543,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452012</v>
+        <v>451981</v>
       </c>
       <c r="R47" t="n">
-        <v>7029081</v>
+        <v>7029020</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6621,7 +6606,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6631,12 +6616,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6647,6 +6632,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -8438,10 +8438,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122716428</v>
+        <v>122720266</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8454,21 +8454,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8478,13 +8478,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451979</v>
+        <v>452125</v>
       </c>
       <c r="R62" t="n">
-        <v>7029020</v>
+        <v>7029254</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran som brutits av</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8686,10 +8686,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122720266</v>
+        <v>122716428</v>
       </c>
       <c r="B64" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8702,21 +8702,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452125</v>
+        <v>451979</v>
       </c>
       <c r="R64" t="n">
-        <v>7029254</v>
+        <v>7029020</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gran som brutits av</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -1081,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122715838</v>
+        <v>122717157</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,34 +1097,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452109</v>
+        <v>451983</v>
       </c>
       <c r="R5" t="n">
-        <v>7029006</v>
+        <v>7029027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1166,12 +1171,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,21 +1187,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1213,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122717157</v>
+        <v>122715838</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1229,39 +1219,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451983</v>
+        <v>452109</v>
       </c>
       <c r="R6" t="n">
-        <v>7029027</v>
+        <v>7029006</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1303,12 +1288,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,6 +1304,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -8195,10 +8195,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715547</v>
+        <v>122719930</v>
       </c>
       <c r="B60" t="n">
-        <v>79882</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8207,20 +8207,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8228,20 +8228,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452141</v>
+        <v>452148</v>
       </c>
       <c r="R60" t="n">
-        <v>7028992</v>
+        <v>7029296</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8270,7 +8279,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8280,12 +8289,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8300,22 +8309,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122719930</v>
+        <v>122715547</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8324,20 +8333,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8345,29 +8354,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452148</v>
+        <v>452141</v>
       </c>
       <c r="R61" t="n">
-        <v>7029296</v>
+        <v>7028992</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8426,12 +8426,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 8493-2025 artfynd.xlsx
+++ b/artfynd/A 8493-2025 artfynd.xlsx
@@ -1081,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122717157</v>
+        <v>122715838</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,39 +1097,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451983</v>
+        <v>452109</v>
       </c>
       <c r="R5" t="n">
-        <v>7029027</v>
+        <v>7029006</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,7 +1156,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1171,12 +1166,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,6 +1182,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1203,10 +1213,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715838</v>
+        <v>122717157</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,34 +1229,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452109</v>
+        <v>451983</v>
       </c>
       <c r="R6" t="n">
-        <v>7029006</v>
+        <v>7029027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1293,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,12 +1303,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (14 cm dbh, ca 140 år gammal) i gammal granskog</t>
+          <t>Ringhack på gammal levande gran (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,21 +1319,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -7952,10 +7952,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122715739</v>
+        <v>122719605</v>
       </c>
       <c r="B58" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7968,37 +7968,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452142</v>
+        <v>452187</v>
       </c>
       <c r="R58" t="n">
-        <v>7029004</v>
+        <v>7029250</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8027,7 +8036,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8037,12 +8046,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På äldre granskog i äldre granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8057,22 +8066,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122719605</v>
+        <v>122715739</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8085,46 +8094,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hallägden, Hallägden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452187</v>
+        <v>452142</v>
       </c>
       <c r="R59" t="n">
-        <v>7029250</v>
+        <v>7029004</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På äldre granskog i äldre granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8183,22 +8183,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122719930</v>
+        <v>122715547</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8207,20 +8207,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
      